--- a/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>374</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J375"/>
+  <dimension ref="A1:J382"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1121,13 +1121,13 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>이미지 자리의 비율</v>
+        <v>거르는 단추 — 필터·정렬·탭이 목록을 실제로 바꾸는지</v>
       </c>
       <c r="G10" t="str">
-        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
+        <v>필터 칩을 눌러 목록이 줄어드는지 세어 본다. 칩에 개수가 적혀 있으면(예: 기본 교육 2) 그 수만큼만 남는지 센다. 정렬도 바꿔 보고, 아무것도 안 남는 조건도 눌러 본다. ⚠ 화면을 «보는» 것으로는 안 잡힌다 — 반드시 눌러서 목록 개수를 세어야 한다.</v>
       </c>
       <c r="H10" t="str">
-        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
+        <v>색만 바뀌지 않고 «보이는 항목»이 달라진다. 적힌 개수와 실제 개수가 같다. 하나도 안 남으면 「결과가 없습니다」가 나온다.</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>공통 요소가 모든 화면에서 같은지</v>
+        <v>썸네일 · 배너 · 겹쳐 놓은 단추가 정말 눌리는지</v>
       </c>
       <c r="G11" t="str">
-        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
+        <v>카드 썸네일과 배너를 하나씩 눌러 어디로 가는지 본다. 사진 위에 얹은 단추(찜 하트·빠른 담기)는 그 자리에서 `document.elementFromPoint(x, y)` 로 맨 위에 무엇이 있는지 본다. ⚠ 그림이라 눌러 보기를 잊기 쉽다.</v>
       </c>
       <c r="H11" t="str">
-        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
+        <v>썸네일·배너가 모두 어딘가로 간다. 겹쳐 놓은 단추를 누르면 그 단추가 눌리지, 밑에 깔린 링크로 넘어가지 않는다.</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -1185,13 +1185,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>좁은 화면(모바일)에서 가로 스크롤</v>
+        <v>쪽 번호가 걸러진 결과를 따라가는지</v>
       </c>
       <c r="G12" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>조건을 걸어 목록을 줄인 뒤 쪽 번호를 본다. 3쪽을 보다가 조건을 바꿔 본다.</v>
       </c>
       <c r="H12" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>한 쪽에 다 들어가면 쪽 번호가 사라진다. 조건을 바꾸면 1쪽으로 돌아간다. 쪽을 누르면 목록이 실제로 달라진다.</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -1202,28 +1202,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B13" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C13" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너</v>
+        <v>화면끼리 숫자와 고른 값이 맞는지</v>
       </c>
       <c r="G13" t="str">
-        <v>'홈'에서 빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>수량·옵션·할부·기간을 골라 놓고 다음 화면에서 그대로 있는지 본다. 같은 것이 나오는 화면 둘을 나란히 열어 진도·개수·합계·N/M·남은 것을 대 본다. 「이번 주」·「D-3」은 오늘 날짜로 다시 센다.</v>
       </c>
       <c r="H13" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>앞 화면에서 고른 값이 뒤 화면에 그대로 있다. 같은 값이 화면마다 같다. 합계가 항목의 합과 맞고, 12/18이면 남은 것은 6이다.</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B14" t="str">
         <v/>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)</v>
+        <v>가게 정보를 바꿨을 때 옛 이름이 남는 곳</v>
       </c>
       <c r="G14" t="str">
-        <v>'홈' 화면을 열고 카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>데이터 파일의 상호를 다른 이름으로 바꾸고 사이트를 다시 연다. 화면·머리말·꼬리말은 물론 브라우저 «탭 제목»까지 본다.</v>
       </c>
       <c r="H14" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>어느 화면에도 옛 이름이 남지 않는다. 탭 제목과 검색 설명까지 새 이름으로 바뀐다.</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -1266,7 +1266,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B15" t="str">
         <v/>
@@ -1281,13 +1281,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>이번 주 인기 장비 8개 카드</v>
+        <v>이미지 자리의 비율</v>
       </c>
       <c r="G15" t="str">
-        <v>'홈' 화면을 열고 이번 주 인기 장비 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'400×400' 처럼 크기가 적힌 이미지 자리가 실제로 그 비율인지 본다.</v>
       </c>
       <c r="H15" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>적힌 대로 보인다. 목록 안에서 늘어나 타원이 되지 않는다.</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -1298,7 +1298,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B16" t="str">
         <v/>
@@ -1313,13 +1313,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>이번 주말 남은 장비 캐러셀(잔여 수량 표시)</v>
+        <v>공통 요소가 모든 화면에서 같은지</v>
       </c>
       <c r="G16" t="str">
-        <v>'홈'에서 이번 주말 남은 장비 캐러셀(잔여 수량 표시)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>여러 화면을 오가며 헤더·푸터·버튼 모양이 같은지 본다.</v>
       </c>
       <c r="H16" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>화면마다 다시 만든 흔적 없이 같은 모습이다.</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -1330,7 +1330,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B17" t="str">
         <v/>
@@ -1345,13 +1345,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>세트로 빌리면 싼 패키지 안내 배너</v>
+        <v>읽기 폭이 한 값인지 — 글이 주인공인 화면들</v>
       </c>
       <c r="G17" t="str">
-        <v>'홈'에서 세트로 빌리면 싼 패키지 안내 배너를 눌러 본다.</v>
+        <v>상세 본문·안내·약관처럼 글이 긴 화면 서넛을 나란히 열어, 글줄이 시작하고 끝나는 자리가 같은지 본다.</v>
       </c>
       <c r="H17" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>화면마다 본문 폭이 같다. 어떤 화면은 넓고 어떤 화면은 좁아 서로 다른 사이트처럼 보이지 않는다.</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1362,7 +1362,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B18" t="str">
         <v/>
@@ -1377,13 +1377,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>처음이신가요 3단계 안내(고른다-받는다-돌려준다)</v>
+        <v>줄어드는 지점이 두 곳뿐인지</v>
       </c>
       <c r="G18" t="str">
-        <v>'홈' 화면을 열고 처음이신가요 3단계 안내(고른다-받는다-돌려준다)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>브라우저 폭을 천천히 줄이며 칸 수가 바뀌는 지점을 세어 본다.</v>
       </c>
       <c r="H18" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>태블릿 가로(1024px)와 세로(720px), 두 곳에서만 바뀐다. 그 사이에 지어낸 지점이 없다.</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B19" t="str">
         <v/>
@@ -1409,13 +1409,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>실제 이용 후기 슬라이드 5개</v>
+        <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>'홈' 화면을 열고 실제 이용 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
       </c>
       <c r="H19" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1429,25 +1429,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B20" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F20" t="str">
-        <v>보증금</v>
+        <v>빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈' 화면에서 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H20" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>연체료 정책 요약 카드</v>
+        <v>카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈'의 연체료 정책 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면을 열고 카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>매장 위치와 운영시간</v>
+        <v>이번 주 인기 장비 8개 카드</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면에서 매장 위치와 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이번 주 인기 장비 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H22" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>하단 카톡 채널 안내</v>
+        <v>이번 주말 남은 장비 캐러셀(잔여 수량 표시)</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈' 화면에서 하단 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 이번 주말 남은 장비 캐러셀(잔여 수량 표시)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H23" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,28 +1554,28 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B24" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v>카테고리 홈</v>
+        <v/>
       </c>
       <c r="D24" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E24" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>카테고리 대표 사진과 한 줄 소개</v>
+        <v>세트로 빌리면 싼 패키지 안내 배너</v>
       </c>
       <c r="G24" t="str">
-        <v>'카테고리 홈' 화면에서 카테고리 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 세트로 빌리면 싼 패키지 안내 배너를 눌러 본다.</v>
       </c>
       <c r="H24" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,10 +1601,10 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>이 종류 인기 장비 8개</v>
+        <v>처음이신가요 3단계 안내(고른다-받는다-돌려준다)</v>
       </c>
       <c r="G25" t="str">
-        <v>'카테고리 홈' 화면을 열고 이 종류 인기 장비 8개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면을 열고 처음이신가요 3단계 안내(고른다-받는다-돌려준다)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H25" t="str">
         <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
         <v/>
@@ -1633,13 +1633,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>하위 종류 필터 칩</v>
+        <v>실제 이용 후기 슬라이드 5개</v>
       </c>
       <c r="G26" t="str">
-        <v>'카테고리 홈'에서 하위 종류 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면을 열고 실제 이용 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1650,7 +1650,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B27" t="str">
         <v/>
@@ -1665,10 +1665,10 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>이 종류를 처음 빌리는 분을 위한 고르는 법</v>
+        <v>보증금</v>
       </c>
       <c r="G27" t="str">
-        <v>'카테고리 홈' 화면에서 이 종류를 처음 빌리는 분을 위한 고르는 법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H27" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B28" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>함께 빌리면 좋은 장비 추천</v>
+        <v>연체료 정책 요약 카드</v>
       </c>
       <c r="G28" t="str">
-        <v>'카테고리 홈' 화면에서 함께 빌리면 좋은 장비 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'의 연체료 정책 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H28" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B29" t="str">
         <v/>
@@ -1729,13 +1729,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>이 종류 자주 묻는 질문 4개</v>
+        <v>매장 위치와 운영시간</v>
       </c>
       <c r="G29" t="str">
-        <v>'카테고리 홈' 화면을 열고 이 종류 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 매장 위치와 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H29" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B30" t="str">
         <v/>
@@ -1761,10 +1761,10 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>이 종류 후기 모음</v>
+        <v>하단 카톡 채널 안내</v>
       </c>
       <c r="G30" t="str">
-        <v>'카테고리 홈' 화면에서 이 종류 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 하단 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H30" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1781,22 +1781,22 @@
         <v>SCN-002</v>
       </c>
       <c r="B31" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C31" t="str">
-        <v/>
+        <v>카테고리 홈</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E31" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F31" t="str">
-        <v>보관</v>
+        <v>카테고리 대표 사진과 한 줄 소개</v>
       </c>
       <c r="G31" t="str">
-        <v>'카테고리 홈' 화면에서 보관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 카테고리 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H31" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1825,13 +1825,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>사용 주의사항 안내</v>
+        <v>이 종류 인기 장비 8개</v>
       </c>
       <c r="G32" t="str">
-        <v>'카테고리 홈' 화면에서 사용 주의사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면을 열고 이 종류 인기 장비 8개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H32" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1842,25 +1842,25 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B33" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C33" t="str">
-        <v>기간으로 찾기 - 결과</v>
+        <v/>
       </c>
       <c r="D33" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E33" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>검색 조건 요약 바(기간·종류·인원)</v>
+        <v>하위 종류 필터 칩</v>
       </c>
       <c r="G33" t="str">
-        <v>'기간으로 찾기 - 결과'에서 검색 조건 요약 바(기간·종류·인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈'에서 하위 종류 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H33" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,10 +1889,10 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>기간 다시 고르기 달력</v>
+        <v>이 종류를 처음 빌리는 분을 위한 고르는 법</v>
       </c>
       <c r="G34" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 기간 다시 고르기 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 이 종류를 처음 빌리는 분을 위한 고르는 법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H34" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -1921,13 +1921,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)</v>
+        <v>함께 빌리면 좋은 장비 추천</v>
       </c>
       <c r="G35" t="str">
-        <v>'기간으로 찾기 - 결과'에서 결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈' 화면에서 함께 빌리면 좋은 장비 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H35" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I35" t="str">
         <v/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -1953,13 +1953,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)</v>
+        <v>이 종류 자주 묻는 질문 4개</v>
       </c>
       <c r="G36" t="str">
-        <v>'기간으로 찾기 - 결과'에서 필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈' 화면을 열고 이 종류 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B37" t="str">
         <v/>
@@ -1985,13 +1985,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)</v>
+        <v>이 종류 후기 모음</v>
       </c>
       <c r="G37" t="str">
-        <v>'기간으로 찾기 - 결과'의 장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 이 종류 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H37" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -2002,7 +2002,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B38" t="str">
         <v/>
@@ -2017,10 +2017,10 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>그 기간에 마감된 장비는 흐리게 뒤로</v>
+        <v>보관</v>
       </c>
       <c r="G38" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 그 기간에 마감된 장비는 흐리게 뒤로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 보관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H38" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2034,7 +2034,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B39" t="str">
         <v/>
@@ -2049,10 +2049,10 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>다음 가능한 날짜 안내</v>
+        <v>사용 주의사항 안내</v>
       </c>
       <c r="G39" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 다음 가능한 날짜 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 사용 주의사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H39" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2069,22 +2069,22 @@
         <v>SCN-003</v>
       </c>
       <c r="B40" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C40" t="str">
-        <v/>
+        <v>기간으로 찾기 - 결과</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>HO-03</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F40" t="str">
-        <v>더 보기 페이지네이션</v>
+        <v>검색 조건 요약 바(기간·종류·인원)</v>
       </c>
       <c r="G40" t="str">
-        <v>'기간으로 찾기 - 결과'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기간으로 찾기 - 결과'에서 검색 조건 요약 바(기간·종류·인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H40" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -2098,28 +2098,28 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B41" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C41" t="str">
-        <v>결과 없음 - 그 기간에 빈 장비가 없음</v>
+        <v/>
       </c>
       <c r="D41" t="str">
-        <v>HO-04</v>
+        <v/>
       </c>
       <c r="E41" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v>고른 기간과 조건 요약</v>
+        <v>기간 다시 고르기 달력</v>
       </c>
       <c r="G41" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 고른 기간과 조건 요약이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 기간 다시 고르기 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H41" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B42" t="str">
         <v/>
@@ -2145,13 +2145,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>왜 없는지 한 줄 설명(주말·연휴에 몰린다)</v>
+        <v>결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)</v>
       </c>
       <c r="G42" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 왜 없는지 한 줄 설명(주말·연휴에 몰린다)가 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H42" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>기간을 앞뒤로 넓혀 보기 버튼</v>
+        <v>필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)</v>
       </c>
       <c r="G43" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 기간을 앞뒤로 넓혀 보기 버튼이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>빌릴 수 있는 가까운 날짜 3개 추천 칩</v>
+        <v>장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)</v>
       </c>
       <c r="G44" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 빌릴 수 있는 가까운 날짜 3개 추천 칩이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'의 장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,13 +2241,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>조건을 풀어 보기(브랜드·수령 방법 해제)</v>
+        <v>그 기간에 마감된 장비는 흐리게 뒤로</v>
       </c>
       <c r="G45" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 조건을 풀어 보기(브랜드·수령 방법 해제)가 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 그 기간에 마감된 장비는 흐리게 뒤로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H45" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -2258,7 +2258,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B46" t="str">
         <v/>
@@ -2273,13 +2273,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>자리 나면 알려드리기 신청</v>
+        <v>다음 가능한 날짜 안내</v>
       </c>
       <c r="G46" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 자리 나면 알려드리기 신청이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 다음 가능한 날짜 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H46" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2290,7 +2290,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B47" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>비슷한 장비 대체 추천 4개</v>
+        <v>더 보기 페이지네이션</v>
       </c>
       <c r="G47" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 비슷한 장비 대체 추천 4개가 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H47" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2322,28 +2322,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B48" t="str">
         <v>홈</v>
       </c>
       <c r="C48" t="str">
-        <v>기획전·특가</v>
+        <v>결과 없음 - 그 기간에 빈 장비가 없음</v>
       </c>
       <c r="D48" t="str">
-        <v>HO-05</v>
+        <v>HO-04</v>
       </c>
       <c r="E48" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F48" t="str">
-        <v>기획전 대표 배너와 남은 기간 카운트다운</v>
+        <v>고른 기간과 조건 요약</v>
       </c>
       <c r="G48" t="str">
-        <v>'기획전·특가'에서 기획전 대표 배너와 남은 기간 카운트다운을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 고른 기간과 조건 요약이 보이는지 확인한다.</v>
       </c>
       <c r="H48" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -2369,13 +2369,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>기획전 쿠폰 받기</v>
+        <v>왜 없는지 한 줄 설명(주말·연휴에 몰린다)</v>
       </c>
       <c r="G49" t="str">
-        <v>'기획전·특가' 화면에서 기획전 쿠폰 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 왜 없는지 한 줄 설명(주말·연휴에 몰린다)가 보이는지 확인한다.</v>
       </c>
       <c r="H49" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2401,13 +2401,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>특가 장비 목록(정가·특가·할인율)</v>
+        <v>기간을 앞뒤로 넓혀 보기 버튼</v>
       </c>
       <c r="G50" t="str">
-        <v>'기획전·특가'의 특가 장비 목록(정가·특가·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 기간을 앞뒤로 넓혀 보기 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H50" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>평일 할인 안내(월~목 30% 싸다)</v>
+        <v>빌릴 수 있는 가까운 날짜 3개 추천 칩</v>
       </c>
       <c r="G51" t="str">
-        <v>'기획전·특가' 화면에서 평일 할인 안내(월~목 30% 싸다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 빌릴 수 있는 가까운 날짜 3개 추천 칩이 보이는지 확인한다.</v>
       </c>
       <c r="H51" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>장기 대여 할인 단계표(7일 이상·30일 이상)</v>
+        <v>조건을 풀어 보기(브랜드·수령 방법 해제)</v>
       </c>
       <c r="G52" t="str">
-        <v>'기획전·특가' 화면에서 장기 대여 할인 단계표(7일 이상·30일 이상)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 조건을 풀어 보기(브랜드·수령 방법 해제)가 보이는지 확인한다.</v>
       </c>
       <c r="H52" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -2497,13 +2497,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>첫 대여 고객 보증금 면제 안내</v>
+        <v>자리 나면 알려드리기 신청</v>
       </c>
       <c r="G53" t="str">
-        <v>'기획전·특가' 화면에서 첫 대여 고객 보증금 면제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 자리 나면 알려드리기 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H53" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2514,7 +2514,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B54" t="str">
         <v/>
@@ -2529,13 +2529,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>기획전 이용 조건과 제외 대상</v>
+        <v>비슷한 장비 대체 추천 4개</v>
       </c>
       <c r="G54" t="str">
-        <v>'기획전·특가' 화면에서 기획전 이용 조건과 제외 대상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 비슷한 장비 대체 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H54" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2549,25 +2549,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B55" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C55" t="str">
-        <v/>
+        <v>기획전·특가</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>HO-05</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F55" t="str">
-        <v>종료된 기획전 안내</v>
+        <v>기획전 대표 배너와 남은 기간 카운트다운</v>
       </c>
       <c r="G55" t="str">
-        <v>'기획전·특가' 화면에서 종료된 기획전 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가'에서 기획전 대표 배너와 남은 기간 카운트다운을 눌러 본다.</v>
       </c>
       <c r="H55" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2578,25 +2578,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B56" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C56" t="str">
-        <v>장비 목록</v>
+        <v/>
       </c>
       <c r="D56" t="str">
-        <v>PD-01</v>
+        <v/>
       </c>
       <c r="E56" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v>종류</v>
+        <v>기획전 쿠폰 받기</v>
       </c>
       <c r="G56" t="str">
-        <v>'장비 목록' 화면에서 종류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 기획전 쿠폰 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H56" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -2625,13 +2625,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>브랜드</v>
+        <v>특가 장비 목록(정가·특가·할인율)</v>
       </c>
       <c r="G57" t="str">
-        <v>'장비 목록' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가'의 특가 장비 목록(정가·특가·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H57" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2657,10 +2657,10 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>대여료</v>
+        <v>평일 할인 안내(월~목 30% 싸다)</v>
       </c>
       <c r="G58" t="str">
-        <v>'장비 목록' 화면에서 대여료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 평일 할인 안내(월~목 30% 싸다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H58" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2689,13 +2689,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>보증금 필터</v>
+        <v>장기 대여 할인 단계표(7일 이상·30일 이상)</v>
       </c>
       <c r="G59" t="str">
-        <v>'장비 목록'에서 보증금 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기획전·특가' 화면에서 장기 대여 할인 단계표(7일 이상·30일 이상)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H59" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>정렬(추천·낮은 대여료·많이 빌린 순·별점)</v>
+        <v>첫 대여 고객 보증금 면제 안내</v>
       </c>
       <c r="G60" t="str">
-        <v>'장비 목록'에서 정렬(추천·낮은 대여료·많이 빌린 순·별점)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기획전·특가' 화면에서 첫 대여 고객 보증금 면제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H60" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B61" t="str">
         <v/>
@@ -2753,13 +2753,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)</v>
+        <v>기획전 이용 조건과 제외 대상</v>
       </c>
       <c r="G61" t="str">
-        <v>'장비 목록'의 장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 기획전 이용 조건과 제외 대상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2770,7 +2770,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B62" t="str">
         <v/>
@@ -2785,13 +2785,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>고른 기간 표시와 바꾸기</v>
+        <v>종료된 기획전 안내</v>
       </c>
       <c r="G62" t="str">
-        <v>'장비 목록'의 고른 기간 표시와 바꾸기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'기획전·특가' 화면에서 종료된 기획전 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H62" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2805,22 +2805,22 @@
         <v>SCN-006</v>
       </c>
       <c r="B63" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C63" t="str">
-        <v/>
+        <v>장비 목록</v>
       </c>
       <c r="D63" t="str">
-        <v/>
+        <v>PD-01</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F63" t="str">
-        <v>그 기간 불가 장비 흐림 처리와 다음 가능일</v>
+        <v>종류</v>
       </c>
       <c r="G63" t="str">
-        <v>'장비 목록' 화면에서 그 기간 불가 장비 흐림 처리와 다음 가능일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 종류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2849,10 +2849,10 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>세트 패키지 섞어 보여주기</v>
+        <v>브랜드</v>
       </c>
       <c r="G64" t="str">
-        <v>'장비 목록' 화면에서 세트 패키지 섞어 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H64" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>무한 스크롤</v>
+        <v>대여료</v>
       </c>
       <c r="G65" t="str">
-        <v>'장비 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 대여료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H65" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2898,28 +2898,28 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B66" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C66" t="str">
-        <v>장비 상세</v>
+        <v/>
       </c>
       <c r="D66" t="str">
-        <v>PD-02</v>
+        <v/>
       </c>
       <c r="E66" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F66" t="str">
-        <v>장비 사진 갤러리 5장</v>
+        <v>보증금 필터</v>
       </c>
       <c r="G66" t="str">
-        <v>'장비 상세' 화면을 열고 장비 사진 갤러리 5장이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'장비 목록'에서 보증금 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H66" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>장비명</v>
+        <v>정렬(추천·낮은 대여료·많이 빌린 순·별점)</v>
       </c>
       <c r="G67" t="str">
-        <v>'장비 상세' 화면에서 장비명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'에서 정렬(추천·낮은 대여료·많이 빌린 순·별점)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,13 +2977,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>브랜드</v>
+        <v>장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)</v>
       </c>
       <c r="G68" t="str">
-        <v>'장비 상세' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'의 장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2994,7 +2994,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B69" t="str">
         <v/>
@@ -3009,13 +3009,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>모델과 별점</v>
+        <v>고른 기간 표시와 바꾸기</v>
       </c>
       <c r="G69" t="str">
-        <v>'장비 상세' 화면에서 모델과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'의 고른 기간 표시와 바꾸기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H69" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B70" t="str">
         <v/>
@@ -3041,10 +3041,10 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>1일 대여료와 고른 기간 총액</v>
+        <v>그 기간 불가 장비 흐림 처리와 다음 가능일</v>
       </c>
       <c r="G70" t="str">
-        <v>'장비 상세' 화면에서 1일 대여료와 고른 기간 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 그 기간 불가 장비 흐림 처리와 다음 가능일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3058,7 +3058,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B71" t="str">
         <v/>
@@ -3073,13 +3073,13 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>보증금 금액과 언제 돌려주는지</v>
+        <v>세트 패키지 섞어 보여주기</v>
       </c>
       <c r="G71" t="str">
-        <v>'장비 상세'의 보증금 금액과 언제 돌려주는지가 실제 데이터와 같은지 대조한다.</v>
+        <v>'장비 목록' 화면에서 세트 패키지 섞어 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B72" t="str">
         <v/>
@@ -3105,10 +3105,10 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>날짜별 재고 달력 열기</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G72" t="str">
-        <v>'장비 상세' 화면에서 날짜별 재고 달력 열기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H72" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3125,25 +3125,25 @@
         <v>SCN-007</v>
       </c>
       <c r="B73" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C73" t="str">
-        <v/>
+        <v>장비 상세</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>PD-02</v>
       </c>
       <c r="E73" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F73" t="str">
-        <v>대여 기간과 수량 고르기</v>
+        <v>장비 사진 갤러리 5장</v>
       </c>
       <c r="G73" t="str">
-        <v>'장비 상세' 화면에서 대여 기간과 수량 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면을 열고 장비 사진 갤러리 5장이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H73" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3169,10 +3169,10 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
+        <v>장비명</v>
       </c>
       <c r="G74" t="str">
-        <v>'장비 상세' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 장비명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H74" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3201,13 +3201,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>구성품 목록과 사진</v>
+        <v>브랜드</v>
       </c>
       <c r="G75" t="str">
-        <v>'장비 상세'의 구성품 목록과 사진을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H75" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3233,10 +3233,10 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>이용 안내(사용법·주의사항·금지사항)</v>
+        <v>모델과 별점</v>
       </c>
       <c r="G76" t="str">
-        <v>'장비 상세' 화면에서 이용 안내(사용법·주의사항·금지사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 모델과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H76" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3265,10 +3265,10 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>파손 시 배상 기준표</v>
+        <v>1일 대여료와 고른 기간 총액</v>
       </c>
       <c r="G77" t="str">
-        <v>'장비 상세' 화면에서 파손 시 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 1일 대여료와 고른 기간 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H77" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3297,13 +3297,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>함께 빌리면 좋은 장비</v>
+        <v>보증금 금액과 언제 돌려주는지</v>
       </c>
       <c r="G78" t="str">
-        <v>'장비 상세' 화면에서 함께 빌리면 좋은 장비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세'의 보증금 금액과 언제 돌려주는지가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H78" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3329,13 +3329,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>후기 목록과 별점 분포</v>
+        <v>날짜별 재고 달력 열기</v>
       </c>
       <c r="G79" t="str">
-        <v>'장비 상세'의 후기 목록과 별점 분포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 날짜별 재고 달력 열기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H79" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>하단 고정 바(총액·보증금·담기·바로 빌리기)</v>
+        <v>대여 기간과 수량 고르기</v>
       </c>
       <c r="G80" t="str">
-        <v>'장비 상세' 화면에서 하단 고정 바(총액·보증금·담기·바로 빌리기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 대여 기간과 수량 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H80" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3378,28 +3378,28 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B81" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C81" t="str">
-        <v>날짜별 가용 재고 달력</v>
+        <v/>
       </c>
       <c r="D81" t="str">
-        <v>PD-03</v>
+        <v/>
       </c>
       <c r="E81" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F81" t="str">
-        <v>월 단위 달력에 날짜마다 남은 수량 표시</v>
+        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
       </c>
       <c r="G81" t="str">
-        <v>'날짜별 가용 재고 달력'의 월 단위 달력에 날짜마다 남은 수량 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'장비 상세' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H81" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3410,7 +3410,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B82" t="str">
         <v/>
@@ -3425,13 +3425,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>다 나간 날은 흐리게 하고 못 고르게 막음</v>
+        <v>구성품 목록과 사진</v>
       </c>
       <c r="G82" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 다 나간 날은 흐리게 하고 못 고르게 막음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세'의 구성품 목록과 사진을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H82" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B83" t="str">
         <v/>
@@ -3457,10 +3457,10 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기</v>
+        <v>이용 안내(사용법·주의사항·금지사항)</v>
       </c>
       <c r="G83" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 이용 안내(사용법·주의사항·금지사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H83" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3474,7 +3474,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B84" t="str">
         <v/>
@@ -3489,10 +3489,10 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>고른 기간에 하루라도 모자라면 그 날을 짚어 알림</v>
+        <v>파손 시 배상 기준표</v>
       </c>
       <c r="G84" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간에 하루라도 모자라면 그 날을 짚어 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 파손 시 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H84" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B85" t="str">
         <v/>
@@ -3521,10 +3521,10 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>수량을 바꾸면 가능한 날이 다시 계산됨</v>
+        <v>함께 빌리면 좋은 장비</v>
       </c>
       <c r="G85" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 수량을 바꾸면 가능한 날이 다시 계산됨이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 함께 빌리면 좋은 장비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H85" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B86" t="str">
         <v/>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>최소</v>
+        <v>후기 목록과 별점 분포</v>
       </c>
       <c r="G86" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 최소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세'의 후기 목록과 별점 분포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H86" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B87" t="str">
         <v/>
@@ -3585,10 +3585,10 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>최대 대여 일수 안내</v>
+        <v>하단 고정 바(총액·보증금·담기·바로 빌리기)</v>
       </c>
       <c r="G87" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 최대 대여 일수 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 하단 고정 바(총액·보증금·담기·바로 빌리기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H87" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3605,22 +3605,22 @@
         <v>SCN-008</v>
       </c>
       <c r="B88" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C88" t="str">
-        <v/>
+        <v>날짜별 가용 재고 달력</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>PD-03</v>
       </c>
       <c r="E88" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F88" t="str">
-        <v>요일별 대여료 차이 표시(주말 할증)</v>
+        <v>월 단위 달력에 날짜마다 남은 수량 표시</v>
       </c>
       <c r="G88" t="str">
-        <v>'날짜별 가용 재고 달력'의 요일별 대여료 차이 표시(주말 할증)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'날짜별 가용 재고 달력'의 월 단위 달력에 날짜마다 남은 수량 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H88" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -3649,10 +3649,10 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>준비</v>
+        <v>다 나간 날은 흐리게 하고 못 고르게 막음</v>
       </c>
       <c r="G89" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 다 나간 날은 흐리게 하고 못 고르게 막음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H89" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3681,10 +3681,10 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>점검에 필요한 날(반납 다음 날은 못 빌림) 안내</v>
+        <v>빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기</v>
       </c>
       <c r="G90" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 점검에 필요한 날(반납 다음 날은 못 빌림) 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H90" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3713,10 +3713,10 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>고른 기간 요약과 총액</v>
+        <v>고른 기간에 하루라도 모자라면 그 날을 짚어 알림</v>
       </c>
       <c r="G91" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간 요약과 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간에 하루라도 모자라면 그 날을 짚어 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H91" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3745,10 +3745,10 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>이 기간으로 예약하기</v>
+        <v>수량을 바꾸면 가능한 날이 다시 계산됨</v>
       </c>
       <c r="G92" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 이 기간으로 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 수량을 바꾸면 가능한 날이 다시 계산됨이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H92" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3762,25 +3762,25 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B93" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C93" t="str">
-        <v>옵션·부속품 고르기</v>
+        <v/>
       </c>
       <c r="D93" t="str">
-        <v>PD-04</v>
+        <v/>
       </c>
       <c r="E93" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F93" t="str">
-        <v>고른 장비와 기간 요약</v>
+        <v>최소</v>
       </c>
       <c r="G93" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 고른 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 최소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H93" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3794,7 +3794,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B94" t="str">
         <v/>
@@ -3809,10 +3809,10 @@
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>옵션 고르기(크기·색·구성)</v>
+        <v>최대 대여 일수 안내</v>
       </c>
       <c r="G94" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 옵션 고르기(크기·색·구성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 최대 대여 일수 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H94" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3826,7 +3826,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B95" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)</v>
+        <v>요일별 대여료 차이 표시(주말 할증)</v>
       </c>
       <c r="G95" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력'의 요일별 대여료 차이 표시(주말 할증)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H95" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3858,7 +3858,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B96" t="str">
         <v/>
@@ -3873,10 +3873,10 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>부속품별 대여료와 보증금</v>
+        <v>준비</v>
       </c>
       <c r="G96" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 부속품별 대여료와 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H96" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B97" t="str">
         <v/>
@@ -3905,10 +3905,10 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>보험 붙이기 선택(파손 면책 하루 3,000원)</v>
+        <v>점검에 필요한 날(반납 다음 날은 못 빌림) 안내</v>
       </c>
       <c r="G97" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 보험 붙이기 선택(파손 면책 하루 3,000원)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 점검에 필요한 날(반납 다음 날은 못 빌림) 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H97" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3922,7 +3922,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B98" t="str">
         <v/>
@@ -3937,10 +3937,10 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>면책 범위와 제외 사항 안내</v>
+        <v>고른 기간 요약과 총액</v>
       </c>
       <c r="G98" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 면책 범위와 제외 사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간 요약과 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3954,7 +3954,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B99" t="str">
         <v/>
@@ -3969,10 +3969,10 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>옵션에 따른 재고 차이 안내</v>
+        <v>이 기간으로 예약하기</v>
       </c>
       <c r="G99" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 옵션에 따른 재고 차이 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 이 기간으로 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3989,25 +3989,25 @@
         <v>SCN-009</v>
       </c>
       <c r="B100" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C100" t="str">
-        <v/>
+        <v>옵션·부속품 고르기</v>
       </c>
       <c r="D100" t="str">
-        <v/>
+        <v>PD-04</v>
       </c>
       <c r="E100" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F100" t="str">
-        <v>금액 요약과 다음 단계</v>
+        <v>고른 장비와 기간 요약</v>
       </c>
       <c r="G100" t="str">
-        <v>'옵션·부속품 고르기'의 금액 요약과 다음 단계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 고른 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H100" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -4018,28 +4018,28 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B101" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C101" t="str">
-        <v>대여 불가 - 그 날짜 마감</v>
+        <v/>
       </c>
       <c r="D101" t="str">
-        <v>PD-05</v>
+        <v/>
       </c>
       <c r="E101" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F101" t="str">
-        <v>고른 기간과 장비 요약</v>
+        <v>옵션 고르기(크기·색·구성)</v>
       </c>
       <c r="G101" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 고른 기간과 장비 요약이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 옵션 고르기(크기·색·구성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H101" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -4065,13 +4065,13 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>어느 날짜가 왜 안 되는지 짚어 알림</v>
+        <v>함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)</v>
       </c>
       <c r="G102" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 어느 날짜가 왜 안 되는지 짚어 알림이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B103" t="str">
         <v/>
@@ -4097,13 +4097,13 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>가장 가까운 빌릴 수 있는 날짜 3개 추천</v>
+        <v>부속품별 대여료와 보증금</v>
       </c>
       <c r="G103" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 가장 가까운 빌릴 수 있는 날짜 3개 추천이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 부속품별 대여료와 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H103" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -4129,13 +4129,13 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>수량을 줄이면 되는지 알림</v>
+        <v>보험 붙이기 선택(파손 면책 하루 3,000원)</v>
       </c>
       <c r="G104" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 수량을 줄이면 되는지 알림이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 보험 붙이기 선택(파손 면책 하루 3,000원)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H104" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B105" t="str">
         <v/>
@@ -4161,13 +4161,13 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>같은 종류 다른 장비 추천 4개</v>
+        <v>면책 범위와 제외 사항 안내</v>
       </c>
       <c r="G105" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 같은 종류 다른 장비 추천 4개가 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 면책 범위와 제외 사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4178,7 +4178,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B106" t="str">
         <v/>
@@ -4193,13 +4193,13 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>취소 자리 나면 알림 신청</v>
+        <v>옵션에 따른 재고 차이 안내</v>
       </c>
       <c r="G106" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 취소 자리 나면 알림 신청이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 옵션에 따른 재고 차이 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H106" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B107" t="str">
         <v/>
@@ -4225,13 +4225,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>알림은 문자로 온다는 안내</v>
+        <v>금액 요약과 다음 단계</v>
       </c>
       <c r="G107" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 알림은 문자로 온다는 안내가 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기'의 금액 요약과 다음 단계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H107" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4245,22 +4245,22 @@
         <v>SCN-010</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C108" t="str">
-        <v/>
+        <v>대여 불가 - 그 날짜 마감</v>
       </c>
       <c r="D108" t="str">
-        <v/>
+        <v>PD-05</v>
       </c>
       <c r="E108" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F108" t="str">
-        <v>대기 순번 표시</v>
+        <v>고른 기간과 장비 요약</v>
       </c>
       <c r="G108" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 대기 순번 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 고른 기간과 장비 요약이 보이는지 확인한다.</v>
       </c>
       <c r="H108" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -4274,28 +4274,28 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B109" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>세트 패키지</v>
+        <v/>
       </c>
       <c r="D109" t="str">
-        <v>PD-06</v>
+        <v/>
       </c>
       <c r="E109" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F109" t="str">
-        <v>패키지 대표 사진과 이름</v>
+        <v>어느 날짜가 왜 안 되는지 짚어 알림</v>
       </c>
       <c r="G109" t="str">
-        <v>'세트 패키지' 화면에서 패키지 대표 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 어느 날짜가 왜 안 되는지 짚어 알림이 보이는지 확인한다.</v>
       </c>
       <c r="H109" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B110" t="str">
         <v/>
@@ -4321,13 +4321,13 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>낱개로 빌릴 때와 견준 절약 금액</v>
+        <v>가장 가까운 빌릴 수 있는 날짜 3개 추천</v>
       </c>
       <c r="G110" t="str">
-        <v>'세트 패키지'의 낱개로 빌릴 때와 견준 절약 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 가장 가까운 빌릴 수 있는 날짜 3개 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H110" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B111" t="str">
         <v/>
@@ -4353,13 +4353,13 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>들어 있는 장비 목록과 각각의 낱개 대여료</v>
+        <v>수량을 줄이면 되는지 알림</v>
       </c>
       <c r="G111" t="str">
-        <v>'세트 패키지'의 들어 있는 장비 목록과 각각의 낱개 대여료를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 수량을 줄이면 되는지 알림이 보이는지 확인한다.</v>
       </c>
       <c r="H111" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>구성 바꾸기(빼면 얼마 빠지는지)</v>
+        <v>같은 종류 다른 장비 추천 4개</v>
       </c>
       <c r="G112" t="str">
-        <v>'세트 패키지' 화면에서 구성 바꾸기(빼면 얼마 빠지는지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 같은 종류 다른 장비 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H112" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>인원수 추천(4인 가족 기준)</v>
+        <v>취소 자리 나면 알림 신청</v>
       </c>
       <c r="G113" t="str">
-        <v>'세트 패키지' 화면에서 인원수 추천(4인 가족 기준)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 취소 자리 나면 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H113" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B114" t="str">
         <v/>
@@ -4449,13 +4449,13 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>패키지 보증금 합계</v>
+        <v>알림은 문자로 온다는 안내</v>
       </c>
       <c r="G114" t="str">
-        <v>'세트 패키지'의 패키지 보증금 합계가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 알림은 문자로 온다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H114" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I114" t="str">
         <v/>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B115" t="str">
         <v/>
@@ -4481,13 +4481,13 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>이 기간에 패키지 전부가 되는지 확인</v>
+        <v>대기 순번 표시</v>
       </c>
       <c r="G115" t="str">
-        <v>'세트 패키지' 화면에서 이 기간에 패키지 전부가 되는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 대기 순번 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H115" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I115" t="str">
         <v/>
@@ -4501,22 +4501,22 @@
         <v>SCN-011</v>
       </c>
       <c r="B116" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C116" t="str">
-        <v/>
+        <v>세트 패키지</v>
       </c>
       <c r="D116" t="str">
-        <v/>
+        <v>PD-06</v>
       </c>
       <c r="E116" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F116" t="str">
-        <v>하나라도 모자라면 어떤 장비가 모자란지 알림</v>
+        <v>패키지 대표 사진과 이름</v>
       </c>
       <c r="G116" t="str">
-        <v>'세트 패키지' 화면에서 하나라도 모자라면 어떤 장비가 모자란지 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 패키지 대표 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H116" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4545,13 +4545,13 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>패키지 이용 후기</v>
+        <v>낱개로 빌릴 때와 견준 절약 금액</v>
       </c>
       <c r="G117" t="str">
-        <v>'세트 패키지' 화면에서 패키지 이용 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 낱개로 빌릴 때와 견준 절약 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H117" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>담기와 바로 빌리기</v>
+        <v>들어 있는 장비 목록과 각각의 낱개 대여료</v>
       </c>
       <c r="G118" t="str">
-        <v>'세트 패키지' 화면에서 담기와 바로 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 들어 있는 장비 목록과 각각의 낱개 대여료를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H118" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4594,28 +4594,28 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B119" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C119" t="str">
-        <v>대여 장바구니</v>
+        <v/>
       </c>
       <c r="D119" t="str">
-        <v>CT-01</v>
+        <v/>
       </c>
       <c r="E119" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F119" t="str">
-        <v>담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)</v>
+        <v>구성 바꾸기(빼면 얼마 빠지는지)</v>
       </c>
       <c r="G119" t="str">
-        <v>'대여 장바구니'의 담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 구성 바꾸기(빼면 얼마 빠지는지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H119" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B120" t="str">
         <v/>
@@ -4641,10 +4641,10 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>줄마다 수량 바꾸기와 삭제</v>
+        <v>인원수 추천(4인 가족 기준)</v>
       </c>
       <c r="G120" t="str">
-        <v>'대여 장바구니' 화면에서 줄마다 수량 바꾸기와 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 인원수 추천(4인 가족 기준)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H120" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B121" t="str">
         <v/>
@@ -4673,13 +4673,13 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>기간이 다른 줄이 섞여 있으면 갈라서 보여주기</v>
+        <v>패키지 보증금 합계</v>
       </c>
       <c r="G121" t="str">
-        <v>'대여 장바구니' 화면에서 기간이 다른 줄이 섞여 있으면 갈라서 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 패키지 보증금 합계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H121" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4690,7 +4690,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B122" t="str">
         <v/>
@@ -4705,10 +4705,10 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>기간을 한꺼번에 맞추기</v>
+        <v>이 기간에 패키지 전부가 되는지 확인</v>
       </c>
       <c r="G122" t="str">
-        <v>'대여 장바구니' 화면에서 기간을 한꺼번에 맞추기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 이 기간에 패키지 전부가 되는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H122" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B123" t="str">
         <v/>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>담은 뒤 재고가 빠진 줄에 경고 표시</v>
+        <v>하나라도 모자라면 어떤 장비가 모자란지 알림</v>
       </c>
       <c r="G123" t="str">
-        <v>'대여 장바구니'의 담은 뒤 재고가 빠진 줄에 경고 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'세트 패키지' 화면에서 하나라도 모자라면 어떤 장비가 모자란지 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H123" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B124" t="str">
         <v/>
@@ -4769,10 +4769,10 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>쿠폰 고르기와 할인 적용</v>
+        <v>패키지 이용 후기</v>
       </c>
       <c r="G124" t="str">
-        <v>'대여 장바구니' 화면에서 쿠폰 고르기와 할인 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 패키지 이용 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B125" t="str">
         <v/>
@@ -4801,13 +4801,13 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)</v>
+        <v>담기와 바로 빌리기</v>
       </c>
       <c r="G125" t="str">
-        <v>'대여 장바구니'의 금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'세트 패키지' 화면에서 담기와 바로 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H125" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I125" t="str">
         <v/>
@@ -4821,25 +4821,25 @@
         <v>SCN-012</v>
       </c>
       <c r="B126" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C126" t="str">
-        <v/>
+        <v>대여 장바구니</v>
       </c>
       <c r="D126" t="str">
-        <v/>
+        <v>CT-01</v>
       </c>
       <c r="E126" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F126" t="str">
-        <v>보증금은 따로 잡힌다는 안내</v>
+        <v>담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)</v>
       </c>
       <c r="G126" t="str">
-        <v>'대여 장바구니' 화면에서 보증금은 따로 잡힌다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니'의 담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H126" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4865,10 +4865,10 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>계속 둘러보기와 신청하기</v>
+        <v>줄마다 수량 바꾸기와 삭제</v>
       </c>
       <c r="G127" t="str">
-        <v>'대여 장바구니' 화면에서 계속 둘러보기와 신청하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 줄마다 수량 바꾸기와 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H127" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4882,25 +4882,25 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B128" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C128" t="str">
-        <v>기간 한꺼번에 바꾸기</v>
+        <v/>
       </c>
       <c r="D128" t="str">
-        <v>CT-02</v>
+        <v/>
       </c>
       <c r="E128" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F128" t="str">
-        <v>지금 기간과 바꿀 기간 나란히 보기</v>
+        <v>기간이 다른 줄이 섞여 있으면 갈라서 보여주기</v>
       </c>
       <c r="G128" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 지금 기간과 바꿀 기간 나란히 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 기간이 다른 줄이 섞여 있으면 갈라서 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H128" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B129" t="str">
         <v/>
@@ -4929,10 +4929,10 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>새 기간 고르는 달력</v>
+        <v>기간을 한꺼번에 맞추기</v>
       </c>
       <c r="G129" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 새 기간 고르는 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 기간을 한꺼번에 맞추기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H129" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,10 +4961,10 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>담은 장비마다 새 기간에 되는지 하나씩 확인 표시</v>
+        <v>담은 뒤 재고가 빠진 줄에 경고 표시</v>
       </c>
       <c r="G130" t="str">
-        <v>'기간 한꺼번에 바꾸기'의 담은 장비마다 새 기간에 되는지 하나씩 확인 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 장바구니'의 담은 뒤 재고가 빠진 줄에 경고 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H130" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B131" t="str">
         <v/>
@@ -4993,10 +4993,10 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>안 되는 장비는 무엇이 언제 막혔는지</v>
+        <v>쿠폰 고르기와 할인 적용</v>
       </c>
       <c r="G131" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 장비는 무엇이 언제 막혔는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 쿠폰 고르기와 할인 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H131" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5010,7 +5010,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B132" t="str">
         <v/>
@@ -5025,13 +5025,13 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>안 되는 것만 빼고 바꾸기</v>
+        <v>금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)</v>
       </c>
       <c r="G132" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 것만 빼고 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니'의 금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H132" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B133" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>기간이 바뀌면 대여료가 얼마나 달라지는지 견주기</v>
+        <v>보증금은 따로 잡힌다는 안내</v>
       </c>
       <c r="G133" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 기간이 바뀌면 대여료가 얼마나 달라지는지 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 보증금은 따로 잡힌다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H133" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B134" t="str">
         <v/>
@@ -5089,10 +5089,10 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>기간 할인 단계가 바뀌면 알림</v>
+        <v>계속 둘러보기와 신청하기</v>
       </c>
       <c r="G134" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 기간 할인 단계가 바뀌면 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 계속 둘러보기와 신청하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H134" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5109,22 +5109,22 @@
         <v>SCN-013</v>
       </c>
       <c r="B135" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C135" t="str">
-        <v/>
+        <v>기간 한꺼번에 바꾸기</v>
       </c>
       <c r="D135" t="str">
-        <v/>
+        <v>CT-02</v>
       </c>
       <c r="E135" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F135" t="str">
-        <v>되돌리기</v>
+        <v>지금 기간과 바꿀 기간 나란히 보기</v>
       </c>
       <c r="G135" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 되돌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 지금 기간과 바꿀 기간 나란히 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H135" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5138,28 +5138,28 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B136" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C136" t="str">
-        <v>빈 장바구니</v>
+        <v/>
       </c>
       <c r="D136" t="str">
-        <v>CT-03</v>
+        <v/>
       </c>
       <c r="E136" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F136" t="str">
-        <v>담은 것이 없다는 안내</v>
+        <v>새 기간 고르는 달력</v>
       </c>
       <c r="G136" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 담은 것이 없다는 안내가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 새 기간 고르는 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H136" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B137" t="str">
         <v/>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>장비 둘러보기 유도</v>
+        <v>담은 장비마다 새 기간에 되는지 하나씩 확인 표시</v>
       </c>
       <c r="G137" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 장비 둘러보기 유도가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기'의 담은 장비마다 새 기간에 되는지 하나씩 확인 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H137" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B138" t="str">
         <v/>
@@ -5217,13 +5217,13 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>최근 본 장비 4개</v>
+        <v>안 되는 장비는 무엇이 언제 막혔는지</v>
       </c>
       <c r="G138" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 최근 본 장비 4개가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 장비는 무엇이 언제 막혔는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H138" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,13 +5249,13 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>찜한 장비 바로가기</v>
+        <v>안 되는 것만 빼고 바꾸기</v>
       </c>
       <c r="G139" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 찜한 장비 바로가기가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 것만 빼고 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H139" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I139" t="str">
         <v/>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,13 +5281,13 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>이번 주말 남은 장비 추천</v>
+        <v>기간이 바뀌면 대여료가 얼마나 달라지는지 견주기</v>
       </c>
       <c r="G140" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 이번 주말 남은 장비 추천이 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 기간이 바뀌면 대여료가 얼마나 달라지는지 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H140" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I140" t="str">
         <v/>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B141" t="str">
         <v/>
@@ -5313,13 +5313,13 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>처음이신가요 3단계 안내 링크</v>
+        <v>기간 할인 단계가 바뀌면 알림</v>
       </c>
       <c r="G141" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 처음이신가요 3단계 안내 링크가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 기간 할인 단계가 바뀌면 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H141" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I141" t="str">
         <v/>
@@ -5330,25 +5330,25 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>SCN-015</v>
+        <v>SCN-013</v>
       </c>
       <c r="B142" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C142" t="str">
-        <v>대여 신청서</v>
+        <v/>
       </c>
       <c r="D142" t="str">
-        <v>BK-01</v>
+        <v/>
       </c>
       <c r="E142" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F142" t="str">
-        <v>빌릴 장비와 기간 요약</v>
+        <v>되돌리기</v>
       </c>
       <c r="G142" t="str">
-        <v>'대여 신청서' 화면에서 빌릴 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 되돌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H142" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5362,28 +5362,28 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B143" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C143" t="str">
-        <v/>
+        <v>빈 장바구니</v>
       </c>
       <c r="D143" t="str">
-        <v/>
+        <v>CT-03</v>
       </c>
       <c r="E143" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F143" t="str">
-        <v>신청자 정보(이름·연락처·이메일)</v>
+        <v>담은 것이 없다는 안내</v>
       </c>
       <c r="G143" t="str">
-        <v>'대여 신청서'의 신청자 정보(이름·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 담은 것이 없다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H143" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B144" t="str">
         <v/>
@@ -5409,13 +5409,13 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
+        <v>장비 둘러보기 유도</v>
       </c>
       <c r="G144" t="str">
-        <v>'대여 신청서' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 장비 둘러보기 유도가 보이는지 확인한다.</v>
       </c>
       <c r="H144" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B145" t="str">
         <v/>
@@ -5441,13 +5441,13 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>방문 수령 시 방문 예정 시각 고르기</v>
+        <v>최근 본 장비 4개</v>
       </c>
       <c r="G145" t="str">
-        <v>'대여 신청서' 화면에서 방문 수령 시 방문 예정 시각 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 최근 본 장비 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H145" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,13 +5473,13 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>택배 시 받는 주소와 회수 주소</v>
+        <v>찜한 장비 바로가기</v>
       </c>
       <c r="G146" t="str">
-        <v>'대여 신청서' 화면에서 택배 시 받는 주소와 회수 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 찜한 장비 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H146" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,13 +5505,13 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>반납 예정일과 반납 방법 안내</v>
+        <v>이번 주말 남은 장비 추천</v>
       </c>
       <c r="G147" t="str">
-        <v>'대여 신청서' 화면에서 반납 예정일과 반납 방법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 이번 주말 남은 장비 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H147" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>신분 확인 안내(고가 장비는 신분증 확인)</v>
+        <v>처음이신가요 3단계 안내 링크</v>
       </c>
       <c r="G148" t="str">
-        <v>'대여 신청서' 화면에서 신분 확인 안내(고가 장비는 신분증 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 처음이신가요 3단계 안내 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H148" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5557,22 +5557,22 @@
         <v>SCN-015</v>
       </c>
       <c r="B149" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C149" t="str">
-        <v/>
+        <v>대여 신청서</v>
       </c>
       <c r="D149" t="str">
-        <v/>
+        <v>BK-01</v>
       </c>
       <c r="E149" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F149" t="str">
-        <v>요청사항</v>
+        <v>빌릴 장비와 기간 요약</v>
       </c>
       <c r="G149" t="str">
-        <v>'대여 신청서' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 빌릴 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H149" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5601,13 +5601,13 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>필수 동의(대여 약관·파손 배상 기준·개인정보)</v>
+        <v>신청자 정보(이름·연락처·이메일)</v>
       </c>
       <c r="G150" t="str">
-        <v>'대여 신청서' 화면에서 필수 동의(대여 약관·파손 배상 기준·개인정보)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서'의 신청자 정보(이름·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H150" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5633,10 +5633,10 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>보증금 안내</v>
+        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
       </c>
       <c r="G151" t="str">
-        <v>'대여 신청서' 화면에서 보증금 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H151" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>금액 요약과 결제로 가기</v>
+        <v>방문 수령 시 방문 예정 시각 고르기</v>
       </c>
       <c r="G152" t="str">
-        <v>'대여 신청서'에서 금액 요약과 결제로 가기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 방문 수령 시 방문 예정 시각 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H152" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5682,28 +5682,28 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B153" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C153" t="str">
-        <v>보증금·결제</v>
+        <v/>
       </c>
       <c r="D153" t="str">
-        <v>BK-02</v>
+        <v/>
       </c>
       <c r="E153" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F153" t="str">
-        <v>결제 금액과 보증금을 갈라서 보여주기</v>
+        <v>택배 시 받는 주소와 회수 주소</v>
       </c>
       <c r="G153" t="str">
-        <v>'보증금·결제'에서 결제 금액과 보증금을 갈라서 보여주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 택배 시 받는 주소와 회수 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H153" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -5729,13 +5729,13 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>결제 수단 고르기(카드·간편결제·계좌이체)</v>
+        <v>반납 예정일과 반납 방법 안내</v>
       </c>
       <c r="G154" t="str">
-        <v>'보증금·결제'에서 결제 수단 고르기(카드·간편결제·계좌이체)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 반납 예정일과 반납 방법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H154" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5746,7 +5746,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B155" t="str">
         <v/>
@@ -5761,10 +5761,10 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)</v>
+        <v>신분 확인 안내(고가 장비는 신분증 확인)</v>
       </c>
       <c r="G155" t="str">
-        <v>'보증금·결제' 화면에서 보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 신분 확인 안내(고가 장비는 신분증 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H155" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B156" t="str">
         <v/>
@@ -5793,13 +5793,13 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>카드 보류가 무엇인지 설명</v>
+        <v>요청사항</v>
       </c>
       <c r="G156" t="str">
-        <v>'보증금·결제'의 카드 보류가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H156" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B157" t="str">
         <v/>
@@ -5825,10 +5825,10 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>보증금 면제 조건 안내</v>
+        <v>필수 동의(대여 약관·파손 배상 기준·개인정보)</v>
       </c>
       <c r="G157" t="str">
-        <v>'보증금·결제' 화면에서 보증금 면제 조건 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 필수 동의(대여 약관·파손 배상 기준·개인정보)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H157" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B158" t="str">
         <v/>
@@ -5857,10 +5857,10 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>언제 얼마가 빠지는지 시각 순서로</v>
+        <v>보증금 안내</v>
       </c>
       <c r="G158" t="str">
-        <v>'보증금·결제' 화면에서 언제 얼마가 빠지는지 시각 순서로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 보증금 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H158" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5874,7 +5874,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B159" t="str">
         <v/>
@@ -5889,13 +5889,13 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>현금영수증</v>
+        <v>금액 요약과 결제로 가기</v>
       </c>
       <c r="G159" t="str">
-        <v>'보증금·결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서'에서 금액 요약과 결제로 가기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H159" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5909,25 +5909,25 @@
         <v>SCN-016</v>
       </c>
       <c r="B160" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C160" t="str">
-        <v/>
+        <v>보증금·결제</v>
       </c>
       <c r="D160" t="str">
-        <v/>
+        <v>BK-02</v>
       </c>
       <c r="E160" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F160" t="str">
-        <v>세금계산서</v>
+        <v>결제 금액과 보증금을 갈라서 보여주기</v>
       </c>
       <c r="G160" t="str">
-        <v>'보증금·결제' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 금액과 보증금을 갈라서 보여주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H160" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>최종 확인 체크</v>
+        <v>결제 수단 고르기(카드·간편결제·계좌이체)</v>
       </c>
       <c r="G161" t="str">
-        <v>'보증금·결제' 화면에서 최종 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 수단 고르기(카드·간편결제·계좌이체)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H161" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5985,13 +5985,13 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>결제 실행</v>
+        <v>보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)</v>
       </c>
       <c r="G162" t="str">
-        <v>'보증금·결제'에서 결제 실행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'보증금·결제' 화면에서 보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H162" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I162" t="str">
         <v/>
@@ -6002,28 +6002,28 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B163" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C163" t="str">
-        <v>대여 확정 완료</v>
+        <v/>
       </c>
       <c r="D163" t="str">
-        <v>BK-03</v>
+        <v/>
       </c>
       <c r="E163" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F163" t="str">
-        <v>확정 안내와 대여번호</v>
+        <v>카드 보류가 무엇인지 설명</v>
       </c>
       <c r="G163" t="str">
-        <v>'대여 확정 완료' 화면에서 확정 안내와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'의 카드 보류가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H163" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -6049,10 +6049,10 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>빌린 장비와 기간 요약</v>
+        <v>보증금 면제 조건 안내</v>
       </c>
       <c r="G164" t="str">
-        <v>'대여 확정 완료' 화면에서 빌린 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 보증금 면제 조건 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H164" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,10 +6081,10 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>수령 방법별 다음 할 일 안내</v>
+        <v>언제 얼마가 빠지는지 시각 순서로</v>
       </c>
       <c r="G165" t="str">
-        <v>'대여 확정 완료' 화면에서 수령 방법별 다음 할 일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 언제 얼마가 빠지는지 시각 순서로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H165" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B166" t="str">
         <v/>
@@ -6113,10 +6113,10 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>매장 방문이면 주소</v>
+        <v>현금영수증</v>
       </c>
       <c r="G166" t="str">
-        <v>'대여 확정 완료' 화면에서 매장 방문이면 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H166" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6130,7 +6130,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B167" t="str">
         <v/>
@@ -6145,10 +6145,10 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>시각</v>
+        <v>세금계산서</v>
       </c>
       <c r="G167" t="str">
-        <v>'대여 확정 완료' 화면에서 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H167" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B168" t="str">
         <v/>
@@ -6177,10 +6177,10 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>QR</v>
+        <v>최종 확인 체크</v>
       </c>
       <c r="G168" t="str">
-        <v>'대여 확정 완료' 화면에서 QR이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 최종 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H168" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B169" t="str">
         <v/>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>택배면 발송 예정일과 송장 안내</v>
+        <v>결제 실행</v>
       </c>
       <c r="G169" t="str">
-        <v>'대여 확정 완료' 화면에서 택배면 발송 예정일과 송장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 실행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6229,22 +6229,22 @@
         <v>SCN-017</v>
       </c>
       <c r="B170" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C170" t="str">
-        <v/>
+        <v>대여 확정 완료</v>
       </c>
       <c r="D170" t="str">
-        <v/>
+        <v>BK-03</v>
       </c>
       <c r="E170" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F170" t="str">
-        <v>반납 예정일 강조와 캘린더에 넣기</v>
+        <v>확정 안내와 대여번호</v>
       </c>
       <c r="G170" t="str">
-        <v>'대여 확정 완료' 화면에서 반납 예정일 강조와 캘린더에 넣기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 확정 안내와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6273,13 +6273,13 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>결제 금액과 보증금 상태</v>
+        <v>빌린 장비와 기간 요약</v>
       </c>
       <c r="G171" t="str">
-        <v>'대여 확정 완료'에서 결제 금액과 보증금 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 확정 완료' 화면에서 빌린 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H171" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I171" t="str">
         <v/>
@@ -6305,10 +6305,10 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>수령 전 준비물(신분증)</v>
+        <v>수령 방법별 다음 할 일 안내</v>
       </c>
       <c r="G172" t="str">
-        <v>'대여 확정 완료' 화면에서 수령 전 준비물(신분증)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 수령 방법별 다음 할 일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H172" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6337,10 +6337,10 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>대여 내역으로 가기</v>
+        <v>매장 방문이면 주소</v>
       </c>
       <c r="G173" t="str">
-        <v>'대여 확정 완료' 화면에서 대여 내역으로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 매장 방문이면 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H173" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6369,10 +6369,10 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>카톡 알림 받기 신청</v>
+        <v>시각</v>
       </c>
       <c r="G174" t="str">
-        <v>'대여 확정 완료' 화면에서 카톡 알림 받기 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6386,28 +6386,28 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B175" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C175" t="str">
-        <v>결제 실패</v>
+        <v/>
       </c>
       <c r="D175" t="str">
-        <v>BK-04</v>
+        <v/>
       </c>
       <c r="E175" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F175" t="str">
-        <v>실패 안내와 무엇 때문인지</v>
+        <v>QR</v>
       </c>
       <c r="G175" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 안내와 무엇 때문인지가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 QR이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6418,7 +6418,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B176" t="str">
         <v/>
@@ -6433,13 +6433,13 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)</v>
+        <v>택배면 발송 예정일과 송장 안내</v>
       </c>
       <c r="G176" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)이 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 택배면 발송 예정일과 송장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I176" t="str">
         <v/>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B177" t="str">
         <v/>
@@ -6465,13 +6465,13 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>보증금 때문에 한도가 모자란 경우 따로 안내</v>
+        <v>반납 예정일 강조와 캘린더에 넣기</v>
       </c>
       <c r="G177" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 때문에 한도가 모자란 경우 따로 안내가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 반납 예정일 강조와 캘린더에 넣기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I177" t="str">
         <v/>
@@ -6482,7 +6482,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B178" t="str">
         <v/>
@@ -6497,13 +6497,13 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>장비는 아직 잡혀 있다는 것과 언제까지인지</v>
+        <v>결제 금액과 보증금 상태</v>
       </c>
       <c r="G178" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 장비는 아직 잡혀 있다는 것과 언제까지인지가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료'에서 결제 금액과 보증금 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H178" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6514,7 +6514,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B179" t="str">
         <v/>
@@ -6529,13 +6529,13 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>다시 시도하기</v>
+        <v>수령 전 준비물(신분증)</v>
       </c>
       <c r="G179" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 수령 전 준비물(신분증)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I179" t="str">
         <v/>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B180" t="str">
         <v/>
@@ -6561,13 +6561,13 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>다른 결제 수단으로</v>
+        <v>대여 내역으로 가기</v>
       </c>
       <c r="G180" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단으로가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 대여 내역으로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I180" t="str">
         <v/>
@@ -6578,7 +6578,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B181" t="str">
         <v/>
@@ -6593,13 +6593,13 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>보증금 방식 바꾸기</v>
+        <v>카톡 알림 받기 신청</v>
       </c>
       <c r="G181" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 방식 바꾸기가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 카톡 알림 받기 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H181" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I181" t="str">
         <v/>
@@ -6613,22 +6613,22 @@
         <v>SCN-018</v>
       </c>
       <c r="B182" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C182" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D182" t="str">
-        <v/>
+        <v>BK-04</v>
       </c>
       <c r="E182" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F182" t="str">
-        <v>고객센터 안내</v>
+        <v>실패 안내와 무엇 때문인지</v>
       </c>
       <c r="G182" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 안내와 무엇 때문인지가 보이는지 확인한다.</v>
       </c>
       <c r="H182" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6642,28 +6642,28 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B183" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C183" t="str">
-        <v>대여 계약 동의·서명</v>
+        <v/>
       </c>
       <c r="D183" t="str">
-        <v>BK-05</v>
+        <v/>
       </c>
       <c r="E183" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F183" t="str">
-        <v>대여 계약 요약(빌리는 것·기간·금액·보증금)</v>
+        <v>흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)</v>
       </c>
       <c r="G183" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 대여 계약 요약(빌리는 것·기간·금액·보증금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)이 보이는지 확인한다.</v>
       </c>
       <c r="H183" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -6689,13 +6689,13 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>조항별 펼쳐보기</v>
+        <v>보증금 때문에 한도가 모자란 경우 따로 안내</v>
       </c>
       <c r="G184" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 조항별 펼쳐보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 때문에 한도가 모자란 경우 따로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H184" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,13 +6721,13 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>파손</v>
+        <v>장비는 아직 잡혀 있다는 것과 언제까지인지</v>
       </c>
       <c r="G185" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 장비는 아직 잡혀 있다는 것과 언제까지인지가 보이는지 확인한다.</v>
       </c>
       <c r="H185" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B186" t="str">
         <v/>
@@ -6753,13 +6753,13 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>분실 시 배상 기준 요약표</v>
+        <v>다시 시도하기</v>
       </c>
       <c r="G186" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 분실 시 배상 기준 요약표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기가 보이는지 확인한다.</v>
       </c>
       <c r="H186" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B187" t="str">
         <v/>
@@ -6785,13 +6785,13 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>연체료 계산 방식</v>
+        <v>다른 결제 수단으로</v>
       </c>
       <c r="G187" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 연체료 계산 방식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단으로가 보이는지 확인한다.</v>
       </c>
       <c r="H187" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6802,7 +6802,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B188" t="str">
         <v/>
@@ -6817,13 +6817,13 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>반납 상태 기준(세척·건조)</v>
+        <v>보증금 방식 바꾸기</v>
       </c>
       <c r="G188" t="str">
-        <v>'대여 계약 동의·서명'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 방식 바꾸기가 보이는지 확인한다.</v>
       </c>
       <c r="H188" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I188" t="str">
         <v/>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B189" t="str">
         <v/>
@@ -6849,13 +6849,13 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>개인정보 이용 범위</v>
+        <v>고객센터 안내</v>
       </c>
       <c r="G189" t="str">
-        <v>'대여 계약 동의·서명'의 개인정보 이용 범위가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H189" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I189" t="str">
         <v/>
@@ -6869,22 +6869,22 @@
         <v>SCN-019</v>
       </c>
       <c r="B190" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C190" t="str">
-        <v/>
+        <v>대여 계약 동의·서명</v>
       </c>
       <c r="D190" t="str">
-        <v/>
+        <v>BK-05</v>
       </c>
       <c r="E190" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F190" t="str">
-        <v>필수와 선택 동의 갈라 두기</v>
+        <v>대여 계약 요약(빌리는 것·기간·금액·보증금)</v>
       </c>
       <c r="G190" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 필수와 선택 동의 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 대여 계약 요약(빌리는 것·기간·금액·보증금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H190" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6913,10 +6913,10 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>전자 서명 칸</v>
+        <v>조항별 펼쳐보기</v>
       </c>
       <c r="G191" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 전자 서명 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 조항별 펼쳐보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H191" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6945,10 +6945,10 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>계약서 사본 받기(이메일·다운로드)</v>
+        <v>파손</v>
       </c>
       <c r="G192" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 계약서 사본 받기(이메일·다운로드)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H192" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6977,10 +6977,10 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>동의 없이는 수령 불가 안내</v>
+        <v>분실 시 배상 기준 요약표</v>
       </c>
       <c r="G193" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 동의 없이는 수령 불가 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 분실 시 배상 기준 요약표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H193" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6994,25 +6994,25 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B194" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C194" t="str">
-        <v>대여 기간 연장</v>
+        <v/>
       </c>
       <c r="D194" t="str">
-        <v>BK-06</v>
+        <v/>
       </c>
       <c r="E194" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F194" t="str">
-        <v>지금 빌린 장비와 반납 예정일</v>
+        <v>연체료 계산 방식</v>
       </c>
       <c r="G194" t="str">
-        <v>'대여 기간 연장' 화면에서 지금 빌린 장비와 반납 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 연체료 계산 방식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H194" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,13 +7041,13 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>얼마나 더 쓸지 고르기</v>
+        <v>반납 상태 기준(세척·건조)</v>
       </c>
       <c r="G195" t="str">
-        <v>'대여 기간 연장' 화면에서 얼마나 더 쓸지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H195" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7058,7 +7058,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B196" t="str">
         <v/>
@@ -7073,13 +7073,13 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>연장할 기간에 그 장비가 비어 있는지 확인</v>
+        <v>개인정보 이용 범위</v>
       </c>
       <c r="G196" t="str">
-        <v>'대여 기간 연장' 화면에서 연장할 기간에 그 장비가 비어 있는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명'의 개인정보 이용 범위가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H196" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -7090,7 +7090,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B197" t="str">
         <v/>
@@ -7105,10 +7105,10 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>다음 예약이 있으면 언제까지만 연장되는지</v>
+        <v>필수와 선택 동의 갈라 두기</v>
       </c>
       <c r="G197" t="str">
-        <v>'대여 기간 연장' 화면에서 다음 예약이 있으면 언제까지만 연장되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 필수와 선택 동의 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B198" t="str">
         <v/>
@@ -7137,10 +7137,10 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>추가 대여료 계산과 기간 할인 다시 적용</v>
+        <v>전자 서명 칸</v>
       </c>
       <c r="G198" t="str">
-        <v>'대여 기간 연장' 화면에서 추가 대여료 계산과 기간 할인 다시 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 전자 서명 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H198" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7154,7 +7154,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B199" t="str">
         <v/>
@@ -7169,10 +7169,10 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>보증금은 그대로 유지된다는 안내</v>
+        <v>계약서 사본 받기(이메일·다운로드)</v>
       </c>
       <c r="G199" t="str">
-        <v>'대여 기간 연장' 화면에서 보증금은 그대로 유지된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 계약서 사본 받기(이메일·다운로드)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H199" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7186,7 +7186,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B200" t="str">
         <v/>
@@ -7201,10 +7201,10 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>연장은 반납일 전에만 된다는 안내</v>
+        <v>동의 없이는 수령 불가 안내</v>
       </c>
       <c r="G200" t="str">
-        <v>'대여 기간 연장' 화면에서 연장은 반납일 전에만 된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 동의 없이는 수령 불가 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H200" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7221,25 +7221,25 @@
         <v>SCN-020</v>
       </c>
       <c r="B201" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C201" t="str">
-        <v/>
+        <v>대여 기간 연장</v>
       </c>
       <c r="D201" t="str">
-        <v/>
+        <v>BK-06</v>
       </c>
       <c r="E201" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F201" t="str">
-        <v>연체 중이면 연장 대신 연체 정산으로 안내</v>
+        <v>지금 빌린 장비와 반납 예정일</v>
       </c>
       <c r="G201" t="str">
-        <v>'대여 기간 연장'에서 연체 중이면 연장 대신 연체 정산으로 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 기간 연장' 화면에서 지금 빌린 장비와 반납 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H201" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7265,13 +7265,13 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>연장 결제</v>
+        <v>얼마나 더 쓸지 고르기</v>
       </c>
       <c r="G202" t="str">
-        <v>'대여 기간 연장'에서 연장 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 기간 연장' 화면에서 얼마나 더 쓸지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H202" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7282,25 +7282,25 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B203" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C203" t="str">
-        <v>수령 확인</v>
+        <v/>
       </c>
       <c r="D203" t="str">
-        <v>RT-01</v>
+        <v/>
       </c>
       <c r="E203" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F203" t="str">
-        <v>수령 QR 코드와 대여번호</v>
+        <v>연장할 기간에 그 장비가 비어 있는지 확인</v>
       </c>
       <c r="G203" t="str">
-        <v>'수령 확인' 화면에서 수령 QR 코드와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 연장할 기간에 그 장비가 비어 있는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -7329,13 +7329,13 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>받을 장비와 구성품 목록</v>
+        <v>다음 예약이 있으면 언제까지만 연장되는지</v>
       </c>
       <c r="G204" t="str">
-        <v>'수령 확인'의 받을 장비와 구성품 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 다음 예약이 있으면 언제까지만 연장되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I204" t="str">
         <v/>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B205" t="str">
         <v/>
@@ -7361,10 +7361,10 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>구성품 하나씩 체크하며 확인</v>
+        <v>추가 대여료 계산과 기간 할인 다시 적용</v>
       </c>
       <c r="G205" t="str">
-        <v>'수령 확인' 화면에서 구성품 하나씩 체크하며 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 추가 대여료 계산과 기간 할인 다시 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H205" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,13 +7393,13 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>받을 때 상태 사진 찍어 올리기</v>
+        <v>보증금은 그대로 유지된다는 안내</v>
       </c>
       <c r="G206" t="str">
-        <v>'수령 확인'의 받을 때 상태 사진 찍어 올리기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 기간 연장' 화면에서 보증금은 그대로 유지된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I206" t="str">
         <v/>
@@ -7410,7 +7410,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B207" t="str">
         <v/>
@@ -7425,13 +7425,13 @@
         <v/>
       </c>
       <c r="F207" t="str">
-        <v>이미 있던 흠집 표시하기</v>
+        <v>연장은 반납일 전에만 된다는 안내</v>
       </c>
       <c r="G207" t="str">
-        <v>'수령 확인'의 이미 있던 흠집 표시하기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 기간 연장' 화면에서 연장은 반납일 전에만 된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H207" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I207" t="str">
         <v/>
@@ -7442,7 +7442,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B208" t="str">
         <v/>
@@ -7457,13 +7457,13 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>신분증 확인 안내</v>
+        <v>연체 중이면 연장 대신 연체 정산으로 안내</v>
       </c>
       <c r="G208" t="str">
-        <v>'수령 확인' 화면에서 신분증 확인 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장'에서 연체 중이면 연장 대신 연체 정산으로 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H208" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7474,7 +7474,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B209" t="str">
         <v/>
@@ -7489,13 +7489,13 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>반납 예정일 다시 알림</v>
+        <v>연장 결제</v>
       </c>
       <c r="G209" t="str">
-        <v>'수령 확인' 화면에서 반납 예정일 다시 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장'에서 연장 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H209" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I209" t="str">
         <v/>
@@ -7509,25 +7509,25 @@
         <v>SCN-021</v>
       </c>
       <c r="B210" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C210" t="str">
-        <v/>
+        <v>수령 확인</v>
       </c>
       <c r="D210" t="str">
-        <v/>
+        <v>RT-01</v>
       </c>
       <c r="E210" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F210" t="str">
-        <v>사용법 간단 안내 링크</v>
+        <v>수령 QR 코드와 대여번호</v>
       </c>
       <c r="G210" t="str">
-        <v>'수령 확인'에서 사용법 간단 안내 링크를 눌러 본다.</v>
+        <v>'수령 확인' 화면에서 수령 QR 코드와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H210" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I210" t="str">
         <v/>
@@ -7553,13 +7553,13 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>수령 확인 완료</v>
+        <v>받을 장비와 구성품 목록</v>
       </c>
       <c r="G211" t="str">
-        <v>'수령 확인' 화면에서 수령 확인 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'수령 확인'의 받을 장비와 구성품 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H211" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -7585,10 +7585,10 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>확인해야 보증금 규정이 시작된다는 안내</v>
+        <v>구성품 하나씩 체크하며 확인</v>
       </c>
       <c r="G212" t="str">
-        <v>'수령 확인' 화면에서 확인해야 보증금 규정이 시작된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'수령 확인' 화면에서 구성품 하나씩 체크하며 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7602,28 +7602,28 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B213" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C213" t="str">
-        <v>이용 중</v>
+        <v/>
       </c>
       <c r="D213" t="str">
-        <v>RT-02</v>
+        <v/>
       </c>
       <c r="E213" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F213" t="str">
-        <v>빌린 장비와 남은 시간 카운트</v>
+        <v>받을 때 상태 사진 찍어 올리기</v>
       </c>
       <c r="G213" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 빌린 장비와 남은 시간 카운트가 보이는지 확인한다.</v>
+        <v>'수령 확인'의 받을 때 상태 사진 찍어 올리기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H213" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B214" t="str">
         <v/>
@@ -7649,13 +7649,13 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>반납 예정일까지 남은 시간을 크게</v>
+        <v>이미 있던 흠집 표시하기</v>
       </c>
       <c r="G214" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 예정일까지 남은 시간을 크게가 보이는지 확인한다.</v>
+        <v>'수령 확인'의 이미 있던 흠집 표시하기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H214" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B215" t="str">
         <v/>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>반납 방법 미리 안내(매장·택배)</v>
+        <v>신분증 확인 안내</v>
       </c>
       <c r="G215" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 방법 미리 안내(매장·택배)가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 신분증 확인 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7698,7 +7698,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B216" t="str">
         <v/>
@@ -7713,13 +7713,13 @@
         <v/>
       </c>
       <c r="F216" t="str">
-        <v>반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)</v>
+        <v>반납 예정일 다시 알림</v>
       </c>
       <c r="G216" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)이 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 반납 예정일 다시 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H216" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I216" t="str">
         <v/>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B217" t="str">
         <v/>
@@ -7745,13 +7745,13 @@
         <v/>
       </c>
       <c r="F217" t="str">
-        <v>사용 중 문제 신고</v>
+        <v>사용법 간단 안내 링크</v>
       </c>
       <c r="G217" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용 중 문제 신고가 보이는지 확인한다.</v>
+        <v>'수령 확인'에서 사용법 간단 안내 링크를 눌러 본다.</v>
       </c>
       <c r="H217" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -7762,7 +7762,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B218" t="str">
         <v/>
@@ -7777,13 +7777,13 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>기간 연장하기</v>
+        <v>수령 확인 완료</v>
       </c>
       <c r="G218" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 기간 연장하기가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 수령 확인 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I218" t="str">
         <v/>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B219" t="str">
         <v/>
@@ -7809,13 +7809,13 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>파손 미리 알리기</v>
+        <v>확인해야 보증금 규정이 시작된다는 안내</v>
       </c>
       <c r="G219" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 파손 미리 알리기가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 확인해야 보증금 규정이 시작된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H219" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -7829,22 +7829,22 @@
         <v>SCN-022</v>
       </c>
       <c r="B220" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C220" t="str">
-        <v/>
+        <v>이용 중</v>
       </c>
       <c r="D220" t="str">
-        <v/>
+        <v>RT-02</v>
       </c>
       <c r="E220" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F220" t="str">
-        <v>사용법과 주의사항 다시 보기</v>
+        <v>빌린 장비와 남은 시간 카운트</v>
       </c>
       <c r="G220" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용법과 주의사항 다시 보기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 빌린 장비와 남은 시간 카운트가 보이는지 확인한다.</v>
       </c>
       <c r="H220" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -7873,10 +7873,10 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>반납 알림 설정</v>
+        <v>반납 예정일까지 남은 시간을 크게</v>
       </c>
       <c r="G221" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 알림 설정이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 예정일까지 남은 시간을 크게가 보이는지 확인한다.</v>
       </c>
       <c r="H221" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -7890,28 +7890,28 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B222" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C222" t="str">
-        <v>반납 안내</v>
+        <v/>
       </c>
       <c r="D222" t="str">
-        <v>RT-03</v>
+        <v/>
       </c>
       <c r="E222" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F222" t="str">
-        <v>반납 기한과 남은 시간</v>
+        <v>반납 방법 미리 안내(매장·택배)</v>
       </c>
       <c r="G222" t="str">
-        <v>'반납 안내'의 반납 기한과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 방법 미리 안내(매장·택배)가 보이는지 확인한다.</v>
       </c>
       <c r="H222" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B223" t="str">
         <v/>
@@ -7937,13 +7937,13 @@
         <v/>
       </c>
       <c r="F223" t="str">
-        <v>반납 방법 고르기(매장 방문·택배 회수)</v>
+        <v>반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)</v>
       </c>
       <c r="G223" t="str">
-        <v>'반납 안내' 화면에서 반납 방법 고르기(매장 방문·택배 회수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)이 보이는지 확인한다.</v>
       </c>
       <c r="H223" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B224" t="str">
         <v/>
@@ -7969,13 +7969,13 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>매장 반납 시 주소</v>
+        <v>사용 중 문제 신고</v>
       </c>
       <c r="G224" t="str">
-        <v>'반납 안내' 화면에서 매장 반납 시 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용 중 문제 신고가 보이는지 확인한다.</v>
       </c>
       <c r="H224" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B225" t="str">
         <v/>
@@ -8001,13 +8001,13 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>운영시간</v>
+        <v>기간 연장하기</v>
       </c>
       <c r="G225" t="str">
-        <v>'반납 안내' 화면에서 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 기간 연장하기가 보이는지 확인한다.</v>
       </c>
       <c r="H225" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B226" t="str">
         <v/>
@@ -8033,13 +8033,13 @@
         <v/>
       </c>
       <c r="F226" t="str">
-        <v>지도</v>
+        <v>파손 미리 알리기</v>
       </c>
       <c r="G226" t="str">
-        <v>'반납 안내' 화면에서 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 파손 미리 알리기가 보이는지 확인한다.</v>
       </c>
       <c r="H226" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I226" t="str">
         <v/>
@@ -8050,7 +8050,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B227" t="str">
         <v/>
@@ -8065,13 +8065,13 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>주차 안내</v>
+        <v>사용법과 주의사항 다시 보기</v>
       </c>
       <c r="G227" t="str">
-        <v>'반납 안내' 화면에서 주차 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용법과 주의사항 다시 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H227" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I227" t="str">
         <v/>
@@ -8082,7 +8082,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B228" t="str">
         <v/>
@@ -8097,13 +8097,13 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>택배 회수 신청과 방문 예정 시각</v>
+        <v>반납 알림 설정</v>
       </c>
       <c r="G228" t="str">
-        <v>'반납 안내' 화면에서 택배 회수 신청과 방문 예정 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 알림 설정이 보이는지 확인한다.</v>
       </c>
       <c r="H228" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I228" t="str">
         <v/>
@@ -8117,25 +8117,25 @@
         <v>SCN-023</v>
       </c>
       <c r="B229" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C229" t="str">
-        <v/>
+        <v>반납 안내</v>
       </c>
       <c r="D229" t="str">
-        <v/>
+        <v>RT-03</v>
       </c>
       <c r="E229" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F229" t="str">
-        <v>반납 전 준비 체크리스트</v>
+        <v>반납 기한과 남은 시간</v>
       </c>
       <c r="G229" t="str">
-        <v>'반납 안내'의 반납 전 준비 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'반납 안내'의 반납 기한과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H229" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8161,13 +8161,13 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>이 상태로 반납하면 안 되는 예시 사진</v>
+        <v>반납 방법 고르기(매장 방문·택배 회수)</v>
       </c>
       <c r="G230" t="str">
-        <v>'반납 안내'의 이 상태로 반납하면 안 되는 예시 사진이 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 안내' 화면에서 반납 방법 고르기(매장 방문·택배 회수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H230" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8193,10 +8193,10 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>늦으면 얼마가 붙는지 표</v>
+        <v>매장 반납 시 주소</v>
       </c>
       <c r="G231" t="str">
-        <v>'반납 안내' 화면에서 늦으면 얼마가 붙는지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 매장 반납 시 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H231" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8225,10 +8225,10 @@
         <v/>
       </c>
       <c r="F232" t="str">
-        <v>구성품 빠지면 얼마인지 표</v>
+        <v>운영시간</v>
       </c>
       <c r="G232" t="str">
-        <v>'반납 안내' 화면에서 구성품 빠지면 얼마인지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H232" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8257,10 +8257,10 @@
         <v/>
       </c>
       <c r="F233" t="str">
-        <v>반납 접수로 가기</v>
+        <v>지도</v>
       </c>
       <c r="G233" t="str">
-        <v>'반납 안내' 화면에서 반납 접수로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H233" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8274,25 +8274,25 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B234" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C234" t="str">
-        <v>반납 접수</v>
+        <v/>
       </c>
       <c r="D234" t="str">
-        <v>RT-04</v>
+        <v/>
       </c>
       <c r="E234" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F234" t="str">
-        <v>반납할 장비와 기간 요약</v>
+        <v>주차 안내</v>
       </c>
       <c r="G234" t="str">
-        <v>'반납 접수' 화면에서 반납할 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 주차 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H234" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B235" t="str">
         <v/>
@@ -8321,10 +8321,10 @@
         <v/>
       </c>
       <c r="F235" t="str">
-        <v>구성품 다 챙겼는지 하나씩 체크</v>
+        <v>택배 회수 신청과 방문 예정 시각</v>
       </c>
       <c r="G235" t="str">
-        <v>'반납 접수' 화면에서 구성품 다 챙겼는지 하나씩 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 택배 회수 신청과 방문 예정 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H235" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8338,7 +8338,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B236" t="str">
         <v/>
@@ -8353,13 +8353,13 @@
         <v/>
       </c>
       <c r="F236" t="str">
-        <v>반납 상태 사진 올리기</v>
+        <v>반납 전 준비 체크리스트</v>
       </c>
       <c r="G236" t="str">
-        <v>'반납 접수'의 반납 상태 사진 올리기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 안내'의 반납 전 준비 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H236" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8370,7 +8370,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B237" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>수령 때 사진과 나란히 견주기</v>
+        <v>이 상태로 반납하면 안 되는 예시 사진</v>
       </c>
       <c r="G237" t="str">
-        <v>'반납 접수' 화면에서 수령 때 사진과 나란히 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내'의 이 상태로 반납하면 안 되는 예시 사진이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H237" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8402,7 +8402,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B238" t="str">
         <v/>
@@ -8417,10 +8417,10 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>파손</v>
+        <v>늦으면 얼마가 붙는지 표</v>
       </c>
       <c r="G238" t="str">
-        <v>'반납 접수' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 늦으면 얼마가 붙는지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H238" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8434,7 +8434,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B239" t="str">
         <v/>
@@ -8449,10 +8449,10 @@
         <v/>
       </c>
       <c r="F239" t="str">
-        <v>분실 있으면 미리 알리기</v>
+        <v>구성품 빠지면 얼마인지 표</v>
       </c>
       <c r="G239" t="str">
-        <v>'반납 접수' 화면에서 분실 있으면 미리 알리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 구성품 빠지면 얼마인지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B240" t="str">
         <v/>
@@ -8481,10 +8481,10 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>미리 알리면 배상이 줄어든다는 안내</v>
+        <v>반납 접수로 가기</v>
       </c>
       <c r="G240" t="str">
-        <v>'반납 접수' 화면에서 미리 알리면 배상이 줄어든다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 반납 접수로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8501,22 +8501,22 @@
         <v>SCN-024</v>
       </c>
       <c r="B241" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C241" t="str">
-        <v/>
+        <v>반납 접수</v>
       </c>
       <c r="D241" t="str">
-        <v/>
+        <v>RT-04</v>
       </c>
       <c r="E241" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F241" t="str">
-        <v>세척</v>
+        <v>반납할 장비와 기간 요약</v>
       </c>
       <c r="G241" t="str">
-        <v>'반납 접수' 화면에서 세척이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 반납할 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H241" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8545,13 +8545,13 @@
         <v/>
       </c>
       <c r="F242" t="str">
-        <v>건조 상태 스스로 확인</v>
+        <v>구성품 다 챙겼는지 하나씩 체크</v>
       </c>
       <c r="G242" t="str">
-        <v>'반납 접수'의 건조 상태 스스로 확인이 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 접수' 화면에서 구성품 다 챙겼는지 하나씩 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H242" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8577,13 +8577,13 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>반납 방법과 시각 확정</v>
+        <v>반납 상태 사진 올리기</v>
       </c>
       <c r="G243" t="str">
-        <v>'반납 접수' 화면에서 반납 방법과 시각 확정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수'의 반납 상태 사진 올리기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H243" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I243" t="str">
         <v/>
@@ -8609,10 +8609,10 @@
         <v/>
       </c>
       <c r="F244" t="str">
-        <v>접수 후 점검에 1~2일 걸린다는 안내</v>
+        <v>수령 때 사진과 나란히 견주기</v>
       </c>
       <c r="G244" t="str">
-        <v>'반납 접수' 화면에서 접수 후 점검에 1~2일 걸린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 수령 때 사진과 나란히 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H244" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8641,10 +8641,10 @@
         <v/>
       </c>
       <c r="F245" t="str">
-        <v>점검 끝나야 보증금이 풀린다는 안내</v>
+        <v>파손</v>
       </c>
       <c r="G245" t="str">
-        <v>'반납 접수' 화면에서 점검 끝나야 보증금이 풀린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8673,10 +8673,10 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>반납 접수 완료</v>
+        <v>분실 있으면 미리 알리기</v>
       </c>
       <c r="G246" t="str">
-        <v>'반납 접수' 화면에서 반납 접수 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 분실 있으면 미리 알리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8690,28 +8690,28 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B247" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C247" t="str">
-        <v>연체 안내</v>
+        <v/>
       </c>
       <c r="D247" t="str">
-        <v>RT-05</v>
+        <v/>
       </c>
       <c r="E247" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F247" t="str">
-        <v>반납 기한이 지났다는 안내와 얼마나 지났는지</v>
+        <v>미리 알리면 배상이 줄어든다는 안내</v>
       </c>
       <c r="G247" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 반납 기한이 지났다는 안내와 얼마나 지났는지가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 미리 알리면 배상이 줄어든다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H247" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I247" t="str">
         <v/>
@@ -8722,7 +8722,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B248" t="str">
         <v/>
@@ -8737,13 +8737,13 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>지금까지 쌓인 연체료</v>
+        <v>세척</v>
       </c>
       <c r="G248" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금까지 쌓인 연체료가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 세척이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I248" t="str">
         <v/>
@@ -8754,7 +8754,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B249" t="str">
         <v/>
@@ -8769,13 +8769,13 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>연체료 계산 방식 공개</v>
+        <v>건조 상태 스스로 확인</v>
       </c>
       <c r="G249" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연체료 계산 방식 공개가 보이는지 확인한다.</v>
+        <v>'반납 접수'의 건조 상태 스스로 확인이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H249" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I249" t="str">
         <v/>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B250" t="str">
         <v/>
@@ -8801,13 +8801,13 @@
         <v/>
       </c>
       <c r="F250" t="str">
-        <v>하루 더 지나면 얼마가 되는지 미리 보기</v>
+        <v>반납 방법과 시각 확정</v>
       </c>
       <c r="G250" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 하루 더 지나면 얼마가 되는지 미리 보기가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 반납 방법과 시각 확정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I250" t="str">
         <v/>
@@ -8818,7 +8818,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B251" t="str">
         <v/>
@@ -8833,13 +8833,13 @@
         <v/>
       </c>
       <c r="F251" t="str">
-        <v>지금 반납하면 얼마인지</v>
+        <v>접수 후 점검에 1~2일 걸린다는 안내</v>
       </c>
       <c r="G251" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납하면 얼마인지가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 접수 후 점검에 1~2일 걸린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I251" t="str">
         <v/>
@@ -8850,7 +8850,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B252" t="str">
         <v/>
@@ -8865,13 +8865,13 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>연장으로 바꿀 수 있는지 안내</v>
+        <v>점검 끝나야 보증금이 풀린다는 안내</v>
       </c>
       <c r="G252" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연장으로 바꿀 수 있는지 안내가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 점검 끝나야 보증금이 풀린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I252" t="str">
         <v/>
@@ -8882,7 +8882,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B253" t="str">
         <v/>
@@ -8897,13 +8897,13 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>보증금에서 먼저 빠진다는 안내</v>
+        <v>반납 접수 완료</v>
       </c>
       <c r="G253" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금에서 먼저 빠진다는 안내가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 반납 접수 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I253" t="str">
         <v/>
@@ -8917,22 +8917,22 @@
         <v>SCN-025</v>
       </c>
       <c r="B254" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C254" t="str">
-        <v/>
+        <v>연체 안내</v>
       </c>
       <c r="D254" t="str">
-        <v/>
+        <v>RT-05</v>
       </c>
       <c r="E254" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F254" t="str">
-        <v>보증금을 넘으면 추가 청구된다는 안내</v>
+        <v>반납 기한이 지났다는 안내와 얼마나 지났는지</v>
       </c>
       <c r="G254" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금을 넘으면 추가 청구된다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 반납 기한이 지났다는 안내와 얼마나 지났는지가 보이는지 확인한다.</v>
       </c>
       <c r="H254" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8961,10 +8961,10 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>연락 없이 7일 넘으면 분실 처리된다는 안내</v>
+        <v>지금까지 쌓인 연체료</v>
       </c>
       <c r="G255" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연락 없이 7일 넘으면 분실 처리된다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금까지 쌓인 연체료가 보이는지 확인한다.</v>
       </c>
       <c r="H255" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8993,10 +8993,10 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>지금 반납 접수하기</v>
+        <v>연체료 계산 방식 공개</v>
       </c>
       <c r="G256" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납 접수하기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연체료 계산 방식 공개가 보이는지 확인한다.</v>
       </c>
       <c r="H256" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9010,28 +9010,28 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B257" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C257" t="str">
-        <v>파손·분실 신고</v>
+        <v/>
       </c>
       <c r="D257" t="str">
-        <v>RT-06</v>
+        <v/>
       </c>
       <c r="E257" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F257" t="str">
-        <v>무엇이 어떻게 됐는지 고르기</v>
+        <v>하루 더 지나면 얼마가 되는지 미리 보기</v>
       </c>
       <c r="G257" t="str">
-        <v>'파손·분실 신고' 화면에서 무엇이 어떻게 됐는지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 하루 더 지나면 얼마가 되는지 미리 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H257" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B258" t="str">
         <v/>
@@ -9057,13 +9057,13 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>파손 부위 고르고 정도 고르기</v>
+        <v>지금 반납하면 얼마인지</v>
       </c>
       <c r="G258" t="str">
-        <v>'파손·분실 신고' 화면에서 파손 부위 고르고 정도 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납하면 얼마인지가 보이는지 확인한다.</v>
       </c>
       <c r="H258" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B259" t="str">
         <v/>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>사진 올리기(필수)</v>
+        <v>연장으로 바꿀 수 있는지 안내</v>
       </c>
       <c r="G259" t="str">
-        <v>'파손·분실 신고' 화면에서 사진 올리기(필수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연장으로 바꿀 수 있는지 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H259" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9106,7 +9106,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B260" t="str">
         <v/>
@@ -9121,13 +9121,13 @@
         <v/>
       </c>
       <c r="F260" t="str">
-        <v>언제 어떻게 생긴 일인지 적기</v>
+        <v>보증금에서 먼저 빠진다는 안내</v>
       </c>
       <c r="G260" t="str">
-        <v>'파손·분실 신고' 화면에서 언제 어떻게 생긴 일인지 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금에서 먼저 빠진다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H260" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I260" t="str">
         <v/>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B261" t="str">
         <v/>
@@ -9153,13 +9153,13 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>부위별 배상 기준액 바로 보기</v>
+        <v>보증금을 넘으면 추가 청구된다는 안내</v>
       </c>
       <c r="G261" t="str">
-        <v>'파손·분실 신고' 화면에서 부위별 배상 기준액 바로 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금을 넘으면 추가 청구된다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H261" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I261" t="str">
         <v/>
@@ -9170,7 +9170,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B262" t="str">
         <v/>
@@ -9185,13 +9185,13 @@
         <v/>
       </c>
       <c r="F262" t="str">
-        <v>가입한 보험이 있으면 면책 되는지 판정</v>
+        <v>연락 없이 7일 넘으면 분실 처리된다는 안내</v>
       </c>
       <c r="G262" t="str">
-        <v>'파손·분실 신고' 화면에서 가입한 보험이 있으면 면책 되는지 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연락 없이 7일 넘으면 분실 처리된다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H262" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I262" t="str">
         <v/>
@@ -9202,7 +9202,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B263" t="str">
         <v/>
@@ -9217,13 +9217,13 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>면책 제외 사유 안내</v>
+        <v>지금 반납 접수하기</v>
       </c>
       <c r="G263" t="str">
-        <v>'파손·분실 신고' 화면에서 면책 제외 사유 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납 접수하기가 보이는지 확인한다.</v>
       </c>
       <c r="H263" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I263" t="str">
         <v/>
@@ -9237,22 +9237,22 @@
         <v>SCN-026</v>
       </c>
       <c r="B264" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C264" t="str">
-        <v/>
+        <v>파손·분실 신고</v>
       </c>
       <c r="D264" t="str">
-        <v/>
+        <v>RT-06</v>
       </c>
       <c r="E264" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F264" t="str">
-        <v>예상 배상액과 보증금에서 얼마가 빠지는지</v>
+        <v>무엇이 어떻게 됐는지 고르기</v>
       </c>
       <c r="G264" t="str">
-        <v>'파손·분실 신고' 화면에서 예상 배상액과 보증금에서 얼마가 빠지는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 무엇이 어떻게 됐는지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H264" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9281,10 +9281,10 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>수리 가능하면 수리비만 낸다는 안내</v>
+        <v>파손 부위 고르고 정도 고르기</v>
       </c>
       <c r="G265" t="str">
-        <v>'파손·분실 신고' 화면에서 수리 가능하면 수리비만 낸다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 파손 부위 고르고 정도 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H265" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9313,10 +9313,10 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>신고하면 배상이 줄 수 있다는 안내</v>
+        <v>사진 올리기(필수)</v>
       </c>
       <c r="G266" t="str">
-        <v>'파손·분실 신고' 화면에서 신고하면 배상이 줄 수 있다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 사진 올리기(필수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H266" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9345,10 +9345,10 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>신고 접수</v>
+        <v>언제 어떻게 생긴 일인지 적기</v>
       </c>
       <c r="G267" t="str">
-        <v>'파손·분실 신고' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 언제 어떻게 생긴 일인지 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H267" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9362,28 +9362,28 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B268" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C268" t="str">
-        <v>점검 진행 중</v>
+        <v/>
       </c>
       <c r="D268" t="str">
-        <v>ST-01</v>
+        <v/>
       </c>
       <c r="E268" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F268" t="str">
-        <v>반납 접수됨과 접수 시각</v>
+        <v>부위별 배상 기준액 바로 보기</v>
       </c>
       <c r="G268" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납 접수됨과 접수 시각이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 부위별 배상 기준액 바로 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H268" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B269" t="str">
         <v/>
@@ -9409,13 +9409,13 @@
         <v/>
       </c>
       <c r="F269" t="str">
-        <v>점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)</v>
+        <v>가입한 보험이 있으면 면책 되는지 판정</v>
       </c>
       <c r="G269" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 가입한 보험이 있으면 면책 되는지 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H269" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I269" t="str">
         <v/>
@@ -9426,7 +9426,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B270" t="str">
         <v/>
@@ -9441,13 +9441,13 @@
         <v/>
       </c>
       <c r="F270" t="str">
-        <v>지금 어느 단계인지</v>
+        <v>면책 제외 사유 안내</v>
       </c>
       <c r="G270" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 지금 어느 단계인지가 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 면책 제외 사유 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H270" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I270" t="str">
         <v/>
@@ -9458,7 +9458,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B271" t="str">
         <v/>
@@ -9473,13 +9473,13 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>각 단계에서 무엇을 보는지 설명</v>
+        <v>예상 배상액과 보증금에서 얼마가 빠지는지</v>
       </c>
       <c r="G271" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 각 단계에서 무엇을 보는지 설명이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 예상 배상액과 보증금에서 얼마가 빠지는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H271" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I271" t="str">
         <v/>
@@ -9490,7 +9490,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B272" t="str">
         <v/>
@@ -9505,13 +9505,13 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>점검 예상 완료 시각</v>
+        <v>수리 가능하면 수리비만 낸다는 안내</v>
       </c>
       <c r="G272" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 예상 완료 시각이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 수리 가능하면 수리비만 낸다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I272" t="str">
         <v/>
@@ -9522,7 +9522,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B273" t="str">
         <v/>
@@ -9537,13 +9537,13 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>점검 결과가 나오면 알림 간다는 안내</v>
+        <v>신고하면 배상이 줄 수 있다는 안내</v>
       </c>
       <c r="G273" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 결과가 나오면 알림 간다는 안내가 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 신고하면 배상이 줄 수 있다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H273" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I273" t="str">
         <v/>
@@ -9554,7 +9554,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B274" t="str">
         <v/>
@@ -9569,13 +9569,13 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>보증금은 점검이 끝나야 풀린다는 안내</v>
+        <v>신고 접수</v>
       </c>
       <c r="G274" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 보증금은 점검이 끝나야 풀린다는 안내가 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H274" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I274" t="str">
         <v/>
@@ -9589,22 +9589,22 @@
         <v>SCN-027</v>
       </c>
       <c r="B275" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C275" t="str">
-        <v/>
+        <v>점검 진행 중</v>
       </c>
       <c r="D275" t="str">
-        <v/>
+        <v>ST-01</v>
       </c>
       <c r="E275" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F275" t="str">
-        <v>반납할 때 올린 사진 다시 보기</v>
+        <v>반납 접수됨과 접수 시각</v>
       </c>
       <c r="G275" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납할 때 올린 사진 다시 보기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납 접수됨과 접수 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H275" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9633,10 +9633,10 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>점검이 늦어지면 어떻게 되는지</v>
+        <v>점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)</v>
       </c>
       <c r="G276" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검이 늦어지면 어떻게 되는지가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)이 보이는지 확인한다.</v>
       </c>
       <c r="H276" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9650,28 +9650,28 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B277" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C277" t="str">
-        <v>정산 내역 - 연체·파손 청구</v>
+        <v/>
       </c>
       <c r="D277" t="str">
-        <v>ST-02</v>
+        <v/>
       </c>
       <c r="E277" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F277" t="str">
-        <v>점검 결과 요약</v>
+        <v>지금 어느 단계인지</v>
       </c>
       <c r="G277" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 점검 결과 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 지금 어느 단계인지가 보이는지 확인한다.</v>
       </c>
       <c r="H277" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B278" t="str">
         <v/>
@@ -9697,13 +9697,13 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)</v>
+        <v>각 단계에서 무엇을 보는지 설명</v>
       </c>
       <c r="G278" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 각 단계에서 무엇을 보는지 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H278" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B279" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>항목마다 근거 사진과 계산식</v>
+        <v>점검 예상 완료 시각</v>
       </c>
       <c r="G279" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 항목마다 근거 사진과 계산식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 예상 완료 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H279" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -9746,7 +9746,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B280" t="str">
         <v/>
@@ -9761,13 +9761,13 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v>보험으로 면책된 금액</v>
+        <v>점검 결과가 나오면 알림 간다는 안내</v>
       </c>
       <c r="G280" t="str">
-        <v>'정산 내역 - 연체·파손 청구'의 보험으로 면책된 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 결과가 나오면 알림 간다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H280" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -9778,7 +9778,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B281" t="str">
         <v/>
@@ -9793,13 +9793,13 @@
         <v/>
       </c>
       <c r="F281" t="str">
-        <v>청구 합계와 보증금에서 차감</v>
+        <v>보증금은 점검이 끝나야 풀린다는 안내</v>
       </c>
       <c r="G281" t="str">
-        <v>'정산 내역 - 연체·파손 청구'의 청구 합계와 보증금에서 차감이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 보증금은 점검이 끝나야 풀린다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H281" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I281" t="str">
         <v/>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B282" t="str">
         <v/>
@@ -9825,13 +9825,13 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v>보증금이 모자라면 추가 청구액</v>
+        <v>반납할 때 올린 사진 다시 보기</v>
       </c>
       <c r="G282" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 보증금이 모자라면 추가 청구액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납할 때 올린 사진 다시 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H282" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I282" t="str">
         <v/>
@@ -9842,7 +9842,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B283" t="str">
         <v/>
@@ -9857,13 +9857,13 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>추가 청구 결제 방법</v>
+        <v>점검이 늦어지면 어떻게 되는지</v>
       </c>
       <c r="G283" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 추가 청구 결제 방법을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검이 늦어지면 어떻게 되는지가 보이는지 확인한다.</v>
       </c>
       <c r="H283" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I283" t="str">
         <v/>
@@ -9877,22 +9877,22 @@
         <v>SCN-028</v>
       </c>
       <c r="B284" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C284" t="str">
-        <v/>
+        <v>정산 내역 - 연체·파손 청구</v>
       </c>
       <c r="D284" t="str">
-        <v/>
+        <v>ST-02</v>
       </c>
       <c r="E284" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F284" t="str">
-        <v>이의 제기하기</v>
+        <v>점검 결과 요약</v>
       </c>
       <c r="G284" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 점검 결과 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H284" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9921,10 +9921,10 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>이의 제기 기한 안내</v>
+        <v>청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)</v>
       </c>
       <c r="G285" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H285" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9953,13 +9953,13 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v>정산 확정되면 되돌릴 수 없다는 안내</v>
+        <v>항목마다 근거 사진과 계산식</v>
       </c>
       <c r="G286" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 정산 확정되면 되돌릴 수 없다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 항목마다 근거 사진과 계산식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H286" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -9985,13 +9985,13 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>정산서 내려받기</v>
+        <v>보험으로 면책된 금액</v>
       </c>
       <c r="G287" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'의 보험으로 면책된 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H287" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -10002,28 +10002,28 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B288" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C288" t="str">
-        <v>보증금 환급</v>
+        <v/>
       </c>
       <c r="D288" t="str">
-        <v>ST-03</v>
+        <v/>
       </c>
       <c r="E288" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F288" t="str">
-        <v>보증금 원금과 차감 내역 요약</v>
+        <v>청구 합계와 보증금에서 차감</v>
       </c>
       <c r="G288" t="str">
-        <v>'보증금 환급' 화면에서 보증금 원금과 차감 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'의 청구 합계와 보증금에서 차감이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H288" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B289" t="str">
         <v/>
@@ -10049,13 +10049,13 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>돌려받을 금액 크게</v>
+        <v>보증금이 모자라면 추가 청구액</v>
       </c>
       <c r="G289" t="str">
-        <v>'보증금 환급'의 돌려받을 금액 크게가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 보증금이 모자라면 추가 청구액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H289" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10066,7 +10066,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B290" t="str">
         <v/>
@@ -10081,13 +10081,13 @@
         <v/>
       </c>
       <c r="F290" t="str">
-        <v>환급 방법(카드 보류 해제·계좌 입금·적립금)</v>
+        <v>추가 청구 결제 방법</v>
       </c>
       <c r="G290" t="str">
-        <v>'보증금 환급' 화면에서 환급 방법(카드 보류 해제·계좌 입금·적립금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 추가 청구 결제 방법을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H290" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I290" t="str">
         <v/>
@@ -10098,7 +10098,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B291" t="str">
         <v/>
@@ -10113,10 +10113,10 @@
         <v/>
       </c>
       <c r="F291" t="str">
-        <v>방법별 걸리는 기간 안내</v>
+        <v>이의 제기하기</v>
       </c>
       <c r="G291" t="str">
-        <v>'보증금 환급' 화면에서 방법별 걸리는 기간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H291" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10130,7 +10130,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B292" t="str">
         <v/>
@@ -10145,13 +10145,13 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>카드 보류 해제가 무엇인지 설명</v>
+        <v>이의 제기 기한 안내</v>
       </c>
       <c r="G292" t="str">
-        <v>'보증금 환급'의 카드 보류 해제가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I292" t="str">
         <v/>
@@ -10162,7 +10162,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B293" t="str">
         <v/>
@@ -10177,13 +10177,13 @@
         <v/>
       </c>
       <c r="F293" t="str">
-        <v>적립금으로 받으면 더 주는 혜택</v>
+        <v>정산 확정되면 되돌릴 수 없다는 안내</v>
       </c>
       <c r="G293" t="str">
-        <v>'보증금 환급' 화면에서 적립금으로 받으면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 정산 확정되면 되돌릴 수 없다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H293" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B294" t="str">
         <v/>
@@ -10209,13 +10209,13 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>환급 진행 단계 표시</v>
+        <v>정산서 내려받기</v>
       </c>
       <c r="G294" t="str">
-        <v>'보증금 환급'의 환급 진행 단계 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H294" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I294" t="str">
         <v/>
@@ -10229,25 +10229,25 @@
         <v>SCN-029</v>
       </c>
       <c r="B295" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C295" t="str">
-        <v/>
+        <v>보증금 환급</v>
       </c>
       <c r="D295" t="str">
-        <v/>
+        <v>ST-03</v>
       </c>
       <c r="E295" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F295" t="str">
-        <v>카드사 사정으로 늦어질 수 있다는 안내</v>
+        <v>보증금 원금과 차감 내역 요약</v>
       </c>
       <c r="G295" t="str">
-        <v>'보증금 환급'의 카드사 사정으로 늦어질 수 있다는 안내를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 보증금 원금과 차감 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H295" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I295" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>언제까지 안 들어오면 어떻게 하는지</v>
+        <v>돌려받을 금액 크게</v>
       </c>
       <c r="G296" t="str">
-        <v>'보증금 환급' 화면에서 언제까지 안 들어오면 어떻게 하는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급'의 돌려받을 금액 크게가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H296" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10305,10 +10305,10 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>환급 내역서 받기</v>
+        <v>환급 방법(카드 보류 해제·계좌 입금·적립금)</v>
       </c>
       <c r="G297" t="str">
-        <v>'보증금 환급' 화면에서 환급 내역서 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 환급 방법(카드 보류 해제·계좌 입금·적립금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H297" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10322,28 +10322,28 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B298" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C298" t="str">
-        <v>환급 완료</v>
+        <v/>
       </c>
       <c r="D298" t="str">
-        <v>ST-04</v>
+        <v/>
       </c>
       <c r="E298" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F298" t="str">
-        <v>환급 완료 안내와 금액</v>
+        <v>방법별 걸리는 기간 안내</v>
       </c>
       <c r="G298" t="str">
-        <v>'환급 완료'의 환급 완료 안내와 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>'보증금 환급' 화면에서 방법별 걸리는 기간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H298" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I298" t="str">
         <v/>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B299" t="str">
         <v/>
@@ -10369,13 +10369,13 @@
         <v/>
       </c>
       <c r="F299" t="str">
-        <v>언제 어떤 방법으로 처리됐는지</v>
+        <v>카드 보류 해제가 무엇인지 설명</v>
       </c>
       <c r="G299" t="str">
-        <v>'환급 완료' 화면에서 언제 어떤 방법으로 처리됐는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급'의 카드 보류 해제가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H299" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,10 +10401,10 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)</v>
+        <v>적립금으로 받으면 더 주는 혜택</v>
       </c>
       <c r="G300" t="str">
-        <v>'환급 완료' 화면에서 이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 적립금으로 받으면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H300" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B301" t="str">
         <v/>
@@ -10433,13 +10433,13 @@
         <v/>
       </c>
       <c r="F301" t="str">
-        <v>영수증과 정산서 내려받기</v>
+        <v>환급 진행 단계 표시</v>
       </c>
       <c r="G301" t="str">
-        <v>'환급 완료'에서 영수증과 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'보증금 환급'의 환급 진행 단계 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H301" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B302" t="str">
         <v/>
@@ -10465,13 +10465,13 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>후기 쓰기 유도와 적립금 혜택</v>
+        <v>카드사 사정으로 늦어질 수 있다는 안내</v>
       </c>
       <c r="G302" t="str">
-        <v>'환급 완료' 화면에서 후기 쓰기 유도와 적립금 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급'의 카드사 사정으로 늦어질 수 있다는 안내를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H302" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B303" t="str">
         <v/>
@@ -10497,10 +10497,10 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>같은 장비 다시 빌리기</v>
+        <v>언제까지 안 들어오면 어떻게 하는지</v>
       </c>
       <c r="G303" t="str">
-        <v>'환급 완료' 화면에서 같은 장비 다시 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 언제까지 안 들어오면 어떻게 하는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10514,7 +10514,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B304" t="str">
         <v/>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>다음에 쓸 쿠폰</v>
+        <v>환급 내역서 받기</v>
       </c>
       <c r="G304" t="str">
-        <v>'환급 완료' 화면에서 다음에 쓸 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 환급 내역서 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10549,22 +10549,22 @@
         <v>SCN-030</v>
       </c>
       <c r="B305" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C305" t="str">
-        <v/>
+        <v>환급 완료</v>
       </c>
       <c r="D305" t="str">
-        <v/>
+        <v>ST-04</v>
       </c>
       <c r="E305" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F305" t="str">
-        <v>이용 횟수와 보증금 면제까지 남은 횟수</v>
+        <v>환급 완료 안내와 금액</v>
       </c>
       <c r="G305" t="str">
-        <v>'환급 완료'의 이용 횟수와 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료'의 환급 완료 안내와 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H305" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -10578,28 +10578,28 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B306" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C306" t="str">
-        <v>내 대여 내역</v>
+        <v/>
       </c>
       <c r="D306" t="str">
-        <v>MY-01</v>
+        <v/>
       </c>
       <c r="E306" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F306" t="str">
-        <v>상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)</v>
+        <v>언제 어떤 방법으로 처리됐는지</v>
       </c>
       <c r="G306" t="str">
-        <v>'내 대여 내역'에서 상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'환급 완료' 화면에서 언제 어떤 방법으로 처리됐는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H306" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I306" t="str">
         <v/>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -10625,13 +10625,13 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>상태별 건수 배지</v>
+        <v>이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)</v>
       </c>
       <c r="G307" t="str">
-        <v>'내 대여 내역'의 상태별 건수 배지가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료' 화면에서 이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H307" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I307" t="str">
         <v/>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B308" t="str">
         <v/>
@@ -10657,13 +10657,13 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>대여 카드 목록(장비 사진·이름·기간·상태·금액)</v>
+        <v>영수증과 정산서 내려받기</v>
       </c>
       <c r="G308" t="str">
-        <v>'내 대여 내역'의 대여 카드 목록(장비 사진·이름·기간·상태·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'환급 완료'에서 영수증과 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H308" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I308" t="str">
         <v/>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B309" t="str">
         <v/>
@@ -10689,13 +10689,13 @@
         <v/>
       </c>
       <c r="F309" t="str">
-        <v>이용 중인 것은 남은 시간 표시</v>
+        <v>후기 쓰기 유도와 적립금 혜택</v>
       </c>
       <c r="G309" t="str">
-        <v>'내 대여 내역'의 이용 중인 것은 남은 시간 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료' 화면에서 후기 쓰기 유도와 적립금 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I309" t="str">
         <v/>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B310" t="str">
         <v/>
@@ -10721,10 +10721,10 @@
         <v/>
       </c>
       <c r="F310" t="str">
-        <v>연체는 붉게 맨 위로</v>
+        <v>같은 장비 다시 빌리기</v>
       </c>
       <c r="G310" t="str">
-        <v>'내 대여 내역' 화면에서 연체는 붉게 맨 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환급 완료' 화면에서 같은 장비 다시 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10738,7 +10738,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B311" t="str">
         <v/>
@@ -10753,10 +10753,10 @@
         <v/>
       </c>
       <c r="F311" t="str">
-        <v>점검 중인 것은 예상 완료 시각</v>
+        <v>다음에 쓸 쿠폰</v>
       </c>
       <c r="G311" t="str">
-        <v>'내 대여 내역' 화면에서 점검 중인 것은 예상 완료 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환급 완료' 화면에서 다음에 쓸 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H311" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10770,7 +10770,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B312" t="str">
         <v/>
@@ -10785,10 +10785,10 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>보증금 상태 배지(보류중·환급완료)</v>
+        <v>이용 횟수와 보증금 면제까지 남은 횟수</v>
       </c>
       <c r="G312" t="str">
-        <v>'내 대여 내역'의 보증금 상태 배지(보류중·환급완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료'의 이용 횟수와 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H312" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -10805,25 +10805,25 @@
         <v>SCN-031</v>
       </c>
       <c r="B313" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C313" t="str">
-        <v/>
+        <v>내 대여 내역</v>
       </c>
       <c r="D313" t="str">
-        <v/>
+        <v>MY-01</v>
       </c>
       <c r="E313" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F313" t="str">
-        <v>기간</v>
+        <v>상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)</v>
       </c>
       <c r="G313" t="str">
-        <v>'내 대여 내역' 화면에서 기간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역'에서 상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>장비명 검색</v>
+        <v>상태별 건수 배지</v>
       </c>
       <c r="G314" t="str">
-        <v>'내 대여 내역'에서 장비명 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 대여 내역'의 상태별 건수 배지가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H314" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10881,13 +10881,13 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v>다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)</v>
+        <v>대여 카드 목록(장비 사진·이름·기간·상태·금액)</v>
       </c>
       <c r="G315" t="str">
-        <v>'내 대여 내역'에서 다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)를 눌러 본다.</v>
+        <v>'내 대여 내역'의 대여 카드 목록(장비 사진·이름·기간·상태·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H315" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I315" t="str">
         <v/>
@@ -10898,25 +10898,25 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B316" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C316" t="str">
-        <v>대여 상세</v>
+        <v/>
       </c>
       <c r="D316" t="str">
-        <v>MY-02</v>
+        <v/>
       </c>
       <c r="E316" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F316" t="str">
-        <v>대여번호와 상태</v>
+        <v>이용 중인 것은 남은 시간 표시</v>
       </c>
       <c r="G316" t="str">
-        <v>'대여 상세'의 대여번호와 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 대여 내역'의 이용 중인 것은 남은 시간 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H316" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B317" t="str">
         <v/>
@@ -10945,10 +10945,10 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)</v>
+        <v>연체는 붉게 맨 위로</v>
       </c>
       <c r="G317" t="str">
-        <v>'대여 상세' 화면에서 진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역' 화면에서 연체는 붉게 맨 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H317" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10962,7 +10962,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B318" t="str">
         <v/>
@@ -10977,10 +10977,10 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v>빌린 장비와 구성품</v>
+        <v>점검 중인 것은 예상 완료 시각</v>
       </c>
       <c r="G318" t="str">
-        <v>'대여 상세' 화면에서 빌린 장비와 구성품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역' 화면에서 점검 중인 것은 예상 완료 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H318" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10994,7 +10994,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B319" t="str">
         <v/>
@@ -11009,13 +11009,13 @@
         <v/>
       </c>
       <c r="F319" t="str">
-        <v>기간과 실제 수령</v>
+        <v>보증금 상태 배지(보류중·환급완료)</v>
       </c>
       <c r="G319" t="str">
-        <v>'대여 상세' 화면에서 기간과 실제 수령이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역'의 보증금 상태 배지(보류중·환급완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H319" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I319" t="str">
         <v/>
@@ -11026,7 +11026,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B320" t="str">
         <v/>
@@ -11041,10 +11041,10 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v>반납 시각</v>
+        <v>기간</v>
       </c>
       <c r="G320" t="str">
-        <v>'대여 상세' 화면에서 반납 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역' 화면에서 기간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H320" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B321" t="str">
         <v/>
@@ -11073,13 +11073,13 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>결제 내역(대여료·배송비·할인·보증금)</v>
+        <v>장비명 검색</v>
       </c>
       <c r="G321" t="str">
-        <v>'대여 상세'에서 결제 내역(대여료·배송비·할인·보증금)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'내 대여 내역'에서 장비명 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H321" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I321" t="str">
         <v/>
@@ -11090,7 +11090,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B322" t="str">
         <v/>
@@ -11105,13 +11105,13 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>보증금 상태와 환급 예정일</v>
+        <v>다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)</v>
       </c>
       <c r="G322" t="str">
-        <v>'대여 상세'의 보증금 상태와 환급 예정일이 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 대여 내역'에서 다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)를 눌러 본다.</v>
       </c>
       <c r="H322" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I322" t="str">
         <v/>
@@ -11125,25 +11125,25 @@
         <v>SCN-032</v>
       </c>
       <c r="B323" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C323" t="str">
-        <v/>
+        <v>대여 상세</v>
       </c>
       <c r="D323" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E323" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F323" t="str">
-        <v>수령 때와 반납 때 사진 견주기</v>
+        <v>대여번호와 상태</v>
       </c>
       <c r="G323" t="str">
-        <v>'대여 상세' 화면에서 수령 때와 반납 때 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'의 대여번호와 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H323" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I323" t="str">
         <v/>
@@ -11169,13 +11169,13 @@
         <v/>
       </c>
       <c r="F324" t="str">
-        <v>계약서와 정산서 내려받기</v>
+        <v>진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)</v>
       </c>
       <c r="G324" t="str">
-        <v>'대여 상세'에서 계약서와 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 상세' 화면에서 진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H324" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I324" t="str">
         <v/>
@@ -11201,13 +11201,13 @@
         <v/>
       </c>
       <c r="F325" t="str">
-        <v>상태에 따른 다음 행동 버튼</v>
+        <v>빌린 장비와 구성품</v>
       </c>
       <c r="G325" t="str">
-        <v>'대여 상세'에서 상태에 따른 다음 행동 버튼을 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 빌린 장비와 구성품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H325" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I325" t="str">
         <v/>
@@ -11233,10 +11233,10 @@
         <v/>
       </c>
       <c r="F326" t="str">
-        <v>이 대여 문의하기</v>
+        <v>기간과 실제 수령</v>
       </c>
       <c r="G326" t="str">
-        <v>'대여 상세' 화면에서 이 대여 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 기간과 실제 수령이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H326" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11250,25 +11250,25 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B327" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C327" t="str">
-        <v>후기 쓰기</v>
+        <v/>
       </c>
       <c r="D327" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E327" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F327" t="str">
-        <v>빌린 장비 확인</v>
+        <v>반납 시각</v>
       </c>
       <c r="G327" t="str">
-        <v>'후기 쓰기' 화면에서 빌린 장비 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 반납 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H327" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B328" t="str">
         <v/>
@@ -11297,13 +11297,13 @@
         <v/>
       </c>
       <c r="F328" t="str">
-        <v>전체 별점 주기</v>
+        <v>결제 내역(대여료·배송비·할인·보증금)</v>
       </c>
       <c r="G328" t="str">
-        <v>'후기 쓰기' 화면에서 전체 별점 주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 결제 내역(대여료·배송비·할인·보증금)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H328" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I328" t="str">
         <v/>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B329" t="str">
         <v/>
@@ -11329,13 +11329,13 @@
         <v/>
       </c>
       <c r="F329" t="str">
-        <v>항목별 별점(상태·설명과 같은지·수령 편의·응대)</v>
+        <v>보증금 상태와 환급 예정일</v>
       </c>
       <c r="G329" t="str">
-        <v>'후기 쓰기' 화면에서 항목별 별점(상태·설명과 같은지·수령 편의·응대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'의 보증금 상태와 환급 예정일이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H329" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I329" t="str">
         <v/>
@@ -11346,7 +11346,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B330" t="str">
         <v/>
@@ -11361,10 +11361,10 @@
         <v/>
       </c>
       <c r="F330" t="str">
-        <v>후기 글 쓰기</v>
+        <v>수령 때와 반납 때 사진 견주기</v>
       </c>
       <c r="G330" t="str">
-        <v>'후기 쓰기' 화면에서 후기 글 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 수령 때와 반납 때 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H330" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11378,7 +11378,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B331" t="str">
         <v/>
@@ -11393,13 +11393,13 @@
         <v/>
       </c>
       <c r="F331" t="str">
-        <v>사진 올리기</v>
+        <v>계약서와 정산서 내려받기</v>
       </c>
       <c r="G331" t="str">
-        <v>'후기 쓰기' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 계약서와 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H331" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I331" t="str">
         <v/>
@@ -11410,7 +11410,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B332" t="str">
         <v/>
@@ -11425,13 +11425,13 @@
         <v/>
       </c>
       <c r="F332" t="str">
-        <v>어떤 용도로 썼는지 태그</v>
+        <v>상태에 따른 다음 행동 버튼</v>
       </c>
       <c r="G332" t="str">
-        <v>'후기 쓰기' 화면에서 어떤 용도로 썼는지 태그가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 상태에 따른 다음 행동 버튼을 눌러 본다.</v>
       </c>
       <c r="H332" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I332" t="str">
         <v/>
@@ -11442,7 +11442,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B333" t="str">
         <v/>
@@ -11457,10 +11457,10 @@
         <v/>
       </c>
       <c r="F333" t="str">
-        <v>다음 사람에게 도움 될 팁 적기</v>
+        <v>이 대여 문의하기</v>
       </c>
       <c r="G333" t="str">
-        <v>'후기 쓰기' 화면에서 다음 사람에게 도움 될 팁 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 이 대여 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H333" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11477,25 +11477,25 @@
         <v>SCN-033</v>
       </c>
       <c r="B334" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C334" t="str">
-        <v/>
+        <v>후기 쓰기</v>
       </c>
       <c r="D334" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E334" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F334" t="str">
-        <v>후기 작성 적립금 안내</v>
+        <v>빌린 장비 확인</v>
       </c>
       <c r="G334" t="str">
-        <v>'후기 쓰기'의 후기 작성 적립금 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 쓰기' 화면에서 빌린 장비 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H334" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I334" t="str">
         <v/>
@@ -11521,10 +11521,10 @@
         <v/>
       </c>
       <c r="F335" t="str">
-        <v>사진 올리면 더 주는 혜택</v>
+        <v>전체 별점 주기</v>
       </c>
       <c r="G335" t="str">
-        <v>'후기 쓰기' 화면에서 사진 올리면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 전체 별점 주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H335" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11553,10 +11553,10 @@
         <v/>
       </c>
       <c r="F336" t="str">
-        <v>비공개로 쓰기</v>
+        <v>항목별 별점(상태·설명과 같은지·수령 편의·응대)</v>
       </c>
       <c r="G336" t="str">
-        <v>'후기 쓰기' 화면에서 비공개로 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 항목별 별점(상태·설명과 같은지·수령 편의·응대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H336" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11585,13 +11585,13 @@
         <v/>
       </c>
       <c r="F337" t="str">
-        <v>등록하기</v>
+        <v>후기 글 쓰기</v>
       </c>
       <c r="G337" t="str">
-        <v>'후기 쓰기'의 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 쓰기' 화면에서 후기 글 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H337" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I337" t="str">
         <v/>
@@ -11602,25 +11602,25 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B338" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C338" t="str">
-        <v>알림·쿠폰</v>
+        <v/>
       </c>
       <c r="D338" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E338" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F338" t="str">
-        <v>받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)</v>
+        <v>사진 올리기</v>
       </c>
       <c r="G338" t="str">
-        <v>'알림·쿠폰' 화면에서 받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H338" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B339" t="str">
         <v/>
@@ -11649,10 +11649,10 @@
         <v/>
       </c>
       <c r="F339" t="str">
-        <v>알림 받을 방법(문자·카톡·이메일)</v>
+        <v>어떤 용도로 썼는지 태그</v>
       </c>
       <c r="G339" t="str">
-        <v>'알림·쿠폰' 화면에서 알림 받을 방법(문자·카톡·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 어떤 용도로 썼는지 태그가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H339" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11666,7 +11666,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B340" t="str">
         <v/>
@@ -11681,13 +11681,13 @@
         <v/>
       </c>
       <c r="F340" t="str">
-        <v>자리 나면 알림 신청 목록</v>
+        <v>다음 사람에게 도움 될 팁 적기</v>
       </c>
       <c r="G340" t="str">
-        <v>'알림·쿠폰'의 자리 나면 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 다음 사람에게 도움 될 팁 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H340" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I340" t="str">
         <v/>
@@ -11698,7 +11698,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B341" t="str">
         <v/>
@@ -11713,13 +11713,13 @@
         <v/>
       </c>
       <c r="F341" t="str">
-        <v>보유 쿠폰 목록과 남은 기간</v>
+        <v>후기 작성 적립금 안내</v>
       </c>
       <c r="G341" t="str">
-        <v>'알림·쿠폰'의 보유 쿠폰 목록과 남은 기간을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 쓰기'의 후기 작성 적립금 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H341" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I341" t="str">
         <v/>
@@ -11730,7 +11730,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B342" t="str">
         <v/>
@@ -11745,13 +11745,13 @@
         <v/>
       </c>
       <c r="F342" t="str">
-        <v>쿠폰 탭(사용가능·사용완료·기간만료)</v>
+        <v>사진 올리면 더 주는 혜택</v>
       </c>
       <c r="G342" t="str">
-        <v>'알림·쿠폰'에서 쿠폰 탭(사용가능·사용완료·기간만료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 쓰기' 화면에서 사진 올리면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H342" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I342" t="str">
         <v/>
@@ -11762,7 +11762,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B343" t="str">
         <v/>
@@ -11777,10 +11777,10 @@
         <v/>
       </c>
       <c r="F343" t="str">
-        <v>적립금 잔액과 쌓인 내역</v>
+        <v>비공개로 쓰기</v>
       </c>
       <c r="G343" t="str">
-        <v>'알림·쿠폰' 화면에서 적립금 잔액과 쌓인 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 비공개로 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H343" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11794,7 +11794,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B344" t="str">
         <v/>
@@ -11809,13 +11809,13 @@
         <v/>
       </c>
       <c r="F344" t="str">
-        <v>적립금 쓰는 법 안내</v>
+        <v>등록하기</v>
       </c>
       <c r="G344" t="str">
-        <v>'알림·쿠폰' 화면에서 적립금 쓰는 법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기'의 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H344" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I344" t="str">
         <v/>
@@ -11829,25 +11829,25 @@
         <v>SCN-034</v>
       </c>
       <c r="B345" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C345" t="str">
-        <v/>
+        <v>알림·쿠폰</v>
       </c>
       <c r="D345" t="str">
-        <v/>
+        <v>MY-04</v>
       </c>
       <c r="E345" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F345" t="str">
-        <v>보증금 면제까지 남은 횟수</v>
+        <v>받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)</v>
       </c>
       <c r="G345" t="str">
-        <v>'알림·쿠폰'의 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림·쿠폰' 화면에서 받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H345" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I345" t="str">
         <v/>
@@ -11873,13 +11873,13 @@
         <v/>
       </c>
       <c r="F346" t="str">
-        <v>쿠폰 등록하기</v>
+        <v>알림 받을 방법(문자·카톡·이메일)</v>
       </c>
       <c r="G346" t="str">
-        <v>'알림·쿠폰'의 쿠폰 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'알림·쿠폰' 화면에서 알림 받을 방법(문자·카톡·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H346" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I346" t="str">
         <v/>
@@ -11890,28 +11890,28 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B347" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C347" t="str">
-        <v>자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D347" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E347" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F347" t="str">
-        <v>질문 검색창</v>
+        <v>자리 나면 알림 신청 목록</v>
       </c>
       <c r="G347" t="str">
-        <v>'자주 묻는 질문'의 질문 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'알림·쿠폰'의 자리 나면 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H347" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I347" t="str">
         <v/>
@@ -11922,7 +11922,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B348" t="str">
         <v/>
@@ -11937,13 +11937,13 @@
         <v/>
       </c>
       <c r="F348" t="str">
-        <v>분류 탭(대여·보증금·수령배송·반납·연체파손·환불)</v>
+        <v>보유 쿠폰 목록과 남은 기간</v>
       </c>
       <c r="G348" t="str">
-        <v>'자주 묻는 질문'에서 분류 탭(대여·보증금·수령배송·반납·연체파손·환불)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'알림·쿠폰'의 보유 쿠폰 목록과 남은 기간을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H348" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I348" t="str">
         <v/>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B349" t="str">
         <v/>
@@ -11969,13 +11969,13 @@
         <v/>
       </c>
       <c r="F349" t="str">
-        <v>많이 찾는 질문 5개 먼저</v>
+        <v>쿠폰 탭(사용가능·사용완료·기간만료)</v>
       </c>
       <c r="G349" t="str">
-        <v>'자주 묻는 질문' 화면을 열고 많이 찾는 질문 5개 먼저가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'알림·쿠폰'에서 쿠폰 탭(사용가능·사용완료·기간만료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H349" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I349" t="str">
         <v/>
@@ -11986,7 +11986,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B350" t="str">
         <v/>
@@ -12001,13 +12001,13 @@
         <v/>
       </c>
       <c r="F350" t="str">
-        <v>질문 아코디언 목록</v>
+        <v>적립금 잔액과 쌓인 내역</v>
       </c>
       <c r="G350" t="str">
-        <v>'자주 묻는 질문'의 질문 아코디언 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'알림·쿠폰' 화면에서 적립금 잔액과 쌓인 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H350" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I350" t="str">
         <v/>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B351" t="str">
         <v/>
@@ -12033,10 +12033,10 @@
         <v/>
       </c>
       <c r="F351" t="str">
-        <v>답 안에서 관련 화면으로 바로 가기</v>
+        <v>적립금 쓰는 법 안내</v>
       </c>
       <c r="G351" t="str">
-        <v>'자주 묻는 질문' 화면에서 답 안에서 관련 화면으로 바로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰' 화면에서 적립금 쓰는 법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H351" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B352" t="str">
         <v/>
@@ -12065,13 +12065,13 @@
         <v/>
       </c>
       <c r="F352" t="str">
-        <v>도움이 됐는지 묻기</v>
+        <v>보증금 면제까지 남은 횟수</v>
       </c>
       <c r="G352" t="str">
-        <v>'자주 묻는 질문' 화면에서 도움이 됐는지 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰'의 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H352" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12082,7 +12082,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B353" t="str">
         <v/>
@@ -12097,13 +12097,13 @@
         <v/>
       </c>
       <c r="F353" t="str">
-        <v>원하는 답이 없을 때 문의하기</v>
+        <v>쿠폰 등록하기</v>
       </c>
       <c r="G353" t="str">
-        <v>'자주 묻는 질문' 화면에서 원하는 답이 없을 때 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰'의 쿠폰 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H353" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12117,25 +12117,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B354" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C354" t="str">
-        <v/>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="D354" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E354" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F354" t="str">
-        <v>고객센터 운영시간과 전화번호</v>
+        <v>질문 검색창</v>
       </c>
       <c r="G354" t="str">
-        <v>'자주 묻는 질문' 화면에서 고객센터 운영시간과 전화번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'의 질문 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H354" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I354" t="str">
         <v/>
@@ -12146,28 +12146,28 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B355" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C355" t="str">
-        <v>1:1 문의</v>
+        <v/>
       </c>
       <c r="D355" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E355" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F355" t="str">
-        <v>문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)</v>
+        <v>분류 탭(대여·보증금·수령배송·반납·연체파손·환불)</v>
       </c>
       <c r="G355" t="str">
-        <v>'1:1 문의' 화면에서 문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'에서 분류 탭(대여·보증금·수령배송·반납·연체파손·환불)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H355" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I355" t="str">
         <v/>
@@ -12178,7 +12178,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B356" t="str">
         <v/>
@@ -12193,13 +12193,13 @@
         <v/>
       </c>
       <c r="F356" t="str">
-        <v>관련 대여 건 고르기와 정보 자동 채움</v>
+        <v>많이 찾는 질문 5개 먼저</v>
       </c>
       <c r="G356" t="str">
-        <v>'1:1 문의'의 관련 대여 건 고르기와 정보 자동 채움이 실제 데이터와 같은지 대조한다.</v>
+        <v>'자주 묻는 질문' 화면을 열고 많이 찾는 질문 5개 먼저가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H356" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I356" t="str">
         <v/>
@@ -12210,7 +12210,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B357" t="str">
         <v/>
@@ -12225,13 +12225,13 @@
         <v/>
       </c>
       <c r="F357" t="str">
-        <v>문의 내용 쓰기</v>
+        <v>질문 아코디언 목록</v>
       </c>
       <c r="G357" t="str">
-        <v>'1:1 문의' 화면에서 문의 내용 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'의 질문 아코디언 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H357" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I357" t="str">
         <v/>
@@ -12242,7 +12242,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B358" t="str">
         <v/>
@@ -12257,10 +12257,10 @@
         <v/>
       </c>
       <c r="F358" t="str">
-        <v>사진 올리기</v>
+        <v>답 안에서 관련 화면으로 바로 가기</v>
       </c>
       <c r="G358" t="str">
-        <v>'1:1 문의' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 답 안에서 관련 화면으로 바로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H358" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B359" t="str">
         <v/>
@@ -12289,10 +12289,10 @@
         <v/>
       </c>
       <c r="F359" t="str">
-        <v>답변 받을 방법(문자·이메일)</v>
+        <v>도움이 됐는지 묻기</v>
       </c>
       <c r="G359" t="str">
-        <v>'1:1 문의' 화면에서 답변 받을 방법(문자·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 도움이 됐는지 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H359" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12306,7 +12306,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B360" t="str">
         <v/>
@@ -12321,10 +12321,10 @@
         <v/>
       </c>
       <c r="F360" t="str">
-        <v>답변까지 걸리는 시간 안내</v>
+        <v>원하는 답이 없을 때 문의하기</v>
       </c>
       <c r="G360" t="str">
-        <v>'1:1 문의' 화면에서 답변까지 걸리는 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 원하는 답이 없을 때 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H360" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12338,7 +12338,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B361" t="str">
         <v/>
@@ -12353,13 +12353,13 @@
         <v/>
       </c>
       <c r="F361" t="str">
-        <v>정산 이의는 기한이 있다는 안내</v>
+        <v>고객센터 운영시간과 전화번호</v>
       </c>
       <c r="G361" t="str">
-        <v>'1:1 문의'에서 정산 이의는 기한이 있다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 고객센터 운영시간과 전화번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H361" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I361" t="str">
         <v/>
@@ -12373,22 +12373,22 @@
         <v>SCN-036</v>
       </c>
       <c r="B362" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C362" t="str">
-        <v/>
+        <v>1:1 문의</v>
       </c>
       <c r="D362" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E362" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F362" t="str">
-        <v>지난 문의 내역과 답변</v>
+        <v>문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)</v>
       </c>
       <c r="G362" t="str">
-        <v>'1:1 문의' 화면에서 지난 문의 내역과 답변이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H362" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12417,13 +12417,13 @@
         <v/>
       </c>
       <c r="F363" t="str">
-        <v>급하면 전화 안내</v>
+        <v>관련 대여 건 고르기와 정보 자동 채움</v>
       </c>
       <c r="G363" t="str">
-        <v>'1:1 문의' 화면에서 급하면 전화 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'의 관련 대여 건 고르기와 정보 자동 채움이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H363" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I363" t="str">
         <v/>
@@ -12449,10 +12449,10 @@
         <v/>
       </c>
       <c r="F364" t="str">
-        <v>문의 보내기</v>
+        <v>문의 내용 쓰기</v>
       </c>
       <c r="G364" t="str">
-        <v>'1:1 문의' 화면에서 문의 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 내용 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H364" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12466,25 +12466,25 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B365" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C365" t="str">
-        <v>대여 약관·규정</v>
+        <v/>
       </c>
       <c r="D365" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E365" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F365" t="str">
-        <v>한 줄 요약으로 먼저 보여주기</v>
+        <v>사진 올리기</v>
       </c>
       <c r="G365" t="str">
-        <v>'대여 약관·규정' 화면에서 한 줄 요약으로 먼저 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H365" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B366" t="str">
         <v/>
@@ -12513,13 +12513,13 @@
         <v/>
       </c>
       <c r="F366" t="str">
-        <v>조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)</v>
+        <v>답변 받을 방법(문자·이메일)</v>
       </c>
       <c r="G366" t="str">
-        <v>'대여 약관·규정'에서 조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 받을 방법(문자·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H366" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I366" t="str">
         <v/>
@@ -12530,7 +12530,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B367" t="str">
         <v/>
@@ -12545,10 +12545,10 @@
         <v/>
       </c>
       <c r="F367" t="str">
-        <v>연체료 계산 방식과 단계표</v>
+        <v>답변까지 걸리는 시간 안내</v>
       </c>
       <c r="G367" t="str">
-        <v>'대여 약관·규정' 화면에서 연체료 계산 방식과 단계표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 답변까지 걸리는 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H367" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12562,7 +12562,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B368" t="str">
         <v/>
@@ -12577,13 +12577,13 @@
         <v/>
       </c>
       <c r="F368" t="str">
-        <v>부품별 파손 배상 기준표</v>
+        <v>정산 이의는 기한이 있다는 안내</v>
       </c>
       <c r="G368" t="str">
-        <v>'대여 약관·규정' 화면에서 부품별 파손 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'에서 정산 이의는 기한이 있다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H368" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I368" t="str">
         <v/>
@@ -12594,7 +12594,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B369" t="str">
         <v/>
@@ -12609,13 +12609,13 @@
         <v/>
       </c>
       <c r="F369" t="str">
-        <v>취소 시점별 환불율 단계표</v>
+        <v>지난 문의 내역과 답변</v>
       </c>
       <c r="G369" t="str">
-        <v>'대여 약관·규정'에서 취소 시점별 환불율 단계표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'1:1 문의' 화면에서 지난 문의 내역과 답변이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H369" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I369" t="str">
         <v/>
@@ -12626,7 +12626,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B370" t="str">
         <v/>
@@ -12641,13 +12641,13 @@
         <v/>
       </c>
       <c r="F370" t="str">
-        <v>무료 취소 기한 계산 예시</v>
+        <v>급하면 전화 안내</v>
       </c>
       <c r="G370" t="str">
-        <v>'대여 약관·규정'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'1:1 문의' 화면에서 급하면 전화 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H370" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I370" t="str">
         <v/>
@@ -12658,7 +12658,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B371" t="str">
         <v/>
@@ -12673,13 +12673,13 @@
         <v/>
       </c>
       <c r="F371" t="str">
-        <v>반납 상태 기준(세척·건조)</v>
+        <v>문의 보내기</v>
       </c>
       <c r="G371" t="str">
-        <v>'대여 약관·규정'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'1:1 문의' 화면에서 문의 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H371" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I371" t="str">
         <v/>
@@ -12693,22 +12693,22 @@
         <v>SCN-037</v>
       </c>
       <c r="B372" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C372" t="str">
-        <v/>
+        <v>대여 약관·규정</v>
       </c>
       <c r="D372" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E372" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F372" t="str">
-        <v>분실 처리 기준</v>
+        <v>한 줄 요약으로 먼저 보여주기</v>
       </c>
       <c r="G372" t="str">
-        <v>'대여 약관·규정' 화면에서 분실 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정' 화면에서 한 줄 요약으로 먼저 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H372" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12737,13 +12737,13 @@
         <v/>
       </c>
       <c r="F373" t="str">
-        <v>내 대여로 계산해보기</v>
+        <v>조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)</v>
       </c>
       <c r="G373" t="str">
-        <v>'대여 약관·규정' 화면에서 내 대여로 계산해보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정'에서 조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H373" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I373" t="str">
         <v/>
@@ -12769,10 +12769,10 @@
         <v/>
       </c>
       <c r="F374" t="str">
-        <v>규정 바뀐 이력</v>
+        <v>연체료 계산 방식과 단계표</v>
       </c>
       <c r="G374" t="str">
-        <v>'대여 약관·규정' 화면에서 규정 바뀐 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정' 화면에서 연체료 계산 방식과 단계표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H374" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12801,24 +12801,248 @@
         <v/>
       </c>
       <c r="F375" t="str">
+        <v>부품별 파손 배상 기준표</v>
+      </c>
+      <c r="G375" t="str">
+        <v>'대여 약관·규정' 화면에서 부품별 파손 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H375" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I375" t="str">
+        <v/>
+      </c>
+      <c r="J375" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B376" t="str">
+        <v/>
+      </c>
+      <c r="C376" t="str">
+        <v/>
+      </c>
+      <c r="D376" t="str">
+        <v/>
+      </c>
+      <c r="E376" t="str">
+        <v/>
+      </c>
+      <c r="F376" t="str">
+        <v>취소 시점별 환불율 단계표</v>
+      </c>
+      <c r="G376" t="str">
+        <v>'대여 약관·규정'에서 취소 시점별 환불율 단계표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H376" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I376" t="str">
+        <v/>
+      </c>
+      <c r="J376" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B377" t="str">
+        <v/>
+      </c>
+      <c r="C377" t="str">
+        <v/>
+      </c>
+      <c r="D377" t="str">
+        <v/>
+      </c>
+      <c r="E377" t="str">
+        <v/>
+      </c>
+      <c r="F377" t="str">
+        <v>무료 취소 기한 계산 예시</v>
+      </c>
+      <c r="G377" t="str">
+        <v>'대여 약관·규정'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H377" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I377" t="str">
+        <v/>
+      </c>
+      <c r="J377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B378" t="str">
+        <v/>
+      </c>
+      <c r="C378" t="str">
+        <v/>
+      </c>
+      <c r="D378" t="str">
+        <v/>
+      </c>
+      <c r="E378" t="str">
+        <v/>
+      </c>
+      <c r="F378" t="str">
+        <v>반납 상태 기준(세척·건조)</v>
+      </c>
+      <c r="G378" t="str">
+        <v>'대여 약관·규정'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+      </c>
+      <c r="H378" t="str">
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+      </c>
+      <c r="I378" t="str">
+        <v/>
+      </c>
+      <c r="J378" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B379" t="str">
+        <v/>
+      </c>
+      <c r="C379" t="str">
+        <v/>
+      </c>
+      <c r="D379" t="str">
+        <v/>
+      </c>
+      <c r="E379" t="str">
+        <v/>
+      </c>
+      <c r="F379" t="str">
+        <v>분실 처리 기준</v>
+      </c>
+      <c r="G379" t="str">
+        <v>'대여 약관·규정' 화면에서 분실 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H379" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I379" t="str">
+        <v/>
+      </c>
+      <c r="J379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B380" t="str">
+        <v/>
+      </c>
+      <c r="C380" t="str">
+        <v/>
+      </c>
+      <c r="D380" t="str">
+        <v/>
+      </c>
+      <c r="E380" t="str">
+        <v/>
+      </c>
+      <c r="F380" t="str">
+        <v>내 대여로 계산해보기</v>
+      </c>
+      <c r="G380" t="str">
+        <v>'대여 약관·규정' 화면에서 내 대여로 계산해보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H380" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I380" t="str">
+        <v/>
+      </c>
+      <c r="J380" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B381" t="str">
+        <v/>
+      </c>
+      <c r="C381" t="str">
+        <v/>
+      </c>
+      <c r="D381" t="str">
+        <v/>
+      </c>
+      <c r="E381" t="str">
+        <v/>
+      </c>
+      <c r="F381" t="str">
+        <v>규정 바뀐 이력</v>
+      </c>
+      <c r="G381" t="str">
+        <v>'대여 약관·규정' 화면에서 규정 바뀐 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H381" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I381" t="str">
+        <v/>
+      </c>
+      <c r="J381" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B382" t="str">
+        <v/>
+      </c>
+      <c r="C382" t="str">
+        <v/>
+      </c>
+      <c r="D382" t="str">
+        <v/>
+      </c>
+      <c r="E382" t="str">
+        <v/>
+      </c>
+      <c r="F382" t="str">
         <v>약관 내려받기</v>
       </c>
-      <c r="G375" t="str">
+      <c r="G382" t="str">
         <v>'대여 약관·규정' 화면에서 약관 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
-      <c r="H375" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
-      </c>
-      <c r="I375" t="str">
-        <v/>
-      </c>
-      <c r="J375" t="str">
+      <c r="H382" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I382" t="str">
+        <v/>
+      </c>
+      <c r="J382" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J375"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J382"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
@@ -727,7 +727,7 @@
         <v>확인 항목 수</v>
       </c>
       <c r="B5">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6">
@@ -735,7 +735,7 @@
         <v xml:space="preserve">  └ 공통(사이트 전체)</v>
       </c>
       <c r="B6">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -803,7 +803,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J382"/>
+  <dimension ref="A1:J388"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1426,28 +1426,28 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C20" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="D20" t="str">
-        <v>HO-01</v>
+        <v/>
       </c>
       <c r="E20" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너</v>
+        <v>끊어진 링크 — 갈 곳이 실제로 있는지</v>
       </c>
       <c r="G20" t="str">
-        <v>'홈'에서 빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>스펙팩 7-9-2 의 검사 글을 사이트 «뿌리»에서 한 번 돌린다. ⚠ pages/ 만 주면 한 층 위의 화면 목록을 못 봐서 멀쩡한 화면이 외톨이로 잘못 잡힌다.</v>
       </c>
       <c r="H20" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>끊어진 링크 0건. `href` 가 가리키는 .html 이 모두 실제로 있다.</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B21" t="str">
         <v/>
@@ -1473,13 +1473,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)</v>
+        <v>없는 그림 · 빈 파일</v>
       </c>
       <c r="G21" t="str">
-        <v>'홈' 화면을 열고 카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>같은 검사 글의 결과에서 «없는 그림»과 «빈 파일» 줄을 본다.</v>
       </c>
       <c r="H21" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>둘 다 0건. `src` 가 가리키는 파일이 모두 있고, 0바이트로 남은 화면이 없다.</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B22" t="str">
         <v/>
@@ -1505,13 +1505,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>이번 주 인기 장비 8개 카드</v>
+        <v>외톨이 화면 — 아무 데서도 안 이어지는 화면</v>
       </c>
       <c r="G22" t="str">
-        <v>'홈' 화면을 열고 이번 주 인기 장비 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>같은 검사 글의 «외톨이» 줄을 본다. 나온 화면은 어디서 이어져야 맞는지 정하고 그 링크를 놓는다.</v>
       </c>
       <c r="H22" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>외톨이 0건. 만들어 놓고 갈 길이 없는 화면이 없다.</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B23" t="str">
         <v/>
@@ -1537,13 +1537,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>이번 주말 남은 장비 캐러셀(잔여 수량 표시)</v>
+        <v>화면 수가 약속한 수와 같은지</v>
       </c>
       <c r="G23" t="str">
-        <v>'홈'에서 이번 주말 남은 장비 캐러셀(잔여 수량 표시)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>만든 .html 수를 세어 스펙팩 4장의 화면 수와 견준다.</v>
       </c>
       <c r="H23" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>두 수가 같다. 목록에는 있는데 안 만든 화면, 만들었는데 목록에 없는 화면 둘 다 0.</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1554,7 +1554,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B24" t="str">
         <v/>
@@ -1569,13 +1569,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>세트로 빌리면 싼 패키지 안내 배너</v>
+        <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>'홈'에서 세트로 빌리면 싼 패키지 안내 배너를 눌러 본다.</v>
+        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SCN-001</v>
+        <v>SCN-000</v>
       </c>
       <c r="B25" t="str">
         <v/>
@@ -1601,13 +1601,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>처음이신가요 3단계 안내(고른다-받는다-돌려준다)</v>
+        <v>굳은 날짜 — 견본 날짜가 오늘에서 거꾸로 잡혔는지</v>
       </c>
       <c r="G25" t="str">
-        <v>'홈' 화면을 열고 처음이신가요 3단계 안내(고른다-받는다-돌려준다)가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>목록·상세의 날짜와 요일을 오늘 기준으로 다시 센다. 요일은 눈으로 세지 말고 달력과 맞춘다.</v>
       </c>
       <c r="H25" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>지난 날짜가 「예정」으로 보이지 않는다. 요일이 그 날짜의 실제 요일과 같다.</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1621,25 +1621,25 @@
         <v>SCN-001</v>
       </c>
       <c r="B26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C26" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>HO-01</v>
       </c>
       <c r="E26" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F26" t="str">
-        <v>실제 이용 후기 슬라이드 5개</v>
+        <v>빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너</v>
       </c>
       <c r="G26" t="str">
-        <v>'홈' 화면을 열고 실제 이용 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈'에서 빌릴 기간을 먼저 고르는 검색바가 얹힌 히어로 배너의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H26" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1665,13 +1665,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>보증금</v>
+        <v>카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)</v>
       </c>
       <c r="G27" t="str">
-        <v>'홈' 화면에서 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 카테고리 바로가기 8종(텐트·타프·화로대·카메라·렌즈·짐벌·조명·음향)이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H27" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1697,13 +1697,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>연체료 정책 요약 카드</v>
+        <v>이번 주 인기 장비 8개 카드</v>
       </c>
       <c r="G28" t="str">
-        <v>'홈'의 연체료 정책 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'홈' 화면을 열고 이번 주 인기 장비 8개 카드가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H28" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1729,13 +1729,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>매장 위치와 운영시간</v>
+        <v>이번 주말 남은 장비 캐러셀(잔여 수량 표시)</v>
       </c>
       <c r="G29" t="str">
-        <v>'홈' 화면에서 매장 위치와 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 이번 주말 남은 장비 캐러셀(잔여 수량 표시)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H29" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1761,13 +1761,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>하단 카톡 채널 안내</v>
+        <v>세트로 빌리면 싼 패키지 안내 배너</v>
       </c>
       <c r="G30" t="str">
-        <v>'홈' 화면에서 하단 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'에서 세트로 빌리면 싼 패키지 안내 배너를 눌러 본다.</v>
       </c>
       <c r="H30" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1778,28 +1778,28 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B31" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C31" t="str">
-        <v>카테고리 홈</v>
+        <v/>
       </c>
       <c r="D31" t="str">
-        <v>HO-02</v>
+        <v/>
       </c>
       <c r="E31" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F31" t="str">
-        <v>카테고리 대표 사진과 한 줄 소개</v>
+        <v>처음이신가요 3단계 안내(고른다-받는다-돌려준다)</v>
       </c>
       <c r="G31" t="str">
-        <v>'카테고리 홈' 화면에서 카테고리 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면을 열고 처음이신가요 3단계 안내(고른다-받는다-돌려준다)가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H31" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B32" t="str">
         <v/>
@@ -1825,10 +1825,10 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>이 종류 인기 장비 8개</v>
+        <v>실제 이용 후기 슬라이드 5개</v>
       </c>
       <c r="G32" t="str">
-        <v>'카테고리 홈' 화면을 열고 이 종류 인기 장비 8개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면을 열고 실제 이용 후기 슬라이드 5개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H32" t="str">
         <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
@@ -1842,7 +1842,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B33" t="str">
         <v/>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>하위 종류 필터 칩</v>
+        <v>보증금</v>
       </c>
       <c r="G33" t="str">
-        <v>'카테고리 홈'에서 하위 종류 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'홈' 화면에서 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H33" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1874,7 +1874,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B34" t="str">
         <v/>
@@ -1889,13 +1889,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>이 종류를 처음 빌리는 분을 위한 고르는 법</v>
+        <v>연체료 정책 요약 카드</v>
       </c>
       <c r="G34" t="str">
-        <v>'카테고리 홈' 화면에서 이 종류를 처음 빌리는 분을 위한 고르는 법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈'의 연체료 정책 요약 카드를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H34" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1906,7 +1906,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B35" t="str">
         <v/>
@@ -1921,10 +1921,10 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>함께 빌리면 좋은 장비 추천</v>
+        <v>매장 위치와 운영시간</v>
       </c>
       <c r="G35" t="str">
-        <v>'카테고리 홈' 화면에서 함께 빌리면 좋은 장비 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'홈' 화면에서 매장 위치와 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H35" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>SCN-002</v>
+        <v>SCN-001</v>
       </c>
       <c r="B36" t="str">
         <v/>
@@ -1953,13 +1953,13 @@
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>이 종류 자주 묻는 질문 4개</v>
+        <v>하단 카톡 채널 안내</v>
       </c>
       <c r="G36" t="str">
-        <v>'카테고리 홈' 화면을 열고 이 종류 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'홈' 화면에서 하단 카톡 채널 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H36" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1973,22 +1973,22 @@
         <v>SCN-002</v>
       </c>
       <c r="B37" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C37" t="str">
-        <v/>
+        <v>카테고리 홈</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>HO-02</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F37" t="str">
-        <v>이 종류 후기 모음</v>
+        <v>카테고리 대표 사진과 한 줄 소개</v>
       </c>
       <c r="G37" t="str">
-        <v>'카테고리 홈' 화면에서 이 종류 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 카테고리 대표 사진과 한 줄 소개가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H37" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2017,13 +2017,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>보관</v>
+        <v>이 종류 인기 장비 8개</v>
       </c>
       <c r="G38" t="str">
-        <v>'카테고리 홈' 화면에서 보관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면을 열고 이 종류 인기 장비 8개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H38" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -2049,13 +2049,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>사용 주의사항 안내</v>
+        <v>하위 종류 필터 칩</v>
       </c>
       <c r="G39" t="str">
-        <v>'카테고리 홈' 화면에서 사용 주의사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈'에서 하위 종류 필터 칩의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H39" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -2066,28 +2066,28 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B40" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C40" t="str">
-        <v>기간으로 찾기 - 결과</v>
+        <v/>
       </c>
       <c r="D40" t="str">
-        <v>HO-03</v>
+        <v/>
       </c>
       <c r="E40" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v>검색 조건 요약 바(기간·종류·인원)</v>
+        <v>이 종류를 처음 빌리는 분을 위한 고르는 법</v>
       </c>
       <c r="G40" t="str">
-        <v>'기간으로 찾기 - 결과'에서 검색 조건 요약 바(기간·종류·인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈' 화면에서 이 종류를 처음 빌리는 분을 위한 고르는 법이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H40" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -2098,7 +2098,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B41" t="str">
         <v/>
@@ -2113,10 +2113,10 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>기간 다시 고르기 달력</v>
+        <v>함께 빌리면 좋은 장비 추천</v>
       </c>
       <c r="G41" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 기간 다시 고르기 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 함께 빌리면 좋은 장비 추천이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H41" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B42" t="str">
         <v/>
@@ -2145,13 +2145,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)</v>
+        <v>이 종류 자주 묻는 질문 4개</v>
       </c>
       <c r="G42" t="str">
-        <v>'기간으로 찾기 - 결과'에서 결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈' 화면을 열고 이 종류 자주 묻는 질문 4개가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H42" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -2162,7 +2162,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B43" t="str">
         <v/>
@@ -2177,13 +2177,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)</v>
+        <v>이 종류 후기 모음</v>
       </c>
       <c r="G43" t="str">
-        <v>'기간으로 찾기 - 결과'에서 필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'카테고리 홈' 화면에서 이 종류 후기 모음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H43" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B44" t="str">
         <v/>
@@ -2209,13 +2209,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)</v>
+        <v>보관</v>
       </c>
       <c r="G44" t="str">
-        <v>'기간으로 찾기 - 결과'의 장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 보관이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H44" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -2226,7 +2226,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>SCN-003</v>
+        <v>SCN-002</v>
       </c>
       <c r="B45" t="str">
         <v/>
@@ -2241,10 +2241,10 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>그 기간에 마감된 장비는 흐리게 뒤로</v>
+        <v>사용 주의사항 안내</v>
       </c>
       <c r="G45" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 그 기간에 마감된 장비는 흐리게 뒤로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'카테고리 홈' 화면에서 사용 주의사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H45" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2261,25 +2261,25 @@
         <v>SCN-003</v>
       </c>
       <c r="B46" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C46" t="str">
-        <v/>
+        <v>기간으로 찾기 - 결과</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>HO-03</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F46" t="str">
-        <v>다음 가능한 날짜 안내</v>
+        <v>검색 조건 요약 바(기간·종류·인원)</v>
       </c>
       <c r="G46" t="str">
-        <v>'기간으로 찾기 - 결과' 화면에서 다음 가능한 날짜 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기간으로 찾기 - 결과'에서 검색 조건 요약 바(기간·종류·인원)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H46" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2305,13 +2305,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>더 보기 페이지네이션</v>
+        <v>기간 다시 고르기 달력</v>
       </c>
       <c r="G47" t="str">
-        <v>'기간으로 찾기 - 결과'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 기간 다시 고르기 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H47" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2322,28 +2322,28 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B48" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C48" t="str">
-        <v>결과 없음 - 그 기간에 빈 장비가 없음</v>
+        <v/>
       </c>
       <c r="D48" t="str">
-        <v>HO-04</v>
+        <v/>
       </c>
       <c r="E48" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v>고른 기간과 조건 요약</v>
+        <v>결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)</v>
       </c>
       <c r="G48" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 고른 기간과 조건 요약이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 결과 수와 정렬(추천·낮은 대여료·별점·잔여 많은 순)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H48" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2354,7 +2354,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B49" t="str">
         <v/>
@@ -2369,13 +2369,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>왜 없는지 한 줄 설명(주말·연휴에 몰린다)</v>
+        <v>필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)</v>
       </c>
       <c r="G49" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 왜 없는지 한 줄 설명(주말·연휴에 몰린다)가 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 필터 패널(대여료 범위·보증금 범위·수령 방법·브랜드)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H49" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B50" t="str">
         <v/>
@@ -2401,13 +2401,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>기간을 앞뒤로 넓혀 보기 버튼</v>
+        <v>장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)</v>
       </c>
       <c r="G50" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 기간을 앞뒤로 넓혀 보기 버튼이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'의 장비 카드 목록(사진·이름·1일 대여료·총 대여료·보증금·잔여 대수·별점)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H50" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B51" t="str">
         <v/>
@@ -2433,13 +2433,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>빌릴 수 있는 가까운 날짜 3개 추천 칩</v>
+        <v>그 기간에 마감된 장비는 흐리게 뒤로</v>
       </c>
       <c r="G51" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 빌릴 수 있는 가까운 날짜 3개 추천 칩이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 그 기간에 마감된 장비는 흐리게 뒤로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H51" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B52" t="str">
         <v/>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>조건을 풀어 보기(브랜드·수령 방법 해제)</v>
+        <v>다음 가능한 날짜 안내</v>
       </c>
       <c r="G52" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 조건을 풀어 보기(브랜드·수령 방법 해제)가 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과' 화면에서 다음 가능한 날짜 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H52" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2482,7 +2482,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SCN-004</v>
+        <v>SCN-003</v>
       </c>
       <c r="B53" t="str">
         <v/>
@@ -2497,13 +2497,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>자리 나면 알려드리기 신청</v>
+        <v>더 보기 페이지네이션</v>
       </c>
       <c r="G53" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 자리 나면 알려드리기 신청이 보이는지 확인한다.</v>
+        <v>'기간으로 찾기 - 결과'에서 더 보기 페이지네이션의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H53" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2517,22 +2517,22 @@
         <v>SCN-004</v>
       </c>
       <c r="B54" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C54" t="str">
-        <v/>
+        <v>결과 없음 - 그 기간에 빈 장비가 없음</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>HO-04</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F54" t="str">
-        <v>비슷한 장비 대체 추천 4개</v>
+        <v>고른 기간과 조건 요약</v>
       </c>
       <c r="G54" t="str">
-        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 비슷한 장비 대체 추천 4개가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 고른 기간과 조건 요약이 보이는지 확인한다.</v>
       </c>
       <c r="H54" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -2546,28 +2546,28 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B55" t="str">
-        <v>홈</v>
+        <v/>
       </c>
       <c r="C55" t="str">
-        <v>기획전·특가</v>
+        <v/>
       </c>
       <c r="D55" t="str">
-        <v>HO-05</v>
+        <v/>
       </c>
       <c r="E55" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v>기획전 대표 배너와 남은 기간 카운트다운</v>
+        <v>왜 없는지 한 줄 설명(주말·연휴에 몰린다)</v>
       </c>
       <c r="G55" t="str">
-        <v>'기획전·특가'에서 기획전 대표 배너와 남은 기간 카운트다운을 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 왜 없는지 한 줄 설명(주말·연휴에 몰린다)가 보이는지 확인한다.</v>
       </c>
       <c r="H55" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2578,7 +2578,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B56" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>기획전 쿠폰 받기</v>
+        <v>기간을 앞뒤로 넓혀 보기 버튼</v>
       </c>
       <c r="G56" t="str">
-        <v>'기획전·특가' 화면에서 기획전 쿠폰 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 기간을 앞뒤로 넓혀 보기 버튼이 보이는지 확인한다.</v>
       </c>
       <c r="H56" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B57" t="str">
         <v/>
@@ -2625,13 +2625,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>특가 장비 목록(정가·특가·할인율)</v>
+        <v>빌릴 수 있는 가까운 날짜 3개 추천 칩</v>
       </c>
       <c r="G57" t="str">
-        <v>'기획전·특가'의 특가 장비 목록(정가·특가·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 빌릴 수 있는 가까운 날짜 3개 추천 칩이 보이는지 확인한다.</v>
       </c>
       <c r="H57" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B58" t="str">
         <v/>
@@ -2657,13 +2657,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>평일 할인 안내(월~목 30% 싸다)</v>
+        <v>조건을 풀어 보기(브랜드·수령 방법 해제)</v>
       </c>
       <c r="G58" t="str">
-        <v>'기획전·특가' 화면에서 평일 할인 안내(월~목 30% 싸다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 조건을 풀어 보기(브랜드·수령 방법 해제)가 보이는지 확인한다.</v>
       </c>
       <c r="H58" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2674,7 +2674,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B59" t="str">
         <v/>
@@ -2689,13 +2689,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>장기 대여 할인 단계표(7일 이상·30일 이상)</v>
+        <v>자리 나면 알려드리기 신청</v>
       </c>
       <c r="G59" t="str">
-        <v>'기획전·특가' 화면에서 장기 대여 할인 단계표(7일 이상·30일 이상)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 자리 나면 알려드리기 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H59" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SCN-005</v>
+        <v>SCN-004</v>
       </c>
       <c r="B60" t="str">
         <v/>
@@ -2721,13 +2721,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>첫 대여 고객 보증금 면제 안내</v>
+        <v>비슷한 장비 대체 추천 4개</v>
       </c>
       <c r="G60" t="str">
-        <v>'기획전·특가' 화면에서 첫 대여 고객 보증금 면제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결과 없음 - 그 기간에 빈 장비가 없음' 화면이 나오게 한 뒤, 비슷한 장비 대체 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H60" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2741,25 +2741,25 @@
         <v>SCN-005</v>
       </c>
       <c r="B61" t="str">
-        <v/>
+        <v>홈</v>
       </c>
       <c r="C61" t="str">
-        <v/>
+        <v>기획전·특가</v>
       </c>
       <c r="D61" t="str">
-        <v/>
+        <v>HO-05</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F61" t="str">
-        <v>기획전 이용 조건과 제외 대상</v>
+        <v>기획전 대표 배너와 남은 기간 카운트다운</v>
       </c>
       <c r="G61" t="str">
-        <v>'기획전·특가' 화면에서 기획전 이용 조건과 제외 대상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가'에서 기획전 대표 배너와 남은 기간 카운트다운을 눌러 본다.</v>
       </c>
       <c r="H61" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2785,10 +2785,10 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>종료된 기획전 안내</v>
+        <v>기획전 쿠폰 받기</v>
       </c>
       <c r="G62" t="str">
-        <v>'기획전·특가' 화면에서 종료된 기획전 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 기획전 쿠폰 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H62" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2802,28 +2802,28 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B63" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C63" t="str">
-        <v>장비 목록</v>
+        <v/>
       </c>
       <c r="D63" t="str">
-        <v>PD-01</v>
+        <v/>
       </c>
       <c r="E63" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F63" t="str">
-        <v>종류</v>
+        <v>특가 장비 목록(정가·특가·할인율)</v>
       </c>
       <c r="G63" t="str">
-        <v>'장비 목록' 화면에서 종류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가'의 특가 장비 목록(정가·특가·할인율)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H63" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2834,7 +2834,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B64" t="str">
         <v/>
@@ -2849,10 +2849,10 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>브랜드</v>
+        <v>평일 할인 안내(월~목 30% 싸다)</v>
       </c>
       <c r="G64" t="str">
-        <v>'장비 목록' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 평일 할인 안내(월~목 30% 싸다)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H64" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B65" t="str">
         <v/>
@@ -2881,10 +2881,10 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>대여료</v>
+        <v>장기 대여 할인 단계표(7일 이상·30일 이상)</v>
       </c>
       <c r="G65" t="str">
-        <v>'장비 목록' 화면에서 대여료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 장기 대여 할인 단계표(7일 이상·30일 이상)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H65" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -2898,7 +2898,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B66" t="str">
         <v/>
@@ -2913,13 +2913,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>보증금 필터</v>
+        <v>첫 대여 고객 보증금 면제 안내</v>
       </c>
       <c r="G66" t="str">
-        <v>'장비 목록'에서 보증금 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기획전·특가' 화면에서 첫 대여 고객 보증금 면제 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H66" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2930,7 +2930,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B67" t="str">
         <v/>
@@ -2945,13 +2945,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>정렬(추천·낮은 대여료·많이 빌린 순·별점)</v>
+        <v>기획전 이용 조건과 제외 대상</v>
       </c>
       <c r="G67" t="str">
-        <v>'장비 목록'에서 정렬(추천·낮은 대여료·많이 빌린 순·별점)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'기획전·특가' 화면에서 기획전 이용 조건과 제외 대상이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H67" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2962,7 +2962,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SCN-006</v>
+        <v>SCN-005</v>
       </c>
       <c r="B68" t="str">
         <v/>
@@ -2977,13 +2977,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)</v>
+        <v>종료된 기획전 안내</v>
       </c>
       <c r="G68" t="str">
-        <v>'장비 목록'의 장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'기획전·특가' 화면에서 종료된 기획전 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H68" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2997,25 +2997,25 @@
         <v>SCN-006</v>
       </c>
       <c r="B69" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C69" t="str">
-        <v/>
+        <v>장비 목록</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>PD-01</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F69" t="str">
-        <v>고른 기간 표시와 바꾸기</v>
+        <v>종류</v>
       </c>
       <c r="G69" t="str">
-        <v>'장비 목록'의 고른 기간 표시와 바꾸기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'장비 목록' 화면에서 종류가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H69" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -3041,10 +3041,10 @@
         <v/>
       </c>
       <c r="F70" t="str">
-        <v>그 기간 불가 장비 흐림 처리와 다음 가능일</v>
+        <v>브랜드</v>
       </c>
       <c r="G70" t="str">
-        <v>'장비 목록' 화면에서 그 기간 불가 장비 흐림 처리와 다음 가능일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H70" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3073,10 +3073,10 @@
         <v/>
       </c>
       <c r="F71" t="str">
-        <v>세트 패키지 섞어 보여주기</v>
+        <v>대여료</v>
       </c>
       <c r="G71" t="str">
-        <v>'장비 목록' 화면에서 세트 패키지 섞어 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 대여료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H71" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3105,13 +3105,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>무한 스크롤</v>
+        <v>보증금 필터</v>
       </c>
       <c r="G72" t="str">
-        <v>'장비 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'에서 보증금 필터의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H72" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -3122,28 +3122,28 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B73" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C73" t="str">
-        <v>장비 상세</v>
+        <v/>
       </c>
       <c r="D73" t="str">
-        <v>PD-02</v>
+        <v/>
       </c>
       <c r="E73" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F73" t="str">
-        <v>장비 사진 갤러리 5장</v>
+        <v>정렬(추천·낮은 대여료·많이 빌린 순·별점)</v>
       </c>
       <c r="G73" t="str">
-        <v>'장비 상세' 화면을 열고 장비 사진 갤러리 5장이 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'장비 목록'에서 정렬(추천·낮은 대여료·많이 빌린 순·별점)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H73" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -3154,7 +3154,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B74" t="str">
         <v/>
@@ -3169,13 +3169,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>장비명</v>
+        <v>장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)</v>
       </c>
       <c r="G74" t="str">
-        <v>'장비 상세' 화면에서 장비명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'의 장비 카드 목록(사진·이름·1일 대여료·보증금·잔여 대수·별점·찜)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H74" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B75" t="str">
         <v/>
@@ -3201,13 +3201,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>브랜드</v>
+        <v>고른 기간 표시와 바꾸기</v>
       </c>
       <c r="G75" t="str">
-        <v>'장비 상세' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록'의 고른 기간 표시와 바꾸기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H75" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3218,7 +3218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B76" t="str">
         <v/>
@@ -3233,10 +3233,10 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>모델과 별점</v>
+        <v>그 기간 불가 장비 흐림 처리와 다음 가능일</v>
       </c>
       <c r="G76" t="str">
-        <v>'장비 상세' 화면에서 모델과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 그 기간 불가 장비 흐림 처리와 다음 가능일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H76" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B77" t="str">
         <v/>
@@ -3265,10 +3265,10 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>1일 대여료와 고른 기간 총액</v>
+        <v>세트 패키지 섞어 보여주기</v>
       </c>
       <c r="G77" t="str">
-        <v>'장비 상세' 화면에서 1일 대여료와 고른 기간 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 목록' 화면에서 세트 패키지 섞어 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H77" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3282,7 +3282,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SCN-007</v>
+        <v>SCN-006</v>
       </c>
       <c r="B78" t="str">
         <v/>
@@ -3297,13 +3297,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>보증금 금액과 언제 돌려주는지</v>
+        <v>무한 스크롤</v>
       </c>
       <c r="G78" t="str">
-        <v>'장비 상세'의 보증금 금액과 언제 돌려주는지가 실제 데이터와 같은지 대조한다.</v>
+        <v>'장비 목록' 화면에서 무한 스크롤이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H78" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3317,25 +3317,25 @@
         <v>SCN-007</v>
       </c>
       <c r="B79" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C79" t="str">
-        <v/>
+        <v>장비 상세</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>PD-02</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F79" t="str">
-        <v>날짜별 재고 달력 열기</v>
+        <v>장비 사진 갤러리 5장</v>
       </c>
       <c r="G79" t="str">
-        <v>'장비 상세' 화면에서 날짜별 재고 달력 열기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면을 열고 장비 사진 갤러리 5장이 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H79" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3361,10 +3361,10 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>대여 기간과 수량 고르기</v>
+        <v>장비명</v>
       </c>
       <c r="G80" t="str">
-        <v>'장비 상세' 화면에서 대여 기간과 수량 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 장비명이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H80" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3393,10 +3393,10 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
+        <v>브랜드</v>
       </c>
       <c r="G81" t="str">
-        <v>'장비 상세' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 브랜드가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H81" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3425,13 +3425,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>구성품 목록과 사진</v>
+        <v>모델과 별점</v>
       </c>
       <c r="G82" t="str">
-        <v>'장비 상세'의 구성품 목록과 사진을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 모델과 별점이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H82" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3457,10 +3457,10 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>이용 안내(사용법·주의사항·금지사항)</v>
+        <v>1일 대여료와 고른 기간 총액</v>
       </c>
       <c r="G83" t="str">
-        <v>'장비 상세' 화면에서 이용 안내(사용법·주의사항·금지사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 1일 대여료와 고른 기간 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H83" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3489,13 +3489,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>파손 시 배상 기준표</v>
+        <v>보증금 금액과 언제 돌려주는지</v>
       </c>
       <c r="G84" t="str">
-        <v>'장비 상세' 화면에서 파손 시 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세'의 보증금 금액과 언제 돌려주는지가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H84" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3521,10 +3521,10 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>함께 빌리면 좋은 장비</v>
+        <v>날짜별 재고 달력 열기</v>
       </c>
       <c r="G85" t="str">
-        <v>'장비 상세' 화면에서 함께 빌리면 좋은 장비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 날짜별 재고 달력 열기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H85" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3553,13 +3553,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>후기 목록과 별점 분포</v>
+        <v>대여 기간과 수량 고르기</v>
       </c>
       <c r="G86" t="str">
-        <v>'장비 상세'의 후기 목록과 별점 분포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 대여 기간과 수량 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H86" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3585,10 +3585,10 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>하단 고정 바(총액·보증금·담기·바로 빌리기)</v>
+        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
       </c>
       <c r="G87" t="str">
-        <v>'장비 상세' 화면에서 하단 고정 바(총액·보증금·담기·바로 빌리기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H87" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3602,28 +3602,28 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B88" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C88" t="str">
-        <v>날짜별 가용 재고 달력</v>
+        <v/>
       </c>
       <c r="D88" t="str">
-        <v>PD-03</v>
+        <v/>
       </c>
       <c r="E88" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F88" t="str">
-        <v>월 단위 달력에 날짜마다 남은 수량 표시</v>
+        <v>구성품 목록과 사진</v>
       </c>
       <c r="G88" t="str">
-        <v>'날짜별 가용 재고 달력'의 월 단위 달력에 날짜마다 남은 수량 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'장비 상세'의 구성품 목록과 사진을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H88" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3634,7 +3634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B89" t="str">
         <v/>
@@ -3649,10 +3649,10 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>다 나간 날은 흐리게 하고 못 고르게 막음</v>
+        <v>이용 안내(사용법·주의사항·금지사항)</v>
       </c>
       <c r="G89" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 다 나간 날은 흐리게 하고 못 고르게 막음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 이용 안내(사용법·주의사항·금지사항)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H89" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3666,7 +3666,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B90" t="str">
         <v/>
@@ -3681,10 +3681,10 @@
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기</v>
+        <v>파손 시 배상 기준표</v>
       </c>
       <c r="G90" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 파손 시 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H90" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B91" t="str">
         <v/>
@@ -3713,10 +3713,10 @@
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>고른 기간에 하루라도 모자라면 그 날을 짚어 알림</v>
+        <v>함께 빌리면 좋은 장비</v>
       </c>
       <c r="G91" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간에 하루라도 모자라면 그 날을 짚어 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 함께 빌리면 좋은 장비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H91" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B92" t="str">
         <v/>
@@ -3745,13 +3745,13 @@
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>수량을 바꾸면 가능한 날이 다시 계산됨</v>
+        <v>후기 목록과 별점 분포</v>
       </c>
       <c r="G92" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 수량을 바꾸면 가능한 날이 다시 계산됨이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세'의 후기 목록과 별점 분포를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H92" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>SCN-008</v>
+        <v>SCN-007</v>
       </c>
       <c r="B93" t="str">
         <v/>
@@ -3777,10 +3777,10 @@
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>최소</v>
+        <v>하단 고정 바(총액·보증금·담기·바로 빌리기)</v>
       </c>
       <c r="G93" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 최소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'장비 상세' 화면에서 하단 고정 바(총액·보증금·담기·바로 빌리기)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H93" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3797,25 +3797,25 @@
         <v>SCN-008</v>
       </c>
       <c r="B94" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C94" t="str">
-        <v/>
+        <v>날짜별 가용 재고 달력</v>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>PD-03</v>
       </c>
       <c r="E94" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F94" t="str">
-        <v>최대 대여 일수 안내</v>
+        <v>월 단위 달력에 날짜마다 남은 수량 표시</v>
       </c>
       <c r="G94" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 최대 대여 일수 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력'의 월 단위 달력에 날짜마다 남은 수량 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H94" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3841,13 +3841,13 @@
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>요일별 대여료 차이 표시(주말 할증)</v>
+        <v>다 나간 날은 흐리게 하고 못 고르게 막음</v>
       </c>
       <c r="G95" t="str">
-        <v>'날짜별 가용 재고 달력'의 요일별 대여료 차이 표시(주말 할증)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 다 나간 날은 흐리게 하고 못 고르게 막음이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H95" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3873,10 +3873,10 @@
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>준비</v>
+        <v>빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기</v>
       </c>
       <c r="G96" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 빌리는 날과 돌려주는 날을 두 번 눌러 기간으로 잡기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H96" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3905,10 +3905,10 @@
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>점검에 필요한 날(반납 다음 날은 못 빌림) 안내</v>
+        <v>고른 기간에 하루라도 모자라면 그 날을 짚어 알림</v>
       </c>
       <c r="G97" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 점검에 필요한 날(반납 다음 날은 못 빌림) 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간에 하루라도 모자라면 그 날을 짚어 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H97" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3937,10 +3937,10 @@
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>고른 기간 요약과 총액</v>
+        <v>수량을 바꾸면 가능한 날이 다시 계산됨</v>
       </c>
       <c r="G98" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간 요약과 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 수량을 바꾸면 가능한 날이 다시 계산됨이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H98" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3969,10 +3969,10 @@
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>이 기간으로 예약하기</v>
+        <v>최소</v>
       </c>
       <c r="G99" t="str">
-        <v>'날짜별 가용 재고 달력' 화면에서 이 기간으로 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 최소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H99" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -3986,25 +3986,25 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B100" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C100" t="str">
-        <v>옵션·부속품 고르기</v>
+        <v/>
       </c>
       <c r="D100" t="str">
-        <v>PD-04</v>
+        <v/>
       </c>
       <c r="E100" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F100" t="str">
-        <v>고른 장비와 기간 요약</v>
+        <v>최대 대여 일수 안내</v>
       </c>
       <c r="G100" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 고른 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 최대 대여 일수 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H100" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B101" t="str">
         <v/>
@@ -4033,13 +4033,13 @@
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>옵션 고르기(크기·색·구성)</v>
+        <v>요일별 대여료 차이 표시(주말 할증)</v>
       </c>
       <c r="G101" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 옵션 고르기(크기·색·구성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력'의 요일별 대여료 차이 표시(주말 할증)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H101" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B102" t="str">
         <v/>
@@ -4065,10 +4065,10 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)</v>
+        <v>준비</v>
       </c>
       <c r="G102" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 준비가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H102" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B103" t="str">
         <v/>
@@ -4097,10 +4097,10 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>부속품별 대여료와 보증금</v>
+        <v>점검에 필요한 날(반납 다음 날은 못 빌림) 안내</v>
       </c>
       <c r="G103" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 부속품별 대여료와 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 점검에 필요한 날(반납 다음 날은 못 빌림) 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H103" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4114,7 +4114,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B104" t="str">
         <v/>
@@ -4129,10 +4129,10 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>보험 붙이기 선택(파손 면책 하루 3,000원)</v>
+        <v>고른 기간 요약과 총액</v>
       </c>
       <c r="G104" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 보험 붙이기 선택(파손 면책 하루 3,000원)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 고른 기간 요약과 총액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H104" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4146,7 +4146,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SCN-009</v>
+        <v>SCN-008</v>
       </c>
       <c r="B105" t="str">
         <v/>
@@ -4161,10 +4161,10 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>면책 범위와 제외 사항 안내</v>
+        <v>이 기간으로 예약하기</v>
       </c>
       <c r="G105" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 면책 범위와 제외 사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'날짜별 가용 재고 달력' 화면에서 이 기간으로 예약하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H105" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4181,22 +4181,22 @@
         <v>SCN-009</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C106" t="str">
-        <v/>
+        <v>옵션·부속품 고르기</v>
       </c>
       <c r="D106" t="str">
-        <v/>
+        <v>PD-04</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F106" t="str">
-        <v>옵션에 따른 재고 차이 안내</v>
+        <v>고른 장비와 기간 요약</v>
       </c>
       <c r="G106" t="str">
-        <v>'옵션·부속품 고르기' 화면에서 옵션에 따른 재고 차이 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 고른 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H106" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4225,13 +4225,13 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>금액 요약과 다음 단계</v>
+        <v>옵션 고르기(크기·색·구성)</v>
       </c>
       <c r="G107" t="str">
-        <v>'옵션·부속품 고르기'의 금액 요약과 다음 단계가 실제 데이터와 같은지 대조한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 옵션 고르기(크기·색·구성)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H107" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I107" t="str">
         <v/>
@@ -4242,28 +4242,28 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B108" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>대여 불가 - 그 날짜 마감</v>
+        <v/>
       </c>
       <c r="D108" t="str">
-        <v>PD-05</v>
+        <v/>
       </c>
       <c r="E108" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F108" t="str">
-        <v>고른 기간과 장비 요약</v>
+        <v>함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)</v>
       </c>
       <c r="G108" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 고른 기간과 장비 요약이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 함께 빌릴 부속품 체크(전용 매트·팩 추가·보관함)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H108" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I108" t="str">
         <v/>
@@ -4274,7 +4274,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B109" t="str">
         <v/>
@@ -4289,13 +4289,13 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>어느 날짜가 왜 안 되는지 짚어 알림</v>
+        <v>부속품별 대여료와 보증금</v>
       </c>
       <c r="G109" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 어느 날짜가 왜 안 되는지 짚어 알림이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 부속품별 대여료와 보증금이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H109" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I109" t="str">
         <v/>
@@ -4306,7 +4306,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B110" t="str">
         <v/>
@@ -4321,13 +4321,13 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>가장 가까운 빌릴 수 있는 날짜 3개 추천</v>
+        <v>보험 붙이기 선택(파손 면책 하루 3,000원)</v>
       </c>
       <c r="G110" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 가장 가까운 빌릴 수 있는 날짜 3개 추천이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 보험 붙이기 선택(파손 면책 하루 3,000원)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H110" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I110" t="str">
         <v/>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B111" t="str">
         <v/>
@@ -4353,13 +4353,13 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>수량을 줄이면 되는지 알림</v>
+        <v>면책 범위와 제외 사항 안내</v>
       </c>
       <c r="G111" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 수량을 줄이면 되는지 알림이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 면책 범위와 제외 사항 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H111" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I111" t="str">
         <v/>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B112" t="str">
         <v/>
@@ -4385,13 +4385,13 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>같은 종류 다른 장비 추천 4개</v>
+        <v>옵션에 따른 재고 차이 안내</v>
       </c>
       <c r="G112" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 같은 종류 다른 장비 추천 4개가 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기' 화면에서 옵션에 따른 재고 차이 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H112" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I112" t="str">
         <v/>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>SCN-010</v>
+        <v>SCN-009</v>
       </c>
       <c r="B113" t="str">
         <v/>
@@ -4417,13 +4417,13 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>취소 자리 나면 알림 신청</v>
+        <v>금액 요약과 다음 단계</v>
       </c>
       <c r="G113" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 취소 자리 나면 알림 신청이 보이는지 확인한다.</v>
+        <v>'옵션·부속품 고르기'의 금액 요약과 다음 단계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H113" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I113" t="str">
         <v/>
@@ -4437,22 +4437,22 @@
         <v>SCN-010</v>
       </c>
       <c r="B114" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C114" t="str">
-        <v/>
+        <v>대여 불가 - 그 날짜 마감</v>
       </c>
       <c r="D114" t="str">
-        <v/>
+        <v>PD-05</v>
       </c>
       <c r="E114" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F114" t="str">
-        <v>알림은 문자로 온다는 안내</v>
+        <v>고른 기간과 장비 요약</v>
       </c>
       <c r="G114" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 알림은 문자로 온다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 고른 기간과 장비 요약이 보이는지 확인한다.</v>
       </c>
       <c r="H114" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -4481,10 +4481,10 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>대기 순번 표시</v>
+        <v>어느 날짜가 왜 안 되는지 짚어 알림</v>
       </c>
       <c r="G115" t="str">
-        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 대기 순번 표시가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 어느 날짜가 왜 안 되는지 짚어 알림이 보이는지 확인한다.</v>
       </c>
       <c r="H115" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -4498,28 +4498,28 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B116" t="str">
-        <v>장비</v>
+        <v/>
       </c>
       <c r="C116" t="str">
-        <v>세트 패키지</v>
+        <v/>
       </c>
       <c r="D116" t="str">
-        <v>PD-06</v>
+        <v/>
       </c>
       <c r="E116" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F116" t="str">
-        <v>패키지 대표 사진과 이름</v>
+        <v>가장 가까운 빌릴 수 있는 날짜 3개 추천</v>
       </c>
       <c r="G116" t="str">
-        <v>'세트 패키지' 화면에서 패키지 대표 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 가장 가까운 빌릴 수 있는 날짜 3개 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H116" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I116" t="str">
         <v/>
@@ -4530,7 +4530,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B117" t="str">
         <v/>
@@ -4545,13 +4545,13 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>낱개로 빌릴 때와 견준 절약 금액</v>
+        <v>수량을 줄이면 되는지 알림</v>
       </c>
       <c r="G117" t="str">
-        <v>'세트 패키지'의 낱개로 빌릴 때와 견준 절약 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 수량을 줄이면 되는지 알림이 보이는지 확인한다.</v>
       </c>
       <c r="H117" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I117" t="str">
         <v/>
@@ -4562,7 +4562,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B118" t="str">
         <v/>
@@ -4577,13 +4577,13 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>들어 있는 장비 목록과 각각의 낱개 대여료</v>
+        <v>같은 종류 다른 장비 추천 4개</v>
       </c>
       <c r="G118" t="str">
-        <v>'세트 패키지'의 들어 있는 장비 목록과 각각의 낱개 대여료를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 같은 종류 다른 장비 추천 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H118" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I118" t="str">
         <v/>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B119" t="str">
         <v/>
@@ -4609,13 +4609,13 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>구성 바꾸기(빼면 얼마 빠지는지)</v>
+        <v>취소 자리 나면 알림 신청</v>
       </c>
       <c r="G119" t="str">
-        <v>'세트 패키지' 화면에서 구성 바꾸기(빼면 얼마 빠지는지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 취소 자리 나면 알림 신청이 보이는지 확인한다.</v>
       </c>
       <c r="H119" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I119" t="str">
         <v/>
@@ -4626,7 +4626,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B120" t="str">
         <v/>
@@ -4641,13 +4641,13 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>인원수 추천(4인 가족 기준)</v>
+        <v>알림은 문자로 온다는 안내</v>
       </c>
       <c r="G120" t="str">
-        <v>'세트 패키지' 화면에서 인원수 추천(4인 가족 기준)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 알림은 문자로 온다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H120" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I120" t="str">
         <v/>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SCN-011</v>
+        <v>SCN-010</v>
       </c>
       <c r="B121" t="str">
         <v/>
@@ -4673,13 +4673,13 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>패키지 보증금 합계</v>
+        <v>대기 순번 표시</v>
       </c>
       <c r="G121" t="str">
-        <v>'세트 패키지'의 패키지 보증금 합계가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '대여 불가 - 그 날짜 마감' 화면이 나오게 한 뒤, 대기 순번 표시가 보이는지 확인한다.</v>
       </c>
       <c r="H121" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I121" t="str">
         <v/>
@@ -4693,22 +4693,22 @@
         <v>SCN-011</v>
       </c>
       <c r="B122" t="str">
-        <v/>
+        <v>장비</v>
       </c>
       <c r="C122" t="str">
-        <v/>
+        <v>세트 패키지</v>
       </c>
       <c r="D122" t="str">
-        <v/>
+        <v>PD-06</v>
       </c>
       <c r="E122" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F122" t="str">
-        <v>이 기간에 패키지 전부가 되는지 확인</v>
+        <v>패키지 대표 사진과 이름</v>
       </c>
       <c r="G122" t="str">
-        <v>'세트 패키지' 화면에서 이 기간에 패키지 전부가 되는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 패키지 대표 사진과 이름이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H122" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4737,13 +4737,13 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>하나라도 모자라면 어떤 장비가 모자란지 알림</v>
+        <v>낱개로 빌릴 때와 견준 절약 금액</v>
       </c>
       <c r="G123" t="str">
-        <v>'세트 패키지' 화면에서 하나라도 모자라면 어떤 장비가 모자란지 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 낱개로 빌릴 때와 견준 절약 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H123" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I123" t="str">
         <v/>
@@ -4769,13 +4769,13 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>패키지 이용 후기</v>
+        <v>들어 있는 장비 목록과 각각의 낱개 대여료</v>
       </c>
       <c r="G124" t="str">
-        <v>'세트 패키지' 화면에서 패키지 이용 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 들어 있는 장비 목록과 각각의 낱개 대여료를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H124" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I124" t="str">
         <v/>
@@ -4801,10 +4801,10 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>담기와 바로 빌리기</v>
+        <v>구성 바꾸기(빼면 얼마 빠지는지)</v>
       </c>
       <c r="G125" t="str">
-        <v>'세트 패키지' 화면에서 담기와 바로 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 구성 바꾸기(빼면 얼마 빠지는지)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H125" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4818,28 +4818,28 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B126" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C126" t="str">
-        <v>대여 장바구니</v>
+        <v/>
       </c>
       <c r="D126" t="str">
-        <v>CT-01</v>
+        <v/>
       </c>
       <c r="E126" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F126" t="str">
-        <v>담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)</v>
+        <v>인원수 추천(4인 가족 기준)</v>
       </c>
       <c r="G126" t="str">
-        <v>'대여 장바구니'의 담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 인원수 추천(4인 가족 기준)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H126" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I126" t="str">
         <v/>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B127" t="str">
         <v/>
@@ -4865,13 +4865,13 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>줄마다 수량 바꾸기와 삭제</v>
+        <v>패키지 보증금 합계</v>
       </c>
       <c r="G127" t="str">
-        <v>'대여 장바구니' 화면에서 줄마다 수량 바꾸기와 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지'의 패키지 보증금 합계가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H127" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I127" t="str">
         <v/>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B128" t="str">
         <v/>
@@ -4897,10 +4897,10 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>기간이 다른 줄이 섞여 있으면 갈라서 보여주기</v>
+        <v>이 기간에 패키지 전부가 되는지 확인</v>
       </c>
       <c r="G128" t="str">
-        <v>'대여 장바구니' 화면에서 기간이 다른 줄이 섞여 있으면 갈라서 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 이 기간에 패키지 전부가 되는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H128" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4914,7 +4914,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B129" t="str">
         <v/>
@@ -4929,10 +4929,10 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>기간을 한꺼번에 맞추기</v>
+        <v>하나라도 모자라면 어떤 장비가 모자란지 알림</v>
       </c>
       <c r="G129" t="str">
-        <v>'대여 장바구니' 화면에서 기간을 한꺼번에 맞추기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 하나라도 모자라면 어떤 장비가 모자란지 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H129" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B130" t="str">
         <v/>
@@ -4961,13 +4961,13 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>담은 뒤 재고가 빠진 줄에 경고 표시</v>
+        <v>패키지 이용 후기</v>
       </c>
       <c r="G130" t="str">
-        <v>'대여 장바구니'의 담은 뒤 재고가 빠진 줄에 경고 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'세트 패키지' 화면에서 패키지 이용 후기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H130" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I130" t="str">
         <v/>
@@ -4978,7 +4978,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>SCN-012</v>
+        <v>SCN-011</v>
       </c>
       <c r="B131" t="str">
         <v/>
@@ -4993,10 +4993,10 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>쿠폰 고르기와 할인 적용</v>
+        <v>담기와 바로 빌리기</v>
       </c>
       <c r="G131" t="str">
-        <v>'대여 장바구니' 화면에서 쿠폰 고르기와 할인 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'세트 패키지' 화면에서 담기와 바로 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H131" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5013,25 +5013,25 @@
         <v>SCN-012</v>
       </c>
       <c r="B132" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C132" t="str">
-        <v/>
+        <v>대여 장바구니</v>
       </c>
       <c r="D132" t="str">
-        <v/>
+        <v>CT-01</v>
       </c>
       <c r="E132" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F132" t="str">
-        <v>금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)</v>
+        <v>담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)</v>
       </c>
       <c r="G132" t="str">
-        <v>'대여 장바구니'의 금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)이 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 장바구니'의 담은 장비 목록(사진·이름·옵션·기간·수량·대여료·보증금)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H132" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I132" t="str">
         <v/>
@@ -5057,10 +5057,10 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>보증금은 따로 잡힌다는 안내</v>
+        <v>줄마다 수량 바꾸기와 삭제</v>
       </c>
       <c r="G133" t="str">
-        <v>'대여 장바구니' 화면에서 보증금은 따로 잡힌다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 줄마다 수량 바꾸기와 삭제가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H133" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5089,10 +5089,10 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>계속 둘러보기와 신청하기</v>
+        <v>기간이 다른 줄이 섞여 있으면 갈라서 보여주기</v>
       </c>
       <c r="G134" t="str">
-        <v>'대여 장바구니' 화면에서 계속 둘러보기와 신청하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 기간이 다른 줄이 섞여 있으면 갈라서 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H134" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5106,25 +5106,25 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B135" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C135" t="str">
-        <v>기간 한꺼번에 바꾸기</v>
+        <v/>
       </c>
       <c r="D135" t="str">
-        <v>CT-02</v>
+        <v/>
       </c>
       <c r="E135" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F135" t="str">
-        <v>지금 기간과 바꿀 기간 나란히 보기</v>
+        <v>기간을 한꺼번에 맞추기</v>
       </c>
       <c r="G135" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 지금 기간과 바꿀 기간 나란히 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 기간을 한꺼번에 맞추기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H135" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B136" t="str">
         <v/>
@@ -5153,13 +5153,13 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>새 기간 고르는 달력</v>
+        <v>담은 뒤 재고가 빠진 줄에 경고 표시</v>
       </c>
       <c r="G136" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 새 기간 고르는 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니'의 담은 뒤 재고가 빠진 줄에 경고 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H136" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I136" t="str">
         <v/>
@@ -5170,7 +5170,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B137" t="str">
         <v/>
@@ -5185,13 +5185,13 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>담은 장비마다 새 기간에 되는지 하나씩 확인 표시</v>
+        <v>쿠폰 고르기와 할인 적용</v>
       </c>
       <c r="G137" t="str">
-        <v>'기간 한꺼번에 바꾸기'의 담은 장비마다 새 기간에 되는지 하나씩 확인 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 장바구니' 화면에서 쿠폰 고르기와 할인 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H137" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I137" t="str">
         <v/>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B138" t="str">
         <v/>
@@ -5217,13 +5217,13 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>안 되는 장비는 무엇이 언제 막혔는지</v>
+        <v>금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)</v>
       </c>
       <c r="G138" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 장비는 무엇이 언제 막혔는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니'의 금액 요약(대여료 합계·기간 할인·배송비·보증금 합계·지금 낼 금액)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H138" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I138" t="str">
         <v/>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B139" t="str">
         <v/>
@@ -5249,10 +5249,10 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>안 되는 것만 빼고 바꾸기</v>
+        <v>보증금은 따로 잡힌다는 안내</v>
       </c>
       <c r="G139" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 것만 빼고 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 보증금은 따로 잡힌다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H139" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>SCN-013</v>
+        <v>SCN-012</v>
       </c>
       <c r="B140" t="str">
         <v/>
@@ -5281,10 +5281,10 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>기간이 바뀌면 대여료가 얼마나 달라지는지 견주기</v>
+        <v>계속 둘러보기와 신청하기</v>
       </c>
       <c r="G140" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 기간이 바뀌면 대여료가 얼마나 달라지는지 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 장바구니' 화면에서 계속 둘러보기와 신청하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H140" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5301,22 +5301,22 @@
         <v>SCN-013</v>
       </c>
       <c r="B141" t="str">
-        <v/>
+        <v>장바구니</v>
       </c>
       <c r="C141" t="str">
-        <v/>
+        <v>기간 한꺼번에 바꾸기</v>
       </c>
       <c r="D141" t="str">
-        <v/>
+        <v>CT-02</v>
       </c>
       <c r="E141" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F141" t="str">
-        <v>기간 할인 단계가 바뀌면 알림</v>
+        <v>지금 기간과 바꿀 기간 나란히 보기</v>
       </c>
       <c r="G141" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 기간 할인 단계가 바뀌면 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 지금 기간과 바꿀 기간 나란히 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H141" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5345,10 +5345,10 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>되돌리기</v>
+        <v>새 기간 고르는 달력</v>
       </c>
       <c r="G142" t="str">
-        <v>'기간 한꺼번에 바꾸기' 화면에서 되돌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 새 기간 고르는 달력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H142" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5362,28 +5362,28 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B143" t="str">
-        <v>장바구니</v>
+        <v/>
       </c>
       <c r="C143" t="str">
-        <v>빈 장바구니</v>
+        <v/>
       </c>
       <c r="D143" t="str">
-        <v>CT-03</v>
+        <v/>
       </c>
       <c r="E143" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F143" t="str">
-        <v>담은 것이 없다는 안내</v>
+        <v>담은 장비마다 새 기간에 되는지 하나씩 확인 표시</v>
       </c>
       <c r="G143" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 담은 것이 없다는 안내가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기'의 담은 장비마다 새 기간에 되는지 하나씩 확인 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H143" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I143" t="str">
         <v/>
@@ -5394,7 +5394,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B144" t="str">
         <v/>
@@ -5409,13 +5409,13 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>장비 둘러보기 유도</v>
+        <v>안 되는 장비는 무엇이 언제 막혔는지</v>
       </c>
       <c r="G144" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 장비 둘러보기 유도가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 장비는 무엇이 언제 막혔는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H144" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I144" t="str">
         <v/>
@@ -5426,7 +5426,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B145" t="str">
         <v/>
@@ -5441,13 +5441,13 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>최근 본 장비 4개</v>
+        <v>안 되는 것만 빼고 바꾸기</v>
       </c>
       <c r="G145" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 최근 본 장비 4개가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 안 되는 것만 빼고 바꾸기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H145" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I145" t="str">
         <v/>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B146" t="str">
         <v/>
@@ -5473,13 +5473,13 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>찜한 장비 바로가기</v>
+        <v>기간이 바뀌면 대여료가 얼마나 달라지는지 견주기</v>
       </c>
       <c r="G146" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 찜한 장비 바로가기가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 기간이 바뀌면 대여료가 얼마나 달라지는지 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H146" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I146" t="str">
         <v/>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B147" t="str">
         <v/>
@@ -5505,13 +5505,13 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>이번 주말 남은 장비 추천</v>
+        <v>기간 할인 단계가 바뀌면 알림</v>
       </c>
       <c r="G147" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 이번 주말 남은 장비 추천이 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 기간 할인 단계가 바뀌면 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H147" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I147" t="str">
         <v/>
@@ -5522,7 +5522,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>SCN-014</v>
+        <v>SCN-013</v>
       </c>
       <c r="B148" t="str">
         <v/>
@@ -5537,13 +5537,13 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>처음이신가요 3단계 안내 링크</v>
+        <v>되돌리기</v>
       </c>
       <c r="G148" t="str">
-        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 처음이신가요 3단계 안내 링크가 보이는지 확인한다.</v>
+        <v>'기간 한꺼번에 바꾸기' 화면에서 되돌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H148" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I148" t="str">
         <v/>
@@ -5554,28 +5554,28 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B149" t="str">
-        <v>예약·결제</v>
+        <v>장바구니</v>
       </c>
       <c r="C149" t="str">
-        <v>대여 신청서</v>
+        <v>빈 장바구니</v>
       </c>
       <c r="D149" t="str">
-        <v>BK-01</v>
+        <v>CT-03</v>
       </c>
       <c r="E149" t="str">
-        <v>기본</v>
+        <v>예외·상태</v>
       </c>
       <c r="F149" t="str">
-        <v>빌릴 장비와 기간 요약</v>
+        <v>담은 것이 없다는 안내</v>
       </c>
       <c r="G149" t="str">
-        <v>'대여 신청서' 화면에서 빌릴 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 담은 것이 없다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H149" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I149" t="str">
         <v/>
@@ -5586,7 +5586,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B150" t="str">
         <v/>
@@ -5601,13 +5601,13 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>신청자 정보(이름·연락처·이메일)</v>
+        <v>장비 둘러보기 유도</v>
       </c>
       <c r="G150" t="str">
-        <v>'대여 신청서'의 신청자 정보(이름·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 장비 둘러보기 유도가 보이는지 확인한다.</v>
       </c>
       <c r="H150" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I150" t="str">
         <v/>
@@ -5618,7 +5618,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B151" t="str">
         <v/>
@@ -5633,13 +5633,13 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
+        <v>최근 본 장비 4개</v>
       </c>
       <c r="G151" t="str">
-        <v>'대여 신청서' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 최근 본 장비 4개가 보이는지 확인한다.</v>
       </c>
       <c r="H151" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I151" t="str">
         <v/>
@@ -5650,7 +5650,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B152" t="str">
         <v/>
@@ -5665,13 +5665,13 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>방문 수령 시 방문 예정 시각 고르기</v>
+        <v>찜한 장비 바로가기</v>
       </c>
       <c r="G152" t="str">
-        <v>'대여 신청서' 화면에서 방문 수령 시 방문 예정 시각 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 찜한 장비 바로가기가 보이는지 확인한다.</v>
       </c>
       <c r="H152" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I152" t="str">
         <v/>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B153" t="str">
         <v/>
@@ -5697,13 +5697,13 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>택배 시 받는 주소와 회수 주소</v>
+        <v>이번 주말 남은 장비 추천</v>
       </c>
       <c r="G153" t="str">
-        <v>'대여 신청서' 화면에서 택배 시 받는 주소와 회수 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 이번 주말 남은 장비 추천이 보이는지 확인한다.</v>
       </c>
       <c r="H153" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I153" t="str">
         <v/>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>SCN-015</v>
+        <v>SCN-014</v>
       </c>
       <c r="B154" t="str">
         <v/>
@@ -5729,13 +5729,13 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>반납 예정일과 반납 방법 안내</v>
+        <v>처음이신가요 3단계 안내 링크</v>
       </c>
       <c r="G154" t="str">
-        <v>'대여 신청서' 화면에서 반납 예정일과 반납 방법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '빈 장바구니' 화면이 나오게 한 뒤, 처음이신가요 3단계 안내 링크가 보이는지 확인한다.</v>
       </c>
       <c r="H154" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I154" t="str">
         <v/>
@@ -5749,22 +5749,22 @@
         <v>SCN-015</v>
       </c>
       <c r="B155" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C155" t="str">
-        <v/>
+        <v>대여 신청서</v>
       </c>
       <c r="D155" t="str">
-        <v/>
+        <v>BK-01</v>
       </c>
       <c r="E155" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F155" t="str">
-        <v>신분 확인 안내(고가 장비는 신분증 확인)</v>
+        <v>빌릴 장비와 기간 요약</v>
       </c>
       <c r="G155" t="str">
-        <v>'대여 신청서' 화면에서 신분 확인 안내(고가 장비는 신분증 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 빌릴 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H155" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5793,13 +5793,13 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>요청사항</v>
+        <v>신청자 정보(이름·연락처·이메일)</v>
       </c>
       <c r="G156" t="str">
-        <v>'대여 신청서' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서'의 신청자 정보(이름·연락처·이메일)이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H156" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I156" t="str">
         <v/>
@@ -5825,10 +5825,10 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>필수 동의(대여 약관·파손 배상 기준·개인정보)</v>
+        <v>수령 방법 고르기(매장 방문·택배 왕복)</v>
       </c>
       <c r="G157" t="str">
-        <v>'대여 신청서' 화면에서 필수 동의(대여 약관·파손 배상 기준·개인정보)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 수령 방법 고르기(매장 방문·택배 왕복)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H157" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5857,10 +5857,10 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>보증금 안내</v>
+        <v>방문 수령 시 방문 예정 시각 고르기</v>
       </c>
       <c r="G158" t="str">
-        <v>'대여 신청서' 화면에서 보증금 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 방문 수령 시 방문 예정 시각 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H158" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -5889,13 +5889,13 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>금액 요약과 결제로 가기</v>
+        <v>택배 시 받는 주소와 회수 주소</v>
       </c>
       <c r="G159" t="str">
-        <v>'대여 신청서'에서 금액 요약과 결제로 가기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 택배 시 받는 주소와 회수 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H159" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I159" t="str">
         <v/>
@@ -5906,28 +5906,28 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B160" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C160" t="str">
-        <v>보증금·결제</v>
+        <v/>
       </c>
       <c r="D160" t="str">
-        <v>BK-02</v>
+        <v/>
       </c>
       <c r="E160" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F160" t="str">
-        <v>결제 금액과 보증금을 갈라서 보여주기</v>
+        <v>반납 예정일과 반납 방법 안내</v>
       </c>
       <c r="G160" t="str">
-        <v>'보증금·결제'에서 결제 금액과 보증금을 갈라서 보여주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 반납 예정일과 반납 방법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H160" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I160" t="str">
         <v/>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B161" t="str">
         <v/>
@@ -5953,13 +5953,13 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>결제 수단 고르기(카드·간편결제·계좌이체)</v>
+        <v>신분 확인 안내(고가 장비는 신분증 확인)</v>
       </c>
       <c r="G161" t="str">
-        <v>'보증금·결제'에서 결제 수단 고르기(카드·간편결제·계좌이체)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 신청서' 화면에서 신분 확인 안내(고가 장비는 신분증 확인)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H161" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I161" t="str">
         <v/>
@@ -5970,7 +5970,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B162" t="str">
         <v/>
@@ -5985,10 +5985,10 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)</v>
+        <v>요청사항</v>
       </c>
       <c r="G162" t="str">
-        <v>'보증금·결제' 화면에서 보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 요청사항이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H162" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B163" t="str">
         <v/>
@@ -6017,13 +6017,13 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>카드 보류가 무엇인지 설명</v>
+        <v>필수 동의(대여 약관·파손 배상 기준·개인정보)</v>
       </c>
       <c r="G163" t="str">
-        <v>'보증금·결제'의 카드 보류가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 필수 동의(대여 약관·파손 배상 기준·개인정보)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H163" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I163" t="str">
         <v/>
@@ -6034,7 +6034,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B164" t="str">
         <v/>
@@ -6049,10 +6049,10 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>보증금 면제 조건 안내</v>
+        <v>보증금 안내</v>
       </c>
       <c r="G164" t="str">
-        <v>'보증금·결제' 화면에서 보증금 면제 조건 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서' 화면에서 보증금 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H164" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6066,7 +6066,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>SCN-016</v>
+        <v>SCN-015</v>
       </c>
       <c r="B165" t="str">
         <v/>
@@ -6081,13 +6081,13 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>언제 얼마가 빠지는지 시각 순서로</v>
+        <v>금액 요약과 결제로 가기</v>
       </c>
       <c r="G165" t="str">
-        <v>'보증금·결제' 화면에서 언제 얼마가 빠지는지 시각 순서로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 신청서'에서 금액 요약과 결제로 가기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H165" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I165" t="str">
         <v/>
@@ -6101,25 +6101,25 @@
         <v>SCN-016</v>
       </c>
       <c r="B166" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C166" t="str">
-        <v/>
+        <v>보증금·결제</v>
       </c>
       <c r="D166" t="str">
-        <v/>
+        <v>BK-02</v>
       </c>
       <c r="E166" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F166" t="str">
-        <v>현금영수증</v>
+        <v>결제 금액과 보증금을 갈라서 보여주기</v>
       </c>
       <c r="G166" t="str">
-        <v>'보증금·결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 금액과 보증금을 갈라서 보여주기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H166" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I166" t="str">
         <v/>
@@ -6145,13 +6145,13 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>세금계산서</v>
+        <v>결제 수단 고르기(카드·간편결제·계좌이체)</v>
       </c>
       <c r="G167" t="str">
-        <v>'보증금·결제' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 수단 고르기(카드·간편결제·계좌이체)를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H167" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I167" t="str">
         <v/>
@@ -6177,10 +6177,10 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>최종 확인 체크</v>
+        <v>보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)</v>
       </c>
       <c r="G168" t="str">
-        <v>'보증금·결제' 화면에서 최종 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 보증금 잡는 방식 고르기(카드 한도 보류·실제 결제 후 환불)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H168" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6209,13 +6209,13 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>결제 실행</v>
+        <v>카드 보류가 무엇인지 설명</v>
       </c>
       <c r="G169" t="str">
-        <v>'보증금·결제'에서 결제 실행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'보증금·결제'의 카드 보류가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H169" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I169" t="str">
         <v/>
@@ -6226,25 +6226,25 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B170" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C170" t="str">
-        <v>대여 확정 완료</v>
+        <v/>
       </c>
       <c r="D170" t="str">
-        <v>BK-03</v>
+        <v/>
       </c>
       <c r="E170" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F170" t="str">
-        <v>확정 안내와 대여번호</v>
+        <v>보증금 면제 조건 안내</v>
       </c>
       <c r="G170" t="str">
-        <v>'대여 확정 완료' 화면에서 확정 안내와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 보증금 면제 조건 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H170" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6258,7 +6258,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B171" t="str">
         <v/>
@@ -6273,10 +6273,10 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>빌린 장비와 기간 요약</v>
+        <v>언제 얼마가 빠지는지 시각 순서로</v>
       </c>
       <c r="G171" t="str">
-        <v>'대여 확정 완료' 화면에서 빌린 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 언제 얼마가 빠지는지 시각 순서로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H171" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B172" t="str">
         <v/>
@@ -6305,10 +6305,10 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>수령 방법별 다음 할 일 안내</v>
+        <v>현금영수증</v>
       </c>
       <c r="G172" t="str">
-        <v>'대여 확정 완료' 화면에서 수령 방법별 다음 할 일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 현금영수증이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H172" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6322,7 +6322,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B173" t="str">
         <v/>
@@ -6337,10 +6337,10 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>매장 방문이면 주소</v>
+        <v>세금계산서</v>
       </c>
       <c r="G173" t="str">
-        <v>'대여 확정 완료' 화면에서 매장 방문이면 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 세금계산서가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H173" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6354,7 +6354,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B174" t="str">
         <v/>
@@ -6369,10 +6369,10 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>시각</v>
+        <v>최종 확인 체크</v>
       </c>
       <c r="G174" t="str">
-        <v>'대여 확정 완료' 화면에서 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제' 화면에서 최종 확인 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H174" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6386,7 +6386,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SCN-017</v>
+        <v>SCN-016</v>
       </c>
       <c r="B175" t="str">
         <v/>
@@ -6401,13 +6401,13 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>QR</v>
+        <v>결제 실행</v>
       </c>
       <c r="G175" t="str">
-        <v>'대여 확정 완료' 화면에서 QR이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금·결제'에서 결제 실행을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H175" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I175" t="str">
         <v/>
@@ -6421,22 +6421,22 @@
         <v>SCN-017</v>
       </c>
       <c r="B176" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C176" t="str">
-        <v/>
+        <v>대여 확정 완료</v>
       </c>
       <c r="D176" t="str">
-        <v/>
+        <v>BK-03</v>
       </c>
       <c r="E176" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F176" t="str">
-        <v>택배면 발송 예정일과 송장 안내</v>
+        <v>확정 안내와 대여번호</v>
       </c>
       <c r="G176" t="str">
-        <v>'대여 확정 완료' 화면에서 택배면 발송 예정일과 송장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 확정 안내와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H176" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6465,10 +6465,10 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>반납 예정일 강조와 캘린더에 넣기</v>
+        <v>빌린 장비와 기간 요약</v>
       </c>
       <c r="G177" t="str">
-        <v>'대여 확정 완료' 화면에서 반납 예정일 강조와 캘린더에 넣기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 빌린 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H177" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6497,13 +6497,13 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>결제 금액과 보증금 상태</v>
+        <v>수령 방법별 다음 할 일 안내</v>
       </c>
       <c r="G178" t="str">
-        <v>'대여 확정 완료'에서 결제 금액과 보증금 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 확정 완료' 화면에서 수령 방법별 다음 할 일 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H178" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I178" t="str">
         <v/>
@@ -6529,10 +6529,10 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>수령 전 준비물(신분증)</v>
+        <v>매장 방문이면 주소</v>
       </c>
       <c r="G179" t="str">
-        <v>'대여 확정 완료' 화면에서 수령 전 준비물(신분증)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 매장 방문이면 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H179" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6561,10 +6561,10 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>대여 내역으로 가기</v>
+        <v>시각</v>
       </c>
       <c r="G180" t="str">
-        <v>'대여 확정 완료' 화면에서 대여 내역으로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H180" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6593,10 +6593,10 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>카톡 알림 받기 신청</v>
+        <v>QR</v>
       </c>
       <c r="G181" t="str">
-        <v>'대여 확정 완료' 화면에서 카톡 알림 받기 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 확정 완료' 화면에서 QR이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H181" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -6610,28 +6610,28 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B182" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C182" t="str">
-        <v>결제 실패</v>
+        <v/>
       </c>
       <c r="D182" t="str">
-        <v>BK-04</v>
+        <v/>
       </c>
       <c r="E182" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F182" t="str">
-        <v>실패 안내와 무엇 때문인지</v>
+        <v>택배면 발송 예정일과 송장 안내</v>
       </c>
       <c r="G182" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 안내와 무엇 때문인지가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 택배면 발송 예정일과 송장 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H182" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I182" t="str">
         <v/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B183" t="str">
         <v/>
@@ -6657,13 +6657,13 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)</v>
+        <v>반납 예정일 강조와 캘린더에 넣기</v>
       </c>
       <c r="G183" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)이 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 반납 예정일 강조와 캘린더에 넣기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H183" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I183" t="str">
         <v/>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B184" t="str">
         <v/>
@@ -6689,13 +6689,13 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>보증금 때문에 한도가 모자란 경우 따로 안내</v>
+        <v>결제 금액과 보증금 상태</v>
       </c>
       <c r="G184" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 때문에 한도가 모자란 경우 따로 안내가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료'에서 결제 금액과 보증금 상태를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H184" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I184" t="str">
         <v/>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B185" t="str">
         <v/>
@@ -6721,13 +6721,13 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>장비는 아직 잡혀 있다는 것과 언제까지인지</v>
+        <v>수령 전 준비물(신분증)</v>
       </c>
       <c r="G185" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 장비는 아직 잡혀 있다는 것과 언제까지인지가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 수령 전 준비물(신분증)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H185" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I185" t="str">
         <v/>
@@ -6738,7 +6738,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B186" t="str">
         <v/>
@@ -6753,13 +6753,13 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>다시 시도하기</v>
+        <v>대여 내역으로 가기</v>
       </c>
       <c r="G186" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 대여 내역으로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H186" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I186" t="str">
         <v/>
@@ -6770,7 +6770,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>SCN-018</v>
+        <v>SCN-017</v>
       </c>
       <c r="B187" t="str">
         <v/>
@@ -6785,13 +6785,13 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>다른 결제 수단으로</v>
+        <v>카톡 알림 받기 신청</v>
       </c>
       <c r="G187" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단으로가 보이는지 확인한다.</v>
+        <v>'대여 확정 완료' 화면에서 카톡 알림 받기 신청이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H187" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I187" t="str">
         <v/>
@@ -6805,22 +6805,22 @@
         <v>SCN-018</v>
       </c>
       <c r="B188" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C188" t="str">
-        <v/>
+        <v>결제 실패</v>
       </c>
       <c r="D188" t="str">
-        <v/>
+        <v>BK-04</v>
       </c>
       <c r="E188" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F188" t="str">
-        <v>보증금 방식 바꾸기</v>
+        <v>실패 안내와 무엇 때문인지</v>
       </c>
       <c r="G188" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 방식 바꾸기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 실패 안내와 무엇 때문인지가 보이는지 확인한다.</v>
       </c>
       <c r="H188" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6849,10 +6849,10 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>고객센터 안내</v>
+        <v>흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)</v>
       </c>
       <c r="G189" t="str">
-        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 흔한 까닭 목록(한도 초과·보증금 한도 부족·카드사 거절)이 보이는지 확인한다.</v>
       </c>
       <c r="H189" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -6866,28 +6866,28 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B190" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C190" t="str">
-        <v>대여 계약 동의·서명</v>
+        <v/>
       </c>
       <c r="D190" t="str">
-        <v>BK-05</v>
+        <v/>
       </c>
       <c r="E190" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F190" t="str">
-        <v>대여 계약 요약(빌리는 것·기간·금액·보증금)</v>
+        <v>보증금 때문에 한도가 모자란 경우 따로 안내</v>
       </c>
       <c r="G190" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 대여 계약 요약(빌리는 것·기간·금액·보증금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 때문에 한도가 모자란 경우 따로 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H190" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I190" t="str">
         <v/>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B191" t="str">
         <v/>
@@ -6913,13 +6913,13 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>조항별 펼쳐보기</v>
+        <v>장비는 아직 잡혀 있다는 것과 언제까지인지</v>
       </c>
       <c r="G191" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 조항별 펼쳐보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 장비는 아직 잡혀 있다는 것과 언제까지인지가 보이는지 확인한다.</v>
       </c>
       <c r="H191" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I191" t="str">
         <v/>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B192" t="str">
         <v/>
@@ -6945,13 +6945,13 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>파손</v>
+        <v>다시 시도하기</v>
       </c>
       <c r="G192" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다시 시도하기가 보이는지 확인한다.</v>
       </c>
       <c r="H192" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I192" t="str">
         <v/>
@@ -6962,7 +6962,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B193" t="str">
         <v/>
@@ -6977,13 +6977,13 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>분실 시 배상 기준 요약표</v>
+        <v>다른 결제 수단으로</v>
       </c>
       <c r="G193" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 분실 시 배상 기준 요약표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 다른 결제 수단으로가 보이는지 확인한다.</v>
       </c>
       <c r="H193" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I193" t="str">
         <v/>
@@ -6994,7 +6994,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B194" t="str">
         <v/>
@@ -7009,13 +7009,13 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>연체료 계산 방식</v>
+        <v>보증금 방식 바꾸기</v>
       </c>
       <c r="G194" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 연체료 계산 방식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 보증금 방식 바꾸기가 보이는지 확인한다.</v>
       </c>
       <c r="H194" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I194" t="str">
         <v/>
@@ -7026,7 +7026,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>SCN-019</v>
+        <v>SCN-018</v>
       </c>
       <c r="B195" t="str">
         <v/>
@@ -7041,13 +7041,13 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>반납 상태 기준(세척·건조)</v>
+        <v>고객센터 안내</v>
       </c>
       <c r="G195" t="str">
-        <v>'대여 계약 동의·서명'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '결제 실패' 화면이 나오게 한 뒤, 고객센터 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H195" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I195" t="str">
         <v/>
@@ -7061,25 +7061,25 @@
         <v>SCN-019</v>
       </c>
       <c r="B196" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C196" t="str">
-        <v/>
+        <v>대여 계약 동의·서명</v>
       </c>
       <c r="D196" t="str">
-        <v/>
+        <v>BK-05</v>
       </c>
       <c r="E196" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F196" t="str">
-        <v>개인정보 이용 범위</v>
+        <v>대여 계약 요약(빌리는 것·기간·금액·보증금)</v>
       </c>
       <c r="G196" t="str">
-        <v>'대여 계약 동의·서명'의 개인정보 이용 범위가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 대여 계약 요약(빌리는 것·기간·금액·보증금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H196" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I196" t="str">
         <v/>
@@ -7105,10 +7105,10 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>필수와 선택 동의 갈라 두기</v>
+        <v>조항별 펼쳐보기</v>
       </c>
       <c r="G197" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 필수와 선택 동의 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 조항별 펼쳐보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H197" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7137,10 +7137,10 @@
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>전자 서명 칸</v>
+        <v>파손</v>
       </c>
       <c r="G198" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 전자 서명 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H198" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7169,10 +7169,10 @@
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>계약서 사본 받기(이메일·다운로드)</v>
+        <v>분실 시 배상 기준 요약표</v>
       </c>
       <c r="G199" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 계약서 사본 받기(이메일·다운로드)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 분실 시 배상 기준 요약표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H199" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7201,10 +7201,10 @@
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>동의 없이는 수령 불가 안내</v>
+        <v>연체료 계산 방식</v>
       </c>
       <c r="G200" t="str">
-        <v>'대여 계약 동의·서명' 화면에서 동의 없이는 수령 불가 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 연체료 계산 방식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H200" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7218,28 +7218,28 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B201" t="str">
-        <v>예약·결제</v>
+        <v/>
       </c>
       <c r="C201" t="str">
-        <v>대여 기간 연장</v>
+        <v/>
       </c>
       <c r="D201" t="str">
-        <v>BK-06</v>
+        <v/>
       </c>
       <c r="E201" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F201" t="str">
-        <v>지금 빌린 장비와 반납 예정일</v>
+        <v>반납 상태 기준(세척·건조)</v>
       </c>
       <c r="G201" t="str">
-        <v>'대여 기간 연장' 화면에서 지금 빌린 장비와 반납 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H201" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I201" t="str">
         <v/>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B202" t="str">
         <v/>
@@ -7265,13 +7265,13 @@
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>얼마나 더 쓸지 고르기</v>
+        <v>개인정보 이용 범위</v>
       </c>
       <c r="G202" t="str">
-        <v>'대여 기간 연장' 화면에서 얼마나 더 쓸지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명'의 개인정보 이용 범위가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H202" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I202" t="str">
         <v/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B203" t="str">
         <v/>
@@ -7297,10 +7297,10 @@
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>연장할 기간에 그 장비가 비어 있는지 확인</v>
+        <v>필수와 선택 동의 갈라 두기</v>
       </c>
       <c r="G203" t="str">
-        <v>'대여 기간 연장' 화면에서 연장할 기간에 그 장비가 비어 있는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 필수와 선택 동의 갈라 두기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H203" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7314,7 +7314,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B204" t="str">
         <v/>
@@ -7329,10 +7329,10 @@
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>다음 예약이 있으면 언제까지만 연장되는지</v>
+        <v>전자 서명 칸</v>
       </c>
       <c r="G204" t="str">
-        <v>'대여 기간 연장' 화면에서 다음 예약이 있으면 언제까지만 연장되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 전자 서명 칸이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H204" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B205" t="str">
         <v/>
@@ -7361,10 +7361,10 @@
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>추가 대여료 계산과 기간 할인 다시 적용</v>
+        <v>계약서 사본 받기(이메일·다운로드)</v>
       </c>
       <c r="G205" t="str">
-        <v>'대여 기간 연장' 화면에서 추가 대여료 계산과 기간 할인 다시 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 계약서 사본 받기(이메일·다운로드)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H205" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7378,7 +7378,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>SCN-020</v>
+        <v>SCN-019</v>
       </c>
       <c r="B206" t="str">
         <v/>
@@ -7393,10 +7393,10 @@
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>보증금은 그대로 유지된다는 안내</v>
+        <v>동의 없이는 수령 불가 안내</v>
       </c>
       <c r="G206" t="str">
-        <v>'대여 기간 연장' 화면에서 보증금은 그대로 유지된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 계약 동의·서명' 화면에서 동의 없이는 수령 불가 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H206" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7413,22 +7413,22 @@
         <v>SCN-020</v>
       </c>
       <c r="B207" t="str">
-        <v/>
+        <v>예약·결제</v>
       </c>
       <c r="C207" t="str">
-        <v/>
+        <v>대여 기간 연장</v>
       </c>
       <c r="D207" t="str">
-        <v/>
+        <v>BK-06</v>
       </c>
       <c r="E207" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F207" t="str">
-        <v>연장은 반납일 전에만 된다는 안내</v>
+        <v>지금 빌린 장비와 반납 예정일</v>
       </c>
       <c r="G207" t="str">
-        <v>'대여 기간 연장' 화면에서 연장은 반납일 전에만 된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 지금 빌린 장비와 반납 예정일이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H207" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7457,13 +7457,13 @@
         <v/>
       </c>
       <c r="F208" t="str">
-        <v>연체 중이면 연장 대신 연체 정산으로 안내</v>
+        <v>얼마나 더 쓸지 고르기</v>
       </c>
       <c r="G208" t="str">
-        <v>'대여 기간 연장'에서 연체 중이면 연장 대신 연체 정산으로 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 기간 연장' 화면에서 얼마나 더 쓸지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H208" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I208" t="str">
         <v/>
@@ -7489,13 +7489,13 @@
         <v/>
       </c>
       <c r="F209" t="str">
-        <v>연장 결제</v>
+        <v>연장할 기간에 그 장비가 비어 있는지 확인</v>
       </c>
       <c r="G209" t="str">
-        <v>'대여 기간 연장'에서 연장 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 기간 연장' 화면에서 연장할 기간에 그 장비가 비어 있는지 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H209" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I209" t="str">
         <v/>
@@ -7506,25 +7506,25 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B210" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C210" t="str">
-        <v>수령 확인</v>
+        <v/>
       </c>
       <c r="D210" t="str">
-        <v>RT-01</v>
+        <v/>
       </c>
       <c r="E210" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F210" t="str">
-        <v>수령 QR 코드와 대여번호</v>
+        <v>다음 예약이 있으면 언제까지만 연장되는지</v>
       </c>
       <c r="G210" t="str">
-        <v>'수령 확인' 화면에서 수령 QR 코드와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 다음 예약이 있으면 언제까지만 연장되는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H210" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7538,7 +7538,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B211" t="str">
         <v/>
@@ -7553,13 +7553,13 @@
         <v/>
       </c>
       <c r="F211" t="str">
-        <v>받을 장비와 구성품 목록</v>
+        <v>추가 대여료 계산과 기간 할인 다시 적용</v>
       </c>
       <c r="G211" t="str">
-        <v>'수령 확인'의 받을 장비와 구성품 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 추가 대여료 계산과 기간 할인 다시 적용이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H211" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I211" t="str">
         <v/>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B212" t="str">
         <v/>
@@ -7585,10 +7585,10 @@
         <v/>
       </c>
       <c r="F212" t="str">
-        <v>구성품 하나씩 체크하며 확인</v>
+        <v>보증금은 그대로 유지된다는 안내</v>
       </c>
       <c r="G212" t="str">
-        <v>'수령 확인' 화면에서 구성품 하나씩 체크하며 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장' 화면에서 보증금은 그대로 유지된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H212" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B213" t="str">
         <v/>
@@ -7617,13 +7617,13 @@
         <v/>
       </c>
       <c r="F213" t="str">
-        <v>받을 때 상태 사진 찍어 올리기</v>
+        <v>연장은 반납일 전에만 된다는 안내</v>
       </c>
       <c r="G213" t="str">
-        <v>'수령 확인'의 받을 때 상태 사진 찍어 올리기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 기간 연장' 화면에서 연장은 반납일 전에만 된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H213" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I213" t="str">
         <v/>
@@ -7634,7 +7634,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B214" t="str">
         <v/>
@@ -7649,13 +7649,13 @@
         <v/>
       </c>
       <c r="F214" t="str">
-        <v>이미 있던 흠집 표시하기</v>
+        <v>연체 중이면 연장 대신 연체 정산으로 안내</v>
       </c>
       <c r="G214" t="str">
-        <v>'수령 확인'의 이미 있던 흠집 표시하기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 기간 연장'에서 연체 중이면 연장 대신 연체 정산으로 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H214" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I214" t="str">
         <v/>
@@ -7666,7 +7666,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>SCN-021</v>
+        <v>SCN-020</v>
       </c>
       <c r="B215" t="str">
         <v/>
@@ -7681,13 +7681,13 @@
         <v/>
       </c>
       <c r="F215" t="str">
-        <v>신분증 확인 안내</v>
+        <v>연장 결제</v>
       </c>
       <c r="G215" t="str">
-        <v>'수령 확인' 화면에서 신분증 확인 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 기간 연장'에서 연장 결제를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H215" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I215" t="str">
         <v/>
@@ -7701,22 +7701,22 @@
         <v>SCN-021</v>
       </c>
       <c r="B216" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C216" t="str">
-        <v/>
+        <v>수령 확인</v>
       </c>
       <c r="D216" t="str">
-        <v/>
+        <v>RT-01</v>
       </c>
       <c r="E216" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F216" t="str">
-        <v>반납 예정일 다시 알림</v>
+        <v>수령 QR 코드와 대여번호</v>
       </c>
       <c r="G216" t="str">
-        <v>'수령 확인' 화면에서 반납 예정일 다시 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'수령 확인' 화면에서 수령 QR 코드와 대여번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H216" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7745,13 +7745,13 @@
         <v/>
       </c>
       <c r="F217" t="str">
-        <v>사용법 간단 안내 링크</v>
+        <v>받을 장비와 구성품 목록</v>
       </c>
       <c r="G217" t="str">
-        <v>'수령 확인'에서 사용법 간단 안내 링크를 눌러 본다.</v>
+        <v>'수령 확인'의 받을 장비와 구성품 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H217" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I217" t="str">
         <v/>
@@ -7777,10 +7777,10 @@
         <v/>
       </c>
       <c r="F218" t="str">
-        <v>수령 확인 완료</v>
+        <v>구성품 하나씩 체크하며 확인</v>
       </c>
       <c r="G218" t="str">
-        <v>'수령 확인' 화면에서 수령 확인 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'수령 확인' 화면에서 구성품 하나씩 체크하며 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H218" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -7809,13 +7809,13 @@
         <v/>
       </c>
       <c r="F219" t="str">
-        <v>확인해야 보증금 규정이 시작된다는 안내</v>
+        <v>받을 때 상태 사진 찍어 올리기</v>
       </c>
       <c r="G219" t="str">
-        <v>'수령 확인' 화면에서 확인해야 보증금 규정이 시작된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'수령 확인'의 받을 때 상태 사진 찍어 올리기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H219" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I219" t="str">
         <v/>
@@ -7826,28 +7826,28 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B220" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C220" t="str">
-        <v>이용 중</v>
+        <v/>
       </c>
       <c r="D220" t="str">
-        <v>RT-02</v>
+        <v/>
       </c>
       <c r="E220" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F220" t="str">
-        <v>빌린 장비와 남은 시간 카운트</v>
+        <v>이미 있던 흠집 표시하기</v>
       </c>
       <c r="G220" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 빌린 장비와 남은 시간 카운트가 보이는지 확인한다.</v>
+        <v>'수령 확인'의 이미 있던 흠집 표시하기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H220" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I220" t="str">
         <v/>
@@ -7858,7 +7858,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B221" t="str">
         <v/>
@@ -7873,13 +7873,13 @@
         <v/>
       </c>
       <c r="F221" t="str">
-        <v>반납 예정일까지 남은 시간을 크게</v>
+        <v>신분증 확인 안내</v>
       </c>
       <c r="G221" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 예정일까지 남은 시간을 크게가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 신분증 확인 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H221" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I221" t="str">
         <v/>
@@ -7890,7 +7890,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B222" t="str">
         <v/>
@@ -7905,13 +7905,13 @@
         <v/>
       </c>
       <c r="F222" t="str">
-        <v>반납 방법 미리 안내(매장·택배)</v>
+        <v>반납 예정일 다시 알림</v>
       </c>
       <c r="G222" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 방법 미리 안내(매장·택배)가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 반납 예정일 다시 알림이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H222" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I222" t="str">
         <v/>
@@ -7922,7 +7922,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B223" t="str">
         <v/>
@@ -7937,13 +7937,13 @@
         <v/>
       </c>
       <c r="F223" t="str">
-        <v>반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)</v>
+        <v>사용법 간단 안내 링크</v>
       </c>
       <c r="G223" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)이 보이는지 확인한다.</v>
+        <v>'수령 확인'에서 사용법 간단 안내 링크를 눌러 본다.</v>
       </c>
       <c r="H223" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I223" t="str">
         <v/>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B224" t="str">
         <v/>
@@ -7969,13 +7969,13 @@
         <v/>
       </c>
       <c r="F224" t="str">
-        <v>사용 중 문제 신고</v>
+        <v>수령 확인 완료</v>
       </c>
       <c r="G224" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용 중 문제 신고가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 수령 확인 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H224" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I224" t="str">
         <v/>
@@ -7986,7 +7986,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>SCN-022</v>
+        <v>SCN-021</v>
       </c>
       <c r="B225" t="str">
         <v/>
@@ -8001,13 +8001,13 @@
         <v/>
       </c>
       <c r="F225" t="str">
-        <v>기간 연장하기</v>
+        <v>확인해야 보증금 규정이 시작된다는 안내</v>
       </c>
       <c r="G225" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 기간 연장하기가 보이는지 확인한다.</v>
+        <v>'수령 확인' 화면에서 확인해야 보증금 규정이 시작된다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H225" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I225" t="str">
         <v/>
@@ -8021,22 +8021,22 @@
         <v>SCN-022</v>
       </c>
       <c r="B226" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C226" t="str">
-        <v/>
+        <v>이용 중</v>
       </c>
       <c r="D226" t="str">
-        <v/>
+        <v>RT-02</v>
       </c>
       <c r="E226" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F226" t="str">
-        <v>파손 미리 알리기</v>
+        <v>빌린 장비와 남은 시간 카운트</v>
       </c>
       <c r="G226" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 파손 미리 알리기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 빌린 장비와 남은 시간 카운트가 보이는지 확인한다.</v>
       </c>
       <c r="H226" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8065,10 +8065,10 @@
         <v/>
       </c>
       <c r="F227" t="str">
-        <v>사용법과 주의사항 다시 보기</v>
+        <v>반납 예정일까지 남은 시간을 크게</v>
       </c>
       <c r="G227" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용법과 주의사항 다시 보기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 예정일까지 남은 시간을 크게가 보이는지 확인한다.</v>
       </c>
       <c r="H227" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8097,10 +8097,10 @@
         <v/>
       </c>
       <c r="F228" t="str">
-        <v>반납 알림 설정</v>
+        <v>반납 방법 미리 안내(매장·택배)</v>
       </c>
       <c r="G228" t="str">
-        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 알림 설정이 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 방법 미리 안내(매장·택배)가 보이는지 확인한다.</v>
       </c>
       <c r="H228" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -8114,28 +8114,28 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B229" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C229" t="str">
-        <v>반납 안내</v>
+        <v/>
       </c>
       <c r="D229" t="str">
-        <v>RT-03</v>
+        <v/>
       </c>
       <c r="E229" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F229" t="str">
-        <v>반납 기한과 남은 시간</v>
+        <v>반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)</v>
       </c>
       <c r="G229" t="str">
-        <v>'반납 안내'의 반납 기한과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 전 해야 할 일 체크리스트(세척·건조·구성품 확인)이 보이는지 확인한다.</v>
       </c>
       <c r="H229" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I229" t="str">
         <v/>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B230" t="str">
         <v/>
@@ -8161,13 +8161,13 @@
         <v/>
       </c>
       <c r="F230" t="str">
-        <v>반납 방법 고르기(매장 방문·택배 회수)</v>
+        <v>사용 중 문제 신고</v>
       </c>
       <c r="G230" t="str">
-        <v>'반납 안내' 화면에서 반납 방법 고르기(매장 방문·택배 회수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용 중 문제 신고가 보이는지 확인한다.</v>
       </c>
       <c r="H230" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I230" t="str">
         <v/>
@@ -8178,7 +8178,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B231" t="str">
         <v/>
@@ -8193,13 +8193,13 @@
         <v/>
       </c>
       <c r="F231" t="str">
-        <v>매장 반납 시 주소</v>
+        <v>기간 연장하기</v>
       </c>
       <c r="G231" t="str">
-        <v>'반납 안내' 화면에서 매장 반납 시 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 기간 연장하기가 보이는지 확인한다.</v>
       </c>
       <c r="H231" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I231" t="str">
         <v/>
@@ -8210,7 +8210,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B232" t="str">
         <v/>
@@ -8225,13 +8225,13 @@
         <v/>
       </c>
       <c r="F232" t="str">
-        <v>운영시간</v>
+        <v>파손 미리 알리기</v>
       </c>
       <c r="G232" t="str">
-        <v>'반납 안내' 화면에서 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 파손 미리 알리기가 보이는지 확인한다.</v>
       </c>
       <c r="H232" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I232" t="str">
         <v/>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B233" t="str">
         <v/>
@@ -8257,13 +8257,13 @@
         <v/>
       </c>
       <c r="F233" t="str">
-        <v>지도</v>
+        <v>사용법과 주의사항 다시 보기</v>
       </c>
       <c r="G233" t="str">
-        <v>'반납 안내' 화면에서 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 사용법과 주의사항 다시 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H233" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I233" t="str">
         <v/>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>SCN-023</v>
+        <v>SCN-022</v>
       </c>
       <c r="B234" t="str">
         <v/>
@@ -8289,13 +8289,13 @@
         <v/>
       </c>
       <c r="F234" t="str">
-        <v>주차 안내</v>
+        <v>반납 알림 설정</v>
       </c>
       <c r="G234" t="str">
-        <v>'반납 안내' 화면에서 주차 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '이용 중' 화면이 나오게 한 뒤, 반납 알림 설정이 보이는지 확인한다.</v>
       </c>
       <c r="H234" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I234" t="str">
         <v/>
@@ -8309,25 +8309,25 @@
         <v>SCN-023</v>
       </c>
       <c r="B235" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C235" t="str">
-        <v/>
+        <v>반납 안내</v>
       </c>
       <c r="D235" t="str">
-        <v/>
+        <v>RT-03</v>
       </c>
       <c r="E235" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F235" t="str">
-        <v>택배 회수 신청과 방문 예정 시각</v>
+        <v>반납 기한과 남은 시간</v>
       </c>
       <c r="G235" t="str">
-        <v>'반납 안내' 화면에서 택배 회수 신청과 방문 예정 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내'의 반납 기한과 남은 시간이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H235" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I235" t="str">
         <v/>
@@ -8353,13 +8353,13 @@
         <v/>
       </c>
       <c r="F236" t="str">
-        <v>반납 전 준비 체크리스트</v>
+        <v>반납 방법 고르기(매장 방문·택배 회수)</v>
       </c>
       <c r="G236" t="str">
-        <v>'반납 안내'의 반납 전 준비 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 반납 방법 고르기(매장 방문·택배 회수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H236" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I236" t="str">
         <v/>
@@ -8385,13 +8385,13 @@
         <v/>
       </c>
       <c r="F237" t="str">
-        <v>이 상태로 반납하면 안 되는 예시 사진</v>
+        <v>매장 반납 시 주소</v>
       </c>
       <c r="G237" t="str">
-        <v>'반납 안내'의 이 상태로 반납하면 안 되는 예시 사진이 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 안내' 화면에서 매장 반납 시 주소가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H237" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I237" t="str">
         <v/>
@@ -8417,10 +8417,10 @@
         <v/>
       </c>
       <c r="F238" t="str">
-        <v>늦으면 얼마가 붙는지 표</v>
+        <v>운영시간</v>
       </c>
       <c r="G238" t="str">
-        <v>'반납 안내' 화면에서 늦으면 얼마가 붙는지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 운영시간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H238" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8449,10 +8449,10 @@
         <v/>
       </c>
       <c r="F239" t="str">
-        <v>구성품 빠지면 얼마인지 표</v>
+        <v>지도</v>
       </c>
       <c r="G239" t="str">
-        <v>'반납 안내' 화면에서 구성품 빠지면 얼마인지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 지도가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H239" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8481,10 +8481,10 @@
         <v/>
       </c>
       <c r="F240" t="str">
-        <v>반납 접수로 가기</v>
+        <v>주차 안내</v>
       </c>
       <c r="G240" t="str">
-        <v>'반납 안내' 화면에서 반납 접수로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 주차 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H240" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8498,25 +8498,25 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B241" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C241" t="str">
-        <v>반납 접수</v>
+        <v/>
       </c>
       <c r="D241" t="str">
-        <v>RT-04</v>
+        <v/>
       </c>
       <c r="E241" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F241" t="str">
-        <v>반납할 장비와 기간 요약</v>
+        <v>택배 회수 신청과 방문 예정 시각</v>
       </c>
       <c r="G241" t="str">
-        <v>'반납 접수' 화면에서 반납할 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 택배 회수 신청과 방문 예정 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H241" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B242" t="str">
         <v/>
@@ -8545,13 +8545,13 @@
         <v/>
       </c>
       <c r="F242" t="str">
-        <v>구성품 다 챙겼는지 하나씩 체크</v>
+        <v>반납 전 준비 체크리스트</v>
       </c>
       <c r="G242" t="str">
-        <v>'반납 접수' 화면에서 구성품 다 챙겼는지 하나씩 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내'의 반납 전 준비 체크리스트를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H242" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I242" t="str">
         <v/>
@@ -8562,7 +8562,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B243" t="str">
         <v/>
@@ -8577,10 +8577,10 @@
         <v/>
       </c>
       <c r="F243" t="str">
-        <v>반납 상태 사진 올리기</v>
+        <v>이 상태로 반납하면 안 되는 예시 사진</v>
       </c>
       <c r="G243" t="str">
-        <v>'반납 접수'의 반납 상태 사진 올리기가 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 안내'의 이 상태로 반납하면 안 되는 예시 사진이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H243" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -8594,7 +8594,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B244" t="str">
         <v/>
@@ -8609,10 +8609,10 @@
         <v/>
       </c>
       <c r="F244" t="str">
-        <v>수령 때 사진과 나란히 견주기</v>
+        <v>늦으면 얼마가 붙는지 표</v>
       </c>
       <c r="G244" t="str">
-        <v>'반납 접수' 화면에서 수령 때 사진과 나란히 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 늦으면 얼마가 붙는지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H244" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B245" t="str">
         <v/>
@@ -8641,10 +8641,10 @@
         <v/>
       </c>
       <c r="F245" t="str">
-        <v>파손</v>
+        <v>구성품 빠지면 얼마인지 표</v>
       </c>
       <c r="G245" t="str">
-        <v>'반납 접수' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 구성품 빠지면 얼마인지 표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H245" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SCN-024</v>
+        <v>SCN-023</v>
       </c>
       <c r="B246" t="str">
         <v/>
@@ -8673,10 +8673,10 @@
         <v/>
       </c>
       <c r="F246" t="str">
-        <v>분실 있으면 미리 알리기</v>
+        <v>반납 접수로 가기</v>
       </c>
       <c r="G246" t="str">
-        <v>'반납 접수' 화면에서 분실 있으면 미리 알리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 안내' 화면에서 반납 접수로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H246" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8693,22 +8693,22 @@
         <v>SCN-024</v>
       </c>
       <c r="B247" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C247" t="str">
-        <v/>
+        <v>반납 접수</v>
       </c>
       <c r="D247" t="str">
-        <v/>
+        <v>RT-04</v>
       </c>
       <c r="E247" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F247" t="str">
-        <v>미리 알리면 배상이 줄어든다는 안내</v>
+        <v>반납할 장비와 기간 요약</v>
       </c>
       <c r="G247" t="str">
-        <v>'반납 접수' 화면에서 미리 알리면 배상이 줄어든다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 반납할 장비와 기간 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H247" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8737,10 +8737,10 @@
         <v/>
       </c>
       <c r="F248" t="str">
-        <v>세척</v>
+        <v>구성품 다 챙겼는지 하나씩 체크</v>
       </c>
       <c r="G248" t="str">
-        <v>'반납 접수' 화면에서 세척이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 구성품 다 챙겼는지 하나씩 체크가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H248" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8769,10 +8769,10 @@
         <v/>
       </c>
       <c r="F249" t="str">
-        <v>건조 상태 스스로 확인</v>
+        <v>반납 상태 사진 올리기</v>
       </c>
       <c r="G249" t="str">
-        <v>'반납 접수'의 건조 상태 스스로 확인이 실제 데이터와 같은지 대조한다.</v>
+        <v>'반납 접수'의 반납 상태 사진 올리기가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H249" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -8801,10 +8801,10 @@
         <v/>
       </c>
       <c r="F250" t="str">
-        <v>반납 방법과 시각 확정</v>
+        <v>수령 때 사진과 나란히 견주기</v>
       </c>
       <c r="G250" t="str">
-        <v>'반납 접수' 화면에서 반납 방법과 시각 확정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 수령 때 사진과 나란히 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H250" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8833,10 +8833,10 @@
         <v/>
       </c>
       <c r="F251" t="str">
-        <v>접수 후 점검에 1~2일 걸린다는 안내</v>
+        <v>파손</v>
       </c>
       <c r="G251" t="str">
-        <v>'반납 접수' 화면에서 접수 후 점검에 1~2일 걸린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 파손이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H251" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8865,10 +8865,10 @@
         <v/>
       </c>
       <c r="F252" t="str">
-        <v>점검 끝나야 보증금이 풀린다는 안내</v>
+        <v>분실 있으면 미리 알리기</v>
       </c>
       <c r="G252" t="str">
-        <v>'반납 접수' 화면에서 점검 끝나야 보증금이 풀린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 분실 있으면 미리 알리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H252" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8897,10 +8897,10 @@
         <v/>
       </c>
       <c r="F253" t="str">
-        <v>반납 접수 완료</v>
+        <v>미리 알리면 배상이 줄어든다는 안내</v>
       </c>
       <c r="G253" t="str">
-        <v>'반납 접수' 화면에서 반납 접수 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'반납 접수' 화면에서 미리 알리면 배상이 줄어든다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H253" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -8914,28 +8914,28 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B254" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C254" t="str">
-        <v>연체 안내</v>
+        <v/>
       </c>
       <c r="D254" t="str">
-        <v>RT-05</v>
+        <v/>
       </c>
       <c r="E254" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F254" t="str">
-        <v>반납 기한이 지났다는 안내와 얼마나 지났는지</v>
+        <v>세척</v>
       </c>
       <c r="G254" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 반납 기한이 지났다는 안내와 얼마나 지났는지가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 세척이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H254" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I254" t="str">
         <v/>
@@ -8946,7 +8946,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B255" t="str">
         <v/>
@@ -8961,13 +8961,13 @@
         <v/>
       </c>
       <c r="F255" t="str">
-        <v>지금까지 쌓인 연체료</v>
+        <v>건조 상태 스스로 확인</v>
       </c>
       <c r="G255" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금까지 쌓인 연체료가 보이는지 확인한다.</v>
+        <v>'반납 접수'의 건조 상태 스스로 확인이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H255" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I255" t="str">
         <v/>
@@ -8978,7 +8978,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B256" t="str">
         <v/>
@@ -8993,13 +8993,13 @@
         <v/>
       </c>
       <c r="F256" t="str">
-        <v>연체료 계산 방식 공개</v>
+        <v>반납 방법과 시각 확정</v>
       </c>
       <c r="G256" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연체료 계산 방식 공개가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 반납 방법과 시각 확정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H256" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I256" t="str">
         <v/>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B257" t="str">
         <v/>
@@ -9025,13 +9025,13 @@
         <v/>
       </c>
       <c r="F257" t="str">
-        <v>하루 더 지나면 얼마가 되는지 미리 보기</v>
+        <v>접수 후 점검에 1~2일 걸린다는 안내</v>
       </c>
       <c r="G257" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 하루 더 지나면 얼마가 되는지 미리 보기가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 접수 후 점검에 1~2일 걸린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H257" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I257" t="str">
         <v/>
@@ -9042,7 +9042,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B258" t="str">
         <v/>
@@ -9057,13 +9057,13 @@
         <v/>
       </c>
       <c r="F258" t="str">
-        <v>지금 반납하면 얼마인지</v>
+        <v>점검 끝나야 보증금이 풀린다는 안내</v>
       </c>
       <c r="G258" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납하면 얼마인지가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 점검 끝나야 보증금이 풀린다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H258" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I258" t="str">
         <v/>
@@ -9074,7 +9074,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>SCN-025</v>
+        <v>SCN-024</v>
       </c>
       <c r="B259" t="str">
         <v/>
@@ -9089,13 +9089,13 @@
         <v/>
       </c>
       <c r="F259" t="str">
-        <v>연장으로 바꿀 수 있는지 안내</v>
+        <v>반납 접수 완료</v>
       </c>
       <c r="G259" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연장으로 바꿀 수 있는지 안내가 보이는지 확인한다.</v>
+        <v>'반납 접수' 화면에서 반납 접수 완료가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H259" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I259" t="str">
         <v/>
@@ -9109,22 +9109,22 @@
         <v>SCN-025</v>
       </c>
       <c r="B260" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C260" t="str">
-        <v/>
+        <v>연체 안내</v>
       </c>
       <c r="D260" t="str">
-        <v/>
+        <v>RT-05</v>
       </c>
       <c r="E260" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F260" t="str">
-        <v>보증금에서 먼저 빠진다는 안내</v>
+        <v>반납 기한이 지났다는 안내와 얼마나 지났는지</v>
       </c>
       <c r="G260" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금에서 먼저 빠진다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 반납 기한이 지났다는 안내와 얼마나 지났는지가 보이는지 확인한다.</v>
       </c>
       <c r="H260" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9153,10 +9153,10 @@
         <v/>
       </c>
       <c r="F261" t="str">
-        <v>보증금을 넘으면 추가 청구된다는 안내</v>
+        <v>지금까지 쌓인 연체료</v>
       </c>
       <c r="G261" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금을 넘으면 추가 청구된다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금까지 쌓인 연체료가 보이는지 확인한다.</v>
       </c>
       <c r="H261" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9185,10 +9185,10 @@
         <v/>
       </c>
       <c r="F262" t="str">
-        <v>연락 없이 7일 넘으면 분실 처리된다는 안내</v>
+        <v>연체료 계산 방식 공개</v>
       </c>
       <c r="G262" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연락 없이 7일 넘으면 분실 처리된다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연체료 계산 방식 공개가 보이는지 확인한다.</v>
       </c>
       <c r="H262" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9217,10 +9217,10 @@
         <v/>
       </c>
       <c r="F263" t="str">
-        <v>지금 반납 접수하기</v>
+        <v>하루 더 지나면 얼마가 되는지 미리 보기</v>
       </c>
       <c r="G263" t="str">
-        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납 접수하기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 하루 더 지나면 얼마가 되는지 미리 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H263" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9234,28 +9234,28 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B264" t="str">
-        <v>수령·반납</v>
+        <v/>
       </c>
       <c r="C264" t="str">
-        <v>파손·분실 신고</v>
+        <v/>
       </c>
       <c r="D264" t="str">
-        <v>RT-06</v>
+        <v/>
       </c>
       <c r="E264" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F264" t="str">
-        <v>무엇이 어떻게 됐는지 고르기</v>
+        <v>지금 반납하면 얼마인지</v>
       </c>
       <c r="G264" t="str">
-        <v>'파손·분실 신고' 화면에서 무엇이 어떻게 됐는지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납하면 얼마인지가 보이는지 확인한다.</v>
       </c>
       <c r="H264" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I264" t="str">
         <v/>
@@ -9266,7 +9266,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B265" t="str">
         <v/>
@@ -9281,13 +9281,13 @@
         <v/>
       </c>
       <c r="F265" t="str">
-        <v>파손 부위 고르고 정도 고르기</v>
+        <v>연장으로 바꿀 수 있는지 안내</v>
       </c>
       <c r="G265" t="str">
-        <v>'파손·분실 신고' 화면에서 파손 부위 고르고 정도 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연장으로 바꿀 수 있는지 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H265" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I265" t="str">
         <v/>
@@ -9298,7 +9298,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B266" t="str">
         <v/>
@@ -9313,13 +9313,13 @@
         <v/>
       </c>
       <c r="F266" t="str">
-        <v>사진 올리기(필수)</v>
+        <v>보증금에서 먼저 빠진다는 안내</v>
       </c>
       <c r="G266" t="str">
-        <v>'파손·분실 신고' 화면에서 사진 올리기(필수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금에서 먼저 빠진다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H266" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I266" t="str">
         <v/>
@@ -9330,7 +9330,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B267" t="str">
         <v/>
@@ -9345,13 +9345,13 @@
         <v/>
       </c>
       <c r="F267" t="str">
-        <v>언제 어떻게 생긴 일인지 적기</v>
+        <v>보증금을 넘으면 추가 청구된다는 안내</v>
       </c>
       <c r="G267" t="str">
-        <v>'파손·분실 신고' 화면에서 언제 어떻게 생긴 일인지 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 보증금을 넘으면 추가 청구된다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H267" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I267" t="str">
         <v/>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B268" t="str">
         <v/>
@@ -9377,13 +9377,13 @@
         <v/>
       </c>
       <c r="F268" t="str">
-        <v>부위별 배상 기준액 바로 보기</v>
+        <v>연락 없이 7일 넘으면 분실 처리된다는 안내</v>
       </c>
       <c r="G268" t="str">
-        <v>'파손·분실 신고' 화면에서 부위별 배상 기준액 바로 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 연락 없이 7일 넘으면 분실 처리된다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H268" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I268" t="str">
         <v/>
@@ -9394,7 +9394,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>SCN-026</v>
+        <v>SCN-025</v>
       </c>
       <c r="B269" t="str">
         <v/>
@@ -9409,13 +9409,13 @@
         <v/>
       </c>
       <c r="F269" t="str">
-        <v>가입한 보험이 있으면 면책 되는지 판정</v>
+        <v>지금 반납 접수하기</v>
       </c>
       <c r="G269" t="str">
-        <v>'파손·분실 신고' 화면에서 가입한 보험이 있으면 면책 되는지 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '연체 안내' 화면이 나오게 한 뒤, 지금 반납 접수하기가 보이는지 확인한다.</v>
       </c>
       <c r="H269" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I269" t="str">
         <v/>
@@ -9429,22 +9429,22 @@
         <v>SCN-026</v>
       </c>
       <c r="B270" t="str">
-        <v/>
+        <v>수령·반납</v>
       </c>
       <c r="C270" t="str">
-        <v/>
+        <v>파손·분실 신고</v>
       </c>
       <c r="D270" t="str">
-        <v/>
+        <v>RT-06</v>
       </c>
       <c r="E270" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F270" t="str">
-        <v>면책 제외 사유 안내</v>
+        <v>무엇이 어떻게 됐는지 고르기</v>
       </c>
       <c r="G270" t="str">
-        <v>'파손·분실 신고' 화면에서 면책 제외 사유 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 무엇이 어떻게 됐는지 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H270" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9473,10 +9473,10 @@
         <v/>
       </c>
       <c r="F271" t="str">
-        <v>예상 배상액과 보증금에서 얼마가 빠지는지</v>
+        <v>파손 부위 고르고 정도 고르기</v>
       </c>
       <c r="G271" t="str">
-        <v>'파손·분실 신고' 화면에서 예상 배상액과 보증금에서 얼마가 빠지는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 파손 부위 고르고 정도 고르기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H271" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9505,10 +9505,10 @@
         <v/>
       </c>
       <c r="F272" t="str">
-        <v>수리 가능하면 수리비만 낸다는 안내</v>
+        <v>사진 올리기(필수)</v>
       </c>
       <c r="G272" t="str">
-        <v>'파손·분실 신고' 화면에서 수리 가능하면 수리비만 낸다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 사진 올리기(필수)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H272" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9537,10 +9537,10 @@
         <v/>
       </c>
       <c r="F273" t="str">
-        <v>신고하면 배상이 줄 수 있다는 안내</v>
+        <v>언제 어떻게 생긴 일인지 적기</v>
       </c>
       <c r="G273" t="str">
-        <v>'파손·분실 신고' 화면에서 신고하면 배상이 줄 수 있다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 언제 어떻게 생긴 일인지 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H273" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9569,10 +9569,10 @@
         <v/>
       </c>
       <c r="F274" t="str">
-        <v>신고 접수</v>
+        <v>부위별 배상 기준액 바로 보기</v>
       </c>
       <c r="G274" t="str">
-        <v>'파손·분실 신고' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'파손·분실 신고' 화면에서 부위별 배상 기준액 바로 보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H274" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -9586,28 +9586,28 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B275" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C275" t="str">
-        <v>점검 진행 중</v>
+        <v/>
       </c>
       <c r="D275" t="str">
-        <v>ST-01</v>
+        <v/>
       </c>
       <c r="E275" t="str">
-        <v>예외·상태</v>
+        <v/>
       </c>
       <c r="F275" t="str">
-        <v>반납 접수됨과 접수 시각</v>
+        <v>가입한 보험이 있으면 면책 되는지 판정</v>
       </c>
       <c r="G275" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납 접수됨과 접수 시각이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 가입한 보험이 있으면 면책 되는지 판정이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H275" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I275" t="str">
         <v/>
@@ -9618,7 +9618,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B276" t="str">
         <v/>
@@ -9633,13 +9633,13 @@
         <v/>
       </c>
       <c r="F276" t="str">
-        <v>점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)</v>
+        <v>면책 제외 사유 안내</v>
       </c>
       <c r="G276" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 면책 제외 사유 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H276" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I276" t="str">
         <v/>
@@ -9650,7 +9650,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B277" t="str">
         <v/>
@@ -9665,13 +9665,13 @@
         <v/>
       </c>
       <c r="F277" t="str">
-        <v>지금 어느 단계인지</v>
+        <v>예상 배상액과 보증금에서 얼마가 빠지는지</v>
       </c>
       <c r="G277" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 지금 어느 단계인지가 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 예상 배상액과 보증금에서 얼마가 빠지는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H277" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I277" t="str">
         <v/>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B278" t="str">
         <v/>
@@ -9697,13 +9697,13 @@
         <v/>
       </c>
       <c r="F278" t="str">
-        <v>각 단계에서 무엇을 보는지 설명</v>
+        <v>수리 가능하면 수리비만 낸다는 안내</v>
       </c>
       <c r="G278" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 각 단계에서 무엇을 보는지 설명이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 수리 가능하면 수리비만 낸다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H278" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I278" t="str">
         <v/>
@@ -9714,7 +9714,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B279" t="str">
         <v/>
@@ -9729,13 +9729,13 @@
         <v/>
       </c>
       <c r="F279" t="str">
-        <v>점검 예상 완료 시각</v>
+        <v>신고하면 배상이 줄 수 있다는 안내</v>
       </c>
       <c r="G279" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 예상 완료 시각이 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 신고하면 배상이 줄 수 있다는 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H279" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I279" t="str">
         <v/>
@@ -9746,7 +9746,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>SCN-027</v>
+        <v>SCN-026</v>
       </c>
       <c r="B280" t="str">
         <v/>
@@ -9761,13 +9761,13 @@
         <v/>
       </c>
       <c r="F280" t="str">
-        <v>점검 결과가 나오면 알림 간다는 안내</v>
+        <v>신고 접수</v>
       </c>
       <c r="G280" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 결과가 나오면 알림 간다는 안내가 보이는지 확인한다.</v>
+        <v>'파손·분실 신고' 화면에서 신고 접수가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H280" t="str">
-        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I280" t="str">
         <v/>
@@ -9781,22 +9781,22 @@
         <v>SCN-027</v>
       </c>
       <c r="B281" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C281" t="str">
-        <v/>
+        <v>점검 진행 중</v>
       </c>
       <c r="D281" t="str">
-        <v/>
+        <v>ST-01</v>
       </c>
       <c r="E281" t="str">
-        <v/>
+        <v>예외·상태</v>
       </c>
       <c r="F281" t="str">
-        <v>보증금은 점검이 끝나야 풀린다는 안내</v>
+        <v>반납 접수됨과 접수 시각</v>
       </c>
       <c r="G281" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 보증금은 점검이 끝나야 풀린다는 안내가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납 접수됨과 접수 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H281" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9825,10 +9825,10 @@
         <v/>
       </c>
       <c r="F282" t="str">
-        <v>반납할 때 올린 사진 다시 보기</v>
+        <v>점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)</v>
       </c>
       <c r="G282" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납할 때 올린 사진 다시 보기가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 단계 진행 막대(접수·수량 확인·상태 점검·정산 확정)이 보이는지 확인한다.</v>
       </c>
       <c r="H282" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9857,10 +9857,10 @@
         <v/>
       </c>
       <c r="F283" t="str">
-        <v>점검이 늦어지면 어떻게 되는지</v>
+        <v>지금 어느 단계인지</v>
       </c>
       <c r="G283" t="str">
-        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검이 늦어지면 어떻게 되는지가 보이는지 확인한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 지금 어느 단계인지가 보이는지 확인한다.</v>
       </c>
       <c r="H283" t="str">
         <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
@@ -9874,28 +9874,28 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B284" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C284" t="str">
-        <v>정산 내역 - 연체·파손 청구</v>
+        <v/>
       </c>
       <c r="D284" t="str">
-        <v>ST-02</v>
+        <v/>
       </c>
       <c r="E284" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F284" t="str">
-        <v>점검 결과 요약</v>
+        <v>각 단계에서 무엇을 보는지 설명</v>
       </c>
       <c r="G284" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 점검 결과 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 각 단계에서 무엇을 보는지 설명이 보이는지 확인한다.</v>
       </c>
       <c r="H284" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I284" t="str">
         <v/>
@@ -9906,7 +9906,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B285" t="str">
         <v/>
@@ -9921,13 +9921,13 @@
         <v/>
       </c>
       <c r="F285" t="str">
-        <v>청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)</v>
+        <v>점검 예상 완료 시각</v>
       </c>
       <c r="G285" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 예상 완료 시각이 보이는지 확인한다.</v>
       </c>
       <c r="H285" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I285" t="str">
         <v/>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B286" t="str">
         <v/>
@@ -9953,13 +9953,13 @@
         <v/>
       </c>
       <c r="F286" t="str">
-        <v>항목마다 근거 사진과 계산식</v>
+        <v>점검 결과가 나오면 알림 간다는 안내</v>
       </c>
       <c r="G286" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 항목마다 근거 사진과 계산식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검 결과가 나오면 알림 간다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H286" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I286" t="str">
         <v/>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B287" t="str">
         <v/>
@@ -9985,13 +9985,13 @@
         <v/>
       </c>
       <c r="F287" t="str">
-        <v>보험으로 면책된 금액</v>
+        <v>보증금은 점검이 끝나야 풀린다는 안내</v>
       </c>
       <c r="G287" t="str">
-        <v>'정산 내역 - 연체·파손 청구'의 보험으로 면책된 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 보증금은 점검이 끝나야 풀린다는 안내가 보이는지 확인한다.</v>
       </c>
       <c r="H287" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I287" t="str">
         <v/>
@@ -10002,7 +10002,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B288" t="str">
         <v/>
@@ -10017,13 +10017,13 @@
         <v/>
       </c>
       <c r="F288" t="str">
-        <v>청구 합계와 보증금에서 차감</v>
+        <v>반납할 때 올린 사진 다시 보기</v>
       </c>
       <c r="G288" t="str">
-        <v>'정산 내역 - 연체·파손 청구'의 청구 합계와 보증금에서 차감이 실제 데이터와 같은지 대조한다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 반납할 때 올린 사진 다시 보기가 보이는지 확인한다.</v>
       </c>
       <c r="H288" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I288" t="str">
         <v/>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>SCN-028</v>
+        <v>SCN-027</v>
       </c>
       <c r="B289" t="str">
         <v/>
@@ -10049,13 +10049,13 @@
         <v/>
       </c>
       <c r="F289" t="str">
-        <v>보증금이 모자라면 추가 청구액</v>
+        <v>점검이 늦어지면 어떻게 되는지</v>
       </c>
       <c r="G289" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 보증금이 모자라면 추가 청구액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>일부러 그 상황을 만들어 '점검 진행 중' 화면이 나오게 한 뒤, 점검이 늦어지면 어떻게 되는지가 보이는지 확인한다.</v>
       </c>
       <c r="H289" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>무엇이 없거나 잘못됐는지 알려주고, 다음에 무엇을 하면 되는지 가리키는 버튼이 있다.</v>
       </c>
       <c r="I289" t="str">
         <v/>
@@ -10069,25 +10069,25 @@
         <v>SCN-028</v>
       </c>
       <c r="B290" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C290" t="str">
-        <v/>
+        <v>정산 내역 - 연체·파손 청구</v>
       </c>
       <c r="D290" t="str">
-        <v/>
+        <v>ST-02</v>
       </c>
       <c r="E290" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F290" t="str">
-        <v>추가 청구 결제 방법</v>
+        <v>점검 결과 요약</v>
       </c>
       <c r="G290" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 추가 청구 결제 방법을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 점검 결과 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H290" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I290" t="str">
         <v/>
@@ -10113,10 +10113,10 @@
         <v/>
       </c>
       <c r="F291" t="str">
-        <v>이의 제기하기</v>
+        <v>청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)</v>
       </c>
       <c r="G291" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 청구 항목별 표(연체료·파손 배상·구성품 부족·세척비)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H291" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10145,10 +10145,10 @@
         <v/>
       </c>
       <c r="F292" t="str">
-        <v>이의 제기 기한 안내</v>
+        <v>항목마다 근거 사진과 계산식</v>
       </c>
       <c r="G292" t="str">
-        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 항목마다 근거 사진과 계산식이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H292" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10177,13 +10177,13 @@
         <v/>
       </c>
       <c r="F293" t="str">
-        <v>정산 확정되면 되돌릴 수 없다는 안내</v>
+        <v>보험으로 면책된 금액</v>
       </c>
       <c r="G293" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 정산 확정되면 되돌릴 수 없다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'의 보험으로 면책된 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H293" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I293" t="str">
         <v/>
@@ -10209,13 +10209,13 @@
         <v/>
       </c>
       <c r="F294" t="str">
-        <v>정산서 내려받기</v>
+        <v>청구 합계와 보증금에서 차감</v>
       </c>
       <c r="G294" t="str">
-        <v>'정산 내역 - 연체·파손 청구'에서 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'의 청구 합계와 보증금에서 차감이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H294" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I294" t="str">
         <v/>
@@ -10226,25 +10226,25 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B295" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C295" t="str">
-        <v>보증금 환급</v>
+        <v/>
       </c>
       <c r="D295" t="str">
-        <v>ST-03</v>
+        <v/>
       </c>
       <c r="E295" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F295" t="str">
-        <v>보증금 원금과 차감 내역 요약</v>
+        <v>보증금이 모자라면 추가 청구액</v>
       </c>
       <c r="G295" t="str">
-        <v>'보증금 환급' 화면에서 보증금 원금과 차감 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 보증금이 모자라면 추가 청구액이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H295" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B296" t="str">
         <v/>
@@ -10273,13 +10273,13 @@
         <v/>
       </c>
       <c r="F296" t="str">
-        <v>돌려받을 금액 크게</v>
+        <v>추가 청구 결제 방법</v>
       </c>
       <c r="G296" t="str">
-        <v>'보증금 환급'의 돌려받을 금액 크게가 실제 데이터와 같은지 대조한다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 추가 청구 결제 방법을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H296" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I296" t="str">
         <v/>
@@ -10290,7 +10290,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B297" t="str">
         <v/>
@@ -10305,10 +10305,10 @@
         <v/>
       </c>
       <c r="F297" t="str">
-        <v>환급 방법(카드 보류 해제·계좌 입금·적립금)</v>
+        <v>이의 제기하기</v>
       </c>
       <c r="G297" t="str">
-        <v>'보증금 환급' 화면에서 환급 방법(카드 보류 해제·계좌 입금·적립금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H297" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10322,7 +10322,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B298" t="str">
         <v/>
@@ -10337,10 +10337,10 @@
         <v/>
       </c>
       <c r="F298" t="str">
-        <v>방법별 걸리는 기간 안내</v>
+        <v>이의 제기 기한 안내</v>
       </c>
       <c r="G298" t="str">
-        <v>'보증금 환급' 화면에서 방법별 걸리는 기간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구' 화면에서 이의 제기 기한 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H298" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10354,7 +10354,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B299" t="str">
         <v/>
@@ -10369,13 +10369,13 @@
         <v/>
       </c>
       <c r="F299" t="str">
-        <v>카드 보류 해제가 무엇인지 설명</v>
+        <v>정산 확정되면 되돌릴 수 없다는 안내</v>
       </c>
       <c r="G299" t="str">
-        <v>'보증금 환급'의 카드 보류 해제가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 정산 확정되면 되돌릴 수 없다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H299" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I299" t="str">
         <v/>
@@ -10386,7 +10386,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>SCN-029</v>
+        <v>SCN-028</v>
       </c>
       <c r="B300" t="str">
         <v/>
@@ -10401,13 +10401,13 @@
         <v/>
       </c>
       <c r="F300" t="str">
-        <v>적립금으로 받으면 더 주는 혜택</v>
+        <v>정산서 내려받기</v>
       </c>
       <c r="G300" t="str">
-        <v>'보증금 환급' 화면에서 적립금으로 받으면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'정산 내역 - 연체·파손 청구'에서 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H300" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I300" t="str">
         <v/>
@@ -10421,25 +10421,25 @@
         <v>SCN-029</v>
       </c>
       <c r="B301" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C301" t="str">
-        <v/>
+        <v>보증금 환급</v>
       </c>
       <c r="D301" t="str">
-        <v/>
+        <v>ST-03</v>
       </c>
       <c r="E301" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F301" t="str">
-        <v>환급 진행 단계 표시</v>
+        <v>보증금 원금과 차감 내역 요약</v>
       </c>
       <c r="G301" t="str">
-        <v>'보증금 환급'의 환급 진행 단계 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'보증금 환급' 화면에서 보증금 원금과 차감 내역 요약이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H301" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I301" t="str">
         <v/>
@@ -10465,13 +10465,13 @@
         <v/>
       </c>
       <c r="F302" t="str">
-        <v>카드사 사정으로 늦어질 수 있다는 안내</v>
+        <v>돌려받을 금액 크게</v>
       </c>
       <c r="G302" t="str">
-        <v>'보증금 환급'의 카드사 사정으로 늦어질 수 있다는 안내를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'보증금 환급'의 돌려받을 금액 크게가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H302" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I302" t="str">
         <v/>
@@ -10497,10 +10497,10 @@
         <v/>
       </c>
       <c r="F303" t="str">
-        <v>언제까지 안 들어오면 어떻게 하는지</v>
+        <v>환급 방법(카드 보류 해제·계좌 입금·적립금)</v>
       </c>
       <c r="G303" t="str">
-        <v>'보증금 환급' 화면에서 언제까지 안 들어오면 어떻게 하는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 환급 방법(카드 보류 해제·계좌 입금·적립금)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H303" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10529,10 +10529,10 @@
         <v/>
       </c>
       <c r="F304" t="str">
-        <v>환급 내역서 받기</v>
+        <v>방법별 걸리는 기간 안내</v>
       </c>
       <c r="G304" t="str">
-        <v>'보증금 환급' 화면에서 환급 내역서 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 방법별 걸리는 기간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H304" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10546,28 +10546,28 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B305" t="str">
-        <v>정산</v>
+        <v/>
       </c>
       <c r="C305" t="str">
-        <v>환급 완료</v>
+        <v/>
       </c>
       <c r="D305" t="str">
-        <v>ST-04</v>
+        <v/>
       </c>
       <c r="E305" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F305" t="str">
-        <v>환급 완료 안내와 금액</v>
+        <v>카드 보류 해제가 무엇인지 설명</v>
       </c>
       <c r="G305" t="str">
-        <v>'환급 완료'의 환급 완료 안내와 금액이 실제 데이터와 같은지 대조한다.</v>
+        <v>'보증금 환급'의 카드 보류 해제가 무엇인지 설명을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H305" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I305" t="str">
         <v/>
@@ -10578,7 +10578,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B306" t="str">
         <v/>
@@ -10593,10 +10593,10 @@
         <v/>
       </c>
       <c r="F306" t="str">
-        <v>언제 어떤 방법으로 처리됐는지</v>
+        <v>적립금으로 받으면 더 주는 혜택</v>
       </c>
       <c r="G306" t="str">
-        <v>'환급 완료' 화면에서 언제 어떤 방법으로 처리됐는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 적립금으로 받으면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H306" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10610,7 +10610,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B307" t="str">
         <v/>
@@ -10625,13 +10625,13 @@
         <v/>
       </c>
       <c r="F307" t="str">
-        <v>이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)</v>
+        <v>환급 진행 단계 표시</v>
       </c>
       <c r="G307" t="str">
-        <v>'환급 완료' 화면에서 이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급'의 환급 진행 단계 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H307" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I307" t="str">
         <v/>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B308" t="str">
         <v/>
@@ -10657,13 +10657,13 @@
         <v/>
       </c>
       <c r="F308" t="str">
-        <v>영수증과 정산서 내려받기</v>
+        <v>카드사 사정으로 늦어질 수 있다는 안내</v>
       </c>
       <c r="G308" t="str">
-        <v>'환급 완료'에서 영수증과 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'보증금 환급'의 카드사 사정으로 늦어질 수 있다는 안내를 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H308" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I308" t="str">
         <v/>
@@ -10674,7 +10674,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B309" t="str">
         <v/>
@@ -10689,10 +10689,10 @@
         <v/>
       </c>
       <c r="F309" t="str">
-        <v>후기 쓰기 유도와 적립금 혜택</v>
+        <v>언제까지 안 들어오면 어떻게 하는지</v>
       </c>
       <c r="G309" t="str">
-        <v>'환급 완료' 화면에서 후기 쓰기 유도와 적립금 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 언제까지 안 들어오면 어떻게 하는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H309" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>SCN-030</v>
+        <v>SCN-029</v>
       </c>
       <c r="B310" t="str">
         <v/>
@@ -10721,10 +10721,10 @@
         <v/>
       </c>
       <c r="F310" t="str">
-        <v>같은 장비 다시 빌리기</v>
+        <v>환급 내역서 받기</v>
       </c>
       <c r="G310" t="str">
-        <v>'환급 완료' 화면에서 같은 장비 다시 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'보증금 환급' 화면에서 환급 내역서 받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H310" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10741,25 +10741,25 @@
         <v>SCN-030</v>
       </c>
       <c r="B311" t="str">
-        <v/>
+        <v>정산</v>
       </c>
       <c r="C311" t="str">
-        <v/>
+        <v>환급 완료</v>
       </c>
       <c r="D311" t="str">
-        <v/>
+        <v>ST-04</v>
       </c>
       <c r="E311" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F311" t="str">
-        <v>다음에 쓸 쿠폰</v>
+        <v>환급 완료 안내와 금액</v>
       </c>
       <c r="G311" t="str">
-        <v>'환급 완료' 화면에서 다음에 쓸 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환급 완료'의 환급 완료 안내와 금액이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H311" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I311" t="str">
         <v/>
@@ -10785,13 +10785,13 @@
         <v/>
       </c>
       <c r="F312" t="str">
-        <v>이용 횟수와 보증금 면제까지 남은 횟수</v>
+        <v>언제 어떤 방법으로 처리됐는지</v>
       </c>
       <c r="G312" t="str">
-        <v>'환급 완료'의 이용 횟수와 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료' 화면에서 언제 어떤 방법으로 처리됐는지가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H312" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I312" t="str">
         <v/>
@@ -10802,28 +10802,28 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B313" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C313" t="str">
-        <v>내 대여 내역</v>
+        <v/>
       </c>
       <c r="D313" t="str">
-        <v>MY-01</v>
+        <v/>
       </c>
       <c r="E313" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F313" t="str">
-        <v>상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)</v>
+        <v>이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)</v>
       </c>
       <c r="G313" t="str">
-        <v>'내 대여 내역'에서 상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'환급 완료' 화면에서 이번 대여 전체 요약(빌린 것·기간·낸 돈·돌려받은 돈)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H313" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I313" t="str">
         <v/>
@@ -10834,7 +10834,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B314" t="str">
         <v/>
@@ -10849,13 +10849,13 @@
         <v/>
       </c>
       <c r="F314" t="str">
-        <v>상태별 건수 배지</v>
+        <v>영수증과 정산서 내려받기</v>
       </c>
       <c r="G314" t="str">
-        <v>'내 대여 내역'의 상태별 건수 배지가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료'에서 영수증과 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H314" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I314" t="str">
         <v/>
@@ -10866,7 +10866,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B315" t="str">
         <v/>
@@ -10881,13 +10881,13 @@
         <v/>
       </c>
       <c r="F315" t="str">
-        <v>대여 카드 목록(장비 사진·이름·기간·상태·금액)</v>
+        <v>후기 쓰기 유도와 적립금 혜택</v>
       </c>
       <c r="G315" t="str">
-        <v>'내 대여 내역'의 대여 카드 목록(장비 사진·이름·기간·상태·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'환급 완료' 화면에서 후기 쓰기 유도와 적립금 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H315" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I315" t="str">
         <v/>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B316" t="str">
         <v/>
@@ -10913,13 +10913,13 @@
         <v/>
       </c>
       <c r="F316" t="str">
-        <v>이용 중인 것은 남은 시간 표시</v>
+        <v>같은 장비 다시 빌리기</v>
       </c>
       <c r="G316" t="str">
-        <v>'내 대여 내역'의 이용 중인 것은 남은 시간 표시가 실제 데이터와 같은지 대조한다.</v>
+        <v>'환급 완료' 화면에서 같은 장비 다시 빌리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H316" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I316" t="str">
         <v/>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B317" t="str">
         <v/>
@@ -10945,10 +10945,10 @@
         <v/>
       </c>
       <c r="F317" t="str">
-        <v>연체는 붉게 맨 위로</v>
+        <v>다음에 쓸 쿠폰</v>
       </c>
       <c r="G317" t="str">
-        <v>'내 대여 내역' 화면에서 연체는 붉게 맨 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환급 완료' 화면에서 다음에 쓸 쿠폰이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H317" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -10962,7 +10962,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>SCN-031</v>
+        <v>SCN-030</v>
       </c>
       <c r="B318" t="str">
         <v/>
@@ -10977,13 +10977,13 @@
         <v/>
       </c>
       <c r="F318" t="str">
-        <v>점검 중인 것은 예상 완료 시각</v>
+        <v>이용 횟수와 보증금 면제까지 남은 횟수</v>
       </c>
       <c r="G318" t="str">
-        <v>'내 대여 내역' 화면에서 점검 중인 것은 예상 완료 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'환급 완료'의 이용 횟수와 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H318" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I318" t="str">
         <v/>
@@ -10997,25 +10997,25 @@
         <v>SCN-031</v>
       </c>
       <c r="B319" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C319" t="str">
-        <v/>
+        <v>내 대여 내역</v>
       </c>
       <c r="D319" t="str">
-        <v/>
+        <v>MY-01</v>
       </c>
       <c r="E319" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F319" t="str">
-        <v>보증금 상태 배지(보류중·환급완료)</v>
+        <v>상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)</v>
       </c>
       <c r="G319" t="str">
-        <v>'내 대여 내역'의 보증금 상태 배지(보류중·환급완료)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 대여 내역'에서 상태 탭(전체·예약확정·이용중·반납접수·점검중·정산완료·취소)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H319" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I319" t="str">
         <v/>
@@ -11041,13 +11041,13 @@
         <v/>
       </c>
       <c r="F320" t="str">
-        <v>기간</v>
+        <v>상태별 건수 배지</v>
       </c>
       <c r="G320" t="str">
-        <v>'내 대여 내역' 화면에서 기간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역'의 상태별 건수 배지가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H320" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I320" t="str">
         <v/>
@@ -11073,13 +11073,13 @@
         <v/>
       </c>
       <c r="F321" t="str">
-        <v>장비명 검색</v>
+        <v>대여 카드 목록(장비 사진·이름·기간·상태·금액)</v>
       </c>
       <c r="G321" t="str">
-        <v>'내 대여 내역'에서 장비명 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'내 대여 내역'의 대여 카드 목록(장비 사진·이름·기간·상태·금액)을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H321" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I321" t="str">
         <v/>
@@ -11105,13 +11105,13 @@
         <v/>
       </c>
       <c r="F322" t="str">
-        <v>다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)</v>
+        <v>이용 중인 것은 남은 시간 표시</v>
       </c>
       <c r="G322" t="str">
-        <v>'내 대여 내역'에서 다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)를 눌러 본다.</v>
+        <v>'내 대여 내역'의 이용 중인 것은 남은 시간 표시가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H322" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I322" t="str">
         <v/>
@@ -11122,28 +11122,28 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B323" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C323" t="str">
-        <v>대여 상세</v>
+        <v/>
       </c>
       <c r="D323" t="str">
-        <v>MY-02</v>
+        <v/>
       </c>
       <c r="E323" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F323" t="str">
-        <v>대여번호와 상태</v>
+        <v>연체는 붉게 맨 위로</v>
       </c>
       <c r="G323" t="str">
-        <v>'대여 상세'의 대여번호와 상태가 실제 데이터와 같은지 대조한다.</v>
+        <v>'내 대여 내역' 화면에서 연체는 붉게 맨 위로가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H323" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I323" t="str">
         <v/>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B324" t="str">
         <v/>
@@ -11169,10 +11169,10 @@
         <v/>
       </c>
       <c r="F324" t="str">
-        <v>진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)</v>
+        <v>점검 중인 것은 예상 완료 시각</v>
       </c>
       <c r="G324" t="str">
-        <v>'대여 상세' 화면에서 진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역' 화면에서 점검 중인 것은 예상 완료 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H324" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11186,7 +11186,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B325" t="str">
         <v/>
@@ -11201,13 +11201,13 @@
         <v/>
       </c>
       <c r="F325" t="str">
-        <v>빌린 장비와 구성품</v>
+        <v>보증금 상태 배지(보류중·환급완료)</v>
       </c>
       <c r="G325" t="str">
-        <v>'대여 상세' 화면에서 빌린 장비와 구성품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역'의 보증금 상태 배지(보류중·환급완료)가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H325" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I325" t="str">
         <v/>
@@ -11218,7 +11218,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B326" t="str">
         <v/>
@@ -11233,10 +11233,10 @@
         <v/>
       </c>
       <c r="F326" t="str">
-        <v>기간과 실제 수령</v>
+        <v>기간</v>
       </c>
       <c r="G326" t="str">
-        <v>'대여 상세' 화면에서 기간과 실제 수령이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역' 화면에서 기간이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H326" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11250,7 +11250,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B327" t="str">
         <v/>
@@ -11265,13 +11265,13 @@
         <v/>
       </c>
       <c r="F327" t="str">
-        <v>반납 시각</v>
+        <v>장비명 검색</v>
       </c>
       <c r="G327" t="str">
-        <v>'대여 상세' 화면에서 반납 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'내 대여 내역'에서 장비명 검색의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H327" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I327" t="str">
         <v/>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>SCN-032</v>
+        <v>SCN-031</v>
       </c>
       <c r="B328" t="str">
         <v/>
@@ -11297,13 +11297,13 @@
         <v/>
       </c>
       <c r="F328" t="str">
-        <v>결제 내역(대여료·배송비·할인·보증금)</v>
+        <v>다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)</v>
       </c>
       <c r="G328" t="str">
-        <v>'대여 상세'에서 결제 내역(대여료·배송비·할인·보증금)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'내 대여 내역'에서 다음에 할 일 버튼(반납하기·후기쓰기·다시빌리기)를 눌러 본다.</v>
       </c>
       <c r="H328" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I328" t="str">
         <v/>
@@ -11317,22 +11317,22 @@
         <v>SCN-032</v>
       </c>
       <c r="B329" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C329" t="str">
-        <v/>
+        <v>대여 상세</v>
       </c>
       <c r="D329" t="str">
-        <v/>
+        <v>MY-02</v>
       </c>
       <c r="E329" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F329" t="str">
-        <v>보증금 상태와 환급 예정일</v>
+        <v>대여번호와 상태</v>
       </c>
       <c r="G329" t="str">
-        <v>'대여 상세'의 보증금 상태와 환급 예정일이 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 상세'의 대여번호와 상태가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H329" t="str">
         <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
@@ -11361,10 +11361,10 @@
         <v/>
       </c>
       <c r="F330" t="str">
-        <v>수령 때와 반납 때 사진 견주기</v>
+        <v>진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)</v>
       </c>
       <c r="G330" t="str">
-        <v>'대여 상세' 화면에서 수령 때와 반납 때 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 진행 단계 타임라인(신청·결제·수령·이용·반납·점검·정산·환급)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H330" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11393,13 +11393,13 @@
         <v/>
       </c>
       <c r="F331" t="str">
-        <v>계약서와 정산서 내려받기</v>
+        <v>빌린 장비와 구성품</v>
       </c>
       <c r="G331" t="str">
-        <v>'대여 상세'에서 계약서와 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'대여 상세' 화면에서 빌린 장비와 구성품이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H331" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I331" t="str">
         <v/>
@@ -11425,13 +11425,13 @@
         <v/>
       </c>
       <c r="F332" t="str">
-        <v>상태에 따른 다음 행동 버튼</v>
+        <v>기간과 실제 수령</v>
       </c>
       <c r="G332" t="str">
-        <v>'대여 상세'에서 상태에 따른 다음 행동 버튼을 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 기간과 실제 수령이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H332" t="str">
-        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I332" t="str">
         <v/>
@@ -11457,10 +11457,10 @@
         <v/>
       </c>
       <c r="F333" t="str">
-        <v>이 대여 문의하기</v>
+        <v>반납 시각</v>
       </c>
       <c r="G333" t="str">
-        <v>'대여 상세' 화면에서 이 대여 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 반납 시각이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H333" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11474,28 +11474,28 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B334" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C334" t="str">
-        <v>후기 쓰기</v>
+        <v/>
       </c>
       <c r="D334" t="str">
-        <v>MY-03</v>
+        <v/>
       </c>
       <c r="E334" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F334" t="str">
-        <v>빌린 장비 확인</v>
+        <v>결제 내역(대여료·배송비·할인·보증금)</v>
       </c>
       <c r="G334" t="str">
-        <v>'후기 쓰기' 화면에서 빌린 장비 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 결제 내역(대여료·배송비·할인·보증금)을 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H334" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I334" t="str">
         <v/>
@@ -11506,7 +11506,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B335" t="str">
         <v/>
@@ -11521,13 +11521,13 @@
         <v/>
       </c>
       <c r="F335" t="str">
-        <v>전체 별점 주기</v>
+        <v>보증금 상태와 환급 예정일</v>
       </c>
       <c r="G335" t="str">
-        <v>'후기 쓰기' 화면에서 전체 별점 주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'의 보증금 상태와 환급 예정일이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H335" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I335" t="str">
         <v/>
@@ -11538,7 +11538,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B336" t="str">
         <v/>
@@ -11553,10 +11553,10 @@
         <v/>
       </c>
       <c r="F336" t="str">
-        <v>항목별 별점(상태·설명과 같은지·수령 편의·응대)</v>
+        <v>수령 때와 반납 때 사진 견주기</v>
       </c>
       <c r="G336" t="str">
-        <v>'후기 쓰기' 화면에서 항목별 별점(상태·설명과 같은지·수령 편의·응대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 수령 때와 반납 때 사진 견주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H336" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11570,7 +11570,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B337" t="str">
         <v/>
@@ -11585,13 +11585,13 @@
         <v/>
       </c>
       <c r="F337" t="str">
-        <v>후기 글 쓰기</v>
+        <v>계약서와 정산서 내려받기</v>
       </c>
       <c r="G337" t="str">
-        <v>'후기 쓰기' 화면에서 후기 글 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 계약서와 정산서 내려받기를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H337" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I337" t="str">
         <v/>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B338" t="str">
         <v/>
@@ -11617,13 +11617,13 @@
         <v/>
       </c>
       <c r="F338" t="str">
-        <v>사진 올리기</v>
+        <v>상태에 따른 다음 행동 버튼</v>
       </c>
       <c r="G338" t="str">
-        <v>'후기 쓰기' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세'에서 상태에 따른 다음 행동 버튼을 눌러 본다.</v>
       </c>
       <c r="H338" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>설계한 화면으로 넘어가고, 뒤로 가기로 원래 화면에 되돌아온다.</v>
       </c>
       <c r="I338" t="str">
         <v/>
@@ -11634,7 +11634,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>SCN-033</v>
+        <v>SCN-032</v>
       </c>
       <c r="B339" t="str">
         <v/>
@@ -11649,10 +11649,10 @@
         <v/>
       </c>
       <c r="F339" t="str">
-        <v>어떤 용도로 썼는지 태그</v>
+        <v>이 대여 문의하기</v>
       </c>
       <c r="G339" t="str">
-        <v>'후기 쓰기' 화면에서 어떤 용도로 썼는지 태그가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 상세' 화면에서 이 대여 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H339" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11669,22 +11669,22 @@
         <v>SCN-033</v>
       </c>
       <c r="B340" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C340" t="str">
-        <v/>
+        <v>후기 쓰기</v>
       </c>
       <c r="D340" t="str">
-        <v/>
+        <v>MY-03</v>
       </c>
       <c r="E340" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F340" t="str">
-        <v>다음 사람에게 도움 될 팁 적기</v>
+        <v>빌린 장비 확인</v>
       </c>
       <c r="G340" t="str">
-        <v>'후기 쓰기' 화면에서 다음 사람에게 도움 될 팁 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 빌린 장비 확인이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H340" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11713,13 +11713,13 @@
         <v/>
       </c>
       <c r="F341" t="str">
-        <v>후기 작성 적립금 안내</v>
+        <v>전체 별점 주기</v>
       </c>
       <c r="G341" t="str">
-        <v>'후기 쓰기'의 후기 작성 적립금 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 쓰기' 화면에서 전체 별점 주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H341" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I341" t="str">
         <v/>
@@ -11745,10 +11745,10 @@
         <v/>
       </c>
       <c r="F342" t="str">
-        <v>사진 올리면 더 주는 혜택</v>
+        <v>항목별 별점(상태·설명과 같은지·수령 편의·응대)</v>
       </c>
       <c r="G342" t="str">
-        <v>'후기 쓰기' 화면에서 사진 올리면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 항목별 별점(상태·설명과 같은지·수령 편의·응대)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H342" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11777,10 +11777,10 @@
         <v/>
       </c>
       <c r="F343" t="str">
-        <v>비공개로 쓰기</v>
+        <v>후기 글 쓰기</v>
       </c>
       <c r="G343" t="str">
-        <v>'후기 쓰기' 화면에서 비공개로 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 후기 글 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H343" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11809,13 +11809,13 @@
         <v/>
       </c>
       <c r="F344" t="str">
-        <v>등록하기</v>
+        <v>사진 올리기</v>
       </c>
       <c r="G344" t="str">
-        <v>'후기 쓰기'의 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'후기 쓰기' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H344" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I344" t="str">
         <v/>
@@ -11826,25 +11826,25 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B345" t="str">
-        <v>마이페이지</v>
+        <v/>
       </c>
       <c r="C345" t="str">
-        <v>알림·쿠폰</v>
+        <v/>
       </c>
       <c r="D345" t="str">
-        <v>MY-04</v>
+        <v/>
       </c>
       <c r="E345" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F345" t="str">
-        <v>받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)</v>
+        <v>어떤 용도로 썼는지 태그</v>
       </c>
       <c r="G345" t="str">
-        <v>'알림·쿠폰' 화면에서 받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 어떤 용도로 썼는지 태그가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H345" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11858,7 +11858,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B346" t="str">
         <v/>
@@ -11873,10 +11873,10 @@
         <v/>
       </c>
       <c r="F346" t="str">
-        <v>알림 받을 방법(문자·카톡·이메일)</v>
+        <v>다음 사람에게 도움 될 팁 적기</v>
       </c>
       <c r="G346" t="str">
-        <v>'알림·쿠폰' 화면에서 알림 받을 방법(문자·카톡·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 다음 사람에게 도움 될 팁 적기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H346" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -11890,7 +11890,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B347" t="str">
         <v/>
@@ -11905,13 +11905,13 @@
         <v/>
       </c>
       <c r="F347" t="str">
-        <v>자리 나면 알림 신청 목록</v>
+        <v>후기 작성 적립금 안내</v>
       </c>
       <c r="G347" t="str">
-        <v>'알림·쿠폰'의 자리 나면 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 쓰기'의 후기 작성 적립금 안내에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H347" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I347" t="str">
         <v/>
@@ -11922,7 +11922,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B348" t="str">
         <v/>
@@ -11937,13 +11937,13 @@
         <v/>
       </c>
       <c r="F348" t="str">
-        <v>보유 쿠폰 목록과 남은 기간</v>
+        <v>사진 올리면 더 주는 혜택</v>
       </c>
       <c r="G348" t="str">
-        <v>'알림·쿠폰'의 보유 쿠폰 목록과 남은 기간을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'후기 쓰기' 화면에서 사진 올리면 더 주는 혜택이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H348" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I348" t="str">
         <v/>
@@ -11954,7 +11954,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B349" t="str">
         <v/>
@@ -11969,13 +11969,13 @@
         <v/>
       </c>
       <c r="F349" t="str">
-        <v>쿠폰 탭(사용가능·사용완료·기간만료)</v>
+        <v>비공개로 쓰기</v>
       </c>
       <c r="G349" t="str">
-        <v>'알림·쿠폰'에서 쿠폰 탭(사용가능·사용완료·기간만료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'후기 쓰기' 화면에서 비공개로 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H349" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I349" t="str">
         <v/>
@@ -11986,7 +11986,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>SCN-034</v>
+        <v>SCN-033</v>
       </c>
       <c r="B350" t="str">
         <v/>
@@ -12001,13 +12001,13 @@
         <v/>
       </c>
       <c r="F350" t="str">
-        <v>적립금 잔액과 쌓인 내역</v>
+        <v>등록하기</v>
       </c>
       <c r="G350" t="str">
-        <v>'알림·쿠폰' 화면에서 적립금 잔액과 쌓인 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'후기 쓰기'의 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H350" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I350" t="str">
         <v/>
@@ -12021,22 +12021,22 @@
         <v>SCN-034</v>
       </c>
       <c r="B351" t="str">
-        <v/>
+        <v>마이페이지</v>
       </c>
       <c r="C351" t="str">
-        <v/>
+        <v>알림·쿠폰</v>
       </c>
       <c r="D351" t="str">
-        <v/>
+        <v>MY-04</v>
       </c>
       <c r="E351" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F351" t="str">
-        <v>적립금 쓰는 법 안내</v>
+        <v>받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)</v>
       </c>
       <c r="G351" t="str">
-        <v>'알림·쿠폰' 화면에서 적립금 쓰는 법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰' 화면에서 받을 알림 켜고 끄기(수령 안내·반납 하루 전·반납 3시간 전·연체·점검 완료·환급 완료)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H351" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12065,13 +12065,13 @@
         <v/>
       </c>
       <c r="F352" t="str">
-        <v>보증금 면제까지 남은 횟수</v>
+        <v>알림 받을 방법(문자·카톡·이메일)</v>
       </c>
       <c r="G352" t="str">
-        <v>'알림·쿠폰'의 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
+        <v>'알림·쿠폰' 화면에서 알림 받을 방법(문자·카톡·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H352" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I352" t="str">
         <v/>
@@ -12097,13 +12097,13 @@
         <v/>
       </c>
       <c r="F353" t="str">
-        <v>쿠폰 등록하기</v>
+        <v>자리 나면 알림 신청 목록</v>
       </c>
       <c r="G353" t="str">
-        <v>'알림·쿠폰'의 쿠폰 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'알림·쿠폰'의 자리 나면 알림 신청 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H353" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I353" t="str">
         <v/>
@@ -12114,28 +12114,28 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B354" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C354" t="str">
-        <v>자주 묻는 질문</v>
+        <v/>
       </c>
       <c r="D354" t="str">
-        <v>CS-01</v>
+        <v/>
       </c>
       <c r="E354" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F354" t="str">
-        <v>질문 검색창</v>
+        <v>보유 쿠폰 목록과 남은 기간</v>
       </c>
       <c r="G354" t="str">
-        <v>'자주 묻는 질문'의 질문 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
+        <v>'알림·쿠폰'의 보유 쿠폰 목록과 남은 기간을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H354" t="str">
-        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I354" t="str">
         <v/>
@@ -12146,7 +12146,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B355" t="str">
         <v/>
@@ -12161,10 +12161,10 @@
         <v/>
       </c>
       <c r="F355" t="str">
-        <v>분류 탭(대여·보증금·수령배송·반납·연체파손·환불)</v>
+        <v>쿠폰 탭(사용가능·사용완료·기간만료)</v>
       </c>
       <c r="G355" t="str">
-        <v>'자주 묻는 질문'에서 분류 탭(대여·보증금·수령배송·반납·연체파손·환불)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'알림·쿠폰'에서 쿠폰 탭(사용가능·사용완료·기간만료)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H355" t="str">
         <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
@@ -12178,7 +12178,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B356" t="str">
         <v/>
@@ -12193,13 +12193,13 @@
         <v/>
       </c>
       <c r="F356" t="str">
-        <v>많이 찾는 질문 5개 먼저</v>
+        <v>적립금 잔액과 쌓인 내역</v>
       </c>
       <c r="G356" t="str">
-        <v>'자주 묻는 질문' 화면을 열고 많이 찾는 질문 5개 먼저가 적힌 수만큼 나오는지 세어 본다.</v>
+        <v>'알림·쿠폰' 화면에서 적립금 잔액과 쌓인 내역이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H356" t="str">
-        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I356" t="str">
         <v/>
@@ -12210,7 +12210,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B357" t="str">
         <v/>
@@ -12225,13 +12225,13 @@
         <v/>
       </c>
       <c r="F357" t="str">
-        <v>질문 아코디언 목록</v>
+        <v>적립금 쓰는 법 안내</v>
       </c>
       <c r="G357" t="str">
-        <v>'자주 묻는 질문'의 질문 아코디언 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
+        <v>'알림·쿠폰' 화면에서 적립금 쓰는 법 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H357" t="str">
-        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I357" t="str">
         <v/>
@@ -12242,7 +12242,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B358" t="str">
         <v/>
@@ -12257,13 +12257,13 @@
         <v/>
       </c>
       <c r="F358" t="str">
-        <v>답 안에서 관련 화면으로 바로 가기</v>
+        <v>보증금 면제까지 남은 횟수</v>
       </c>
       <c r="G358" t="str">
-        <v>'자주 묻는 질문' 화면에서 답 안에서 관련 화면으로 바로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰'의 보증금 면제까지 남은 횟수가 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H358" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I358" t="str">
         <v/>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>SCN-035</v>
+        <v>SCN-034</v>
       </c>
       <c r="B359" t="str">
         <v/>
@@ -12289,13 +12289,13 @@
         <v/>
       </c>
       <c r="F359" t="str">
-        <v>도움이 됐는지 묻기</v>
+        <v>쿠폰 등록하기</v>
       </c>
       <c r="G359" t="str">
-        <v>'자주 묻는 질문' 화면에서 도움이 됐는지 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'알림·쿠폰'의 쿠폰 등록하기에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H359" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I359" t="str">
         <v/>
@@ -12309,25 +12309,25 @@
         <v>SCN-035</v>
       </c>
       <c r="B360" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C360" t="str">
-        <v/>
+        <v>자주 묻는 질문</v>
       </c>
       <c r="D360" t="str">
-        <v/>
+        <v>CS-01</v>
       </c>
       <c r="E360" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F360" t="str">
-        <v>원하는 답이 없을 때 문의하기</v>
+        <v>질문 검색창</v>
       </c>
       <c r="G360" t="str">
-        <v>'자주 묻는 질문' 화면에서 원하는 답이 없을 때 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'의 질문 검색창에 빈 값과 잘못된 값을 각각 넣고 실행해 본다.</v>
       </c>
       <c r="H360" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>빈 값·잘못된 값에는 무엇이 잘못됐는지 안내가 뜨고, 올바른 값이면 다음 단계로 넘어간다.</v>
       </c>
       <c r="I360" t="str">
         <v/>
@@ -12353,13 +12353,13 @@
         <v/>
       </c>
       <c r="F361" t="str">
-        <v>고객센터 운영시간과 전화번호</v>
+        <v>분류 탭(대여·보증금·수령배송·반납·연체파손·환불)</v>
       </c>
       <c r="G361" t="str">
-        <v>'자주 묻는 질문' 화면에서 고객센터 운영시간과 전화번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문'에서 분류 탭(대여·보증금·수령배송·반납·연체파손·환불)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H361" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I361" t="str">
         <v/>
@@ -12370,28 +12370,28 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B362" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C362" t="str">
-        <v>1:1 문의</v>
+        <v/>
       </c>
       <c r="D362" t="str">
-        <v>CS-02</v>
+        <v/>
       </c>
       <c r="E362" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F362" t="str">
-        <v>문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)</v>
+        <v>많이 찾는 질문 5개 먼저</v>
       </c>
       <c r="G362" t="str">
-        <v>'1:1 문의' 화면에서 문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면을 열고 많이 찾는 질문 5개 먼저가 적힌 수만큼 나오는지 세어 본다.</v>
       </c>
       <c r="H362" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>적힌 개수가 빠짐없이 보이고, 깨진 이미지나 빈 칸이 없다.</v>
       </c>
       <c r="I362" t="str">
         <v/>
@@ -12402,7 +12402,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B363" t="str">
         <v/>
@@ -12417,13 +12417,13 @@
         <v/>
       </c>
       <c r="F363" t="str">
-        <v>관련 대여 건 고르기와 정보 자동 채움</v>
+        <v>질문 아코디언 목록</v>
       </c>
       <c r="G363" t="str">
-        <v>'1:1 문의'의 관련 대여 건 고르기와 정보 자동 채움이 실제 데이터와 같은지 대조한다.</v>
+        <v>'자주 묻는 질문'의 질문 아코디언 목록을 끝까지 내려 보고, 항목 하나를 눌러 본다.</v>
       </c>
       <c r="H363" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>항목이 잘리거나 겹치지 않고, 하나를 누르면 그 상세 화면으로 간다.</v>
       </c>
       <c r="I363" t="str">
         <v/>
@@ -12434,7 +12434,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B364" t="str">
         <v/>
@@ -12449,10 +12449,10 @@
         <v/>
       </c>
       <c r="F364" t="str">
-        <v>문의 내용 쓰기</v>
+        <v>답 안에서 관련 화면으로 바로 가기</v>
       </c>
       <c r="G364" t="str">
-        <v>'1:1 문의' 화면에서 문의 내용 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 답 안에서 관련 화면으로 바로 가기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H364" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12466,7 +12466,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B365" t="str">
         <v/>
@@ -12481,10 +12481,10 @@
         <v/>
       </c>
       <c r="F365" t="str">
-        <v>사진 올리기</v>
+        <v>도움이 됐는지 묻기</v>
       </c>
       <c r="G365" t="str">
-        <v>'1:1 문의' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 도움이 됐는지 묻기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H365" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B366" t="str">
         <v/>
@@ -12513,10 +12513,10 @@
         <v/>
       </c>
       <c r="F366" t="str">
-        <v>답변 받을 방법(문자·이메일)</v>
+        <v>원하는 답이 없을 때 문의하기</v>
       </c>
       <c r="G366" t="str">
-        <v>'1:1 문의' 화면에서 답변 받을 방법(문자·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 원하는 답이 없을 때 문의하기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H366" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12530,7 +12530,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>SCN-036</v>
+        <v>SCN-035</v>
       </c>
       <c r="B367" t="str">
         <v/>
@@ -12545,10 +12545,10 @@
         <v/>
       </c>
       <c r="F367" t="str">
-        <v>답변까지 걸리는 시간 안내</v>
+        <v>고객센터 운영시간과 전화번호</v>
       </c>
       <c r="G367" t="str">
-        <v>'1:1 문의' 화면에서 답변까지 걸리는 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'자주 묻는 질문' 화면에서 고객센터 운영시간과 전화번호가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H367" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12565,25 +12565,25 @@
         <v>SCN-036</v>
       </c>
       <c r="B368" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C368" t="str">
-        <v/>
+        <v>1:1 문의</v>
       </c>
       <c r="D368" t="str">
-        <v/>
+        <v>CS-02</v>
       </c>
       <c r="E368" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F368" t="str">
-        <v>정산 이의는 기한이 있다는 안내</v>
+        <v>문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)</v>
       </c>
       <c r="G368" t="str">
-        <v>'1:1 문의'에서 정산 이의는 기한이 있다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 종류 고르기(대여·보증금·정산 이의·파손·배송·기타)가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H368" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I368" t="str">
         <v/>
@@ -12609,13 +12609,13 @@
         <v/>
       </c>
       <c r="F369" t="str">
-        <v>지난 문의 내역과 답변</v>
+        <v>관련 대여 건 고르기와 정보 자동 채움</v>
       </c>
       <c r="G369" t="str">
-        <v>'1:1 문의' 화면에서 지난 문의 내역과 답변이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'의 관련 대여 건 고르기와 정보 자동 채움이 실제 데이터와 같은지 대조한다.</v>
       </c>
       <c r="H369" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
       </c>
       <c r="I369" t="str">
         <v/>
@@ -12641,10 +12641,10 @@
         <v/>
       </c>
       <c r="F370" t="str">
-        <v>급하면 전화 안내</v>
+        <v>문의 내용 쓰기</v>
       </c>
       <c r="G370" t="str">
-        <v>'1:1 문의' 화면에서 급하면 전화 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 내용 쓰기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H370" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12673,10 +12673,10 @@
         <v/>
       </c>
       <c r="F371" t="str">
-        <v>문의 보내기</v>
+        <v>사진 올리기</v>
       </c>
       <c r="G371" t="str">
-        <v>'1:1 문의' 화면에서 문의 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 사진 올리기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H371" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12690,25 +12690,25 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B372" t="str">
-        <v>고객센터</v>
+        <v/>
       </c>
       <c r="C372" t="str">
-        <v>대여 약관·규정</v>
+        <v/>
       </c>
       <c r="D372" t="str">
-        <v>CS-03</v>
+        <v/>
       </c>
       <c r="E372" t="str">
-        <v>기본</v>
+        <v/>
       </c>
       <c r="F372" t="str">
-        <v>한 줄 요약으로 먼저 보여주기</v>
+        <v>답변 받을 방법(문자·이메일)</v>
       </c>
       <c r="G372" t="str">
-        <v>'대여 약관·규정' 화면에서 한 줄 요약으로 먼저 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 답변 받을 방법(문자·이메일)이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H372" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B373" t="str">
         <v/>
@@ -12737,13 +12737,13 @@
         <v/>
       </c>
       <c r="F373" t="str">
-        <v>조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)</v>
+        <v>답변까지 걸리는 시간 안내</v>
       </c>
       <c r="G373" t="str">
-        <v>'대여 약관·규정'에서 조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
+        <v>'1:1 문의' 화면에서 답변까지 걸리는 시간 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H373" t="str">
-        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I373" t="str">
         <v/>
@@ -12754,7 +12754,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B374" t="str">
         <v/>
@@ -12769,13 +12769,13 @@
         <v/>
       </c>
       <c r="F374" t="str">
-        <v>연체료 계산 방식과 단계표</v>
+        <v>정산 이의는 기한이 있다는 안내</v>
       </c>
       <c r="G374" t="str">
-        <v>'대여 약관·규정' 화면에서 연체료 계산 방식과 단계표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의'에서 정산 이의는 기한이 있다는 안내를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
       </c>
       <c r="H374" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
       </c>
       <c r="I374" t="str">
         <v/>
@@ -12786,7 +12786,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B375" t="str">
         <v/>
@@ -12801,10 +12801,10 @@
         <v/>
       </c>
       <c r="F375" t="str">
-        <v>부품별 파손 배상 기준표</v>
+        <v>지난 문의 내역과 답변</v>
       </c>
       <c r="G375" t="str">
-        <v>'대여 약관·규정' 화면에서 부품별 파손 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'1:1 문의' 화면에서 지난 문의 내역과 답변이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H375" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12818,7 +12818,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B376" t="str">
         <v/>
@@ -12833,13 +12833,13 @@
         <v/>
       </c>
       <c r="F376" t="str">
-        <v>취소 시점별 환불율 단계표</v>
+        <v>급하면 전화 안내</v>
       </c>
       <c r="G376" t="str">
-        <v>'대여 약관·규정'에서 취소 시점별 환불율 단계표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'1:1 문의' 화면에서 급하면 전화 안내가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H376" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I376" t="str">
         <v/>
@@ -12850,7 +12850,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>SCN-037</v>
+        <v>SCN-036</v>
       </c>
       <c r="B377" t="str">
         <v/>
@@ -12865,13 +12865,13 @@
         <v/>
       </c>
       <c r="F377" t="str">
-        <v>무료 취소 기한 계산 예시</v>
+        <v>문의 보내기</v>
       </c>
       <c r="G377" t="str">
-        <v>'대여 약관·규정'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+        <v>'1:1 문의' 화면에서 문의 보내기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H377" t="str">
-        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I377" t="str">
         <v/>
@@ -12885,25 +12885,25 @@
         <v>SCN-037</v>
       </c>
       <c r="B378" t="str">
-        <v/>
+        <v>고객센터</v>
       </c>
       <c r="C378" t="str">
-        <v/>
+        <v>대여 약관·규정</v>
       </c>
       <c r="D378" t="str">
-        <v/>
+        <v>CS-03</v>
       </c>
       <c r="E378" t="str">
-        <v/>
+        <v>기본</v>
       </c>
       <c r="F378" t="str">
-        <v>반납 상태 기준(세척·건조)</v>
+        <v>한 줄 요약으로 먼저 보여주기</v>
       </c>
       <c r="G378" t="str">
-        <v>'대여 약관·규정'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+        <v>'대여 약관·규정' 화면에서 한 줄 요약으로 먼저 보여주기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H378" t="str">
-        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
       </c>
       <c r="I378" t="str">
         <v/>
@@ -12929,13 +12929,13 @@
         <v/>
       </c>
       <c r="F379" t="str">
-        <v>분실 처리 기준</v>
+        <v>조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)</v>
       </c>
       <c r="G379" t="str">
-        <v>'대여 약관·규정' 화면에서 분실 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정'에서 조항 탭(대여·보증금·연체·파손배상·취소환불·개인정보)의 조건을 바꿔 가며 결과가 달라지는지 본다.</v>
       </c>
       <c r="H379" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+        <v>고른 조건에 맞게 내용이 바뀌고, 해당하는 것이 없을 때는 빈 화면 안내가 뜬다.</v>
       </c>
       <c r="I379" t="str">
         <v/>
@@ -12961,10 +12961,10 @@
         <v/>
       </c>
       <c r="F380" t="str">
-        <v>내 대여로 계산해보기</v>
+        <v>연체료 계산 방식과 단계표</v>
       </c>
       <c r="G380" t="str">
-        <v>'대여 약관·규정' 화면에서 내 대여로 계산해보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정' 화면에서 연체료 계산 방식과 단계표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H380" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -12993,10 +12993,10 @@
         <v/>
       </c>
       <c r="F381" t="str">
-        <v>규정 바뀐 이력</v>
+        <v>부품별 파손 배상 기준표</v>
       </c>
       <c r="G381" t="str">
-        <v>'대여 약관·규정' 화면에서 규정 바뀐 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+        <v>'대여 약관·규정' 화면에서 부품별 파손 배상 기준표가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
       <c r="H381" t="str">
         <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
@@ -13025,24 +13025,216 @@
         <v/>
       </c>
       <c r="F382" t="str">
+        <v>취소 시점별 환불율 단계표</v>
+      </c>
+      <c r="G382" t="str">
+        <v>'대여 약관·규정'에서 취소 시점별 환불율 단계표를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H382" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I382" t="str">
+        <v/>
+      </c>
+      <c r="J382" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B383" t="str">
+        <v/>
+      </c>
+      <c r="C383" t="str">
+        <v/>
+      </c>
+      <c r="D383" t="str">
+        <v/>
+      </c>
+      <c r="E383" t="str">
+        <v/>
+      </c>
+      <c r="F383" t="str">
+        <v>무료 취소 기한 계산 예시</v>
+      </c>
+      <c r="G383" t="str">
+        <v>'대여 약관·규정'에서 무료 취소 기한 계산 예시를 성공·실패·취소 세 경우로 각각 끝까지 해 본다.</v>
+      </c>
+      <c r="H383" t="str">
+        <v>세 경우가 서로 다른 화면으로 안내되고, 중간에 멈추거나 같은 화면에 머무르지 않는다.</v>
+      </c>
+      <c r="I383" t="str">
+        <v/>
+      </c>
+      <c r="J383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B384" t="str">
+        <v/>
+      </c>
+      <c r="C384" t="str">
+        <v/>
+      </c>
+      <c r="D384" t="str">
+        <v/>
+      </c>
+      <c r="E384" t="str">
+        <v/>
+      </c>
+      <c r="F384" t="str">
+        <v>반납 상태 기준(세척·건조)</v>
+      </c>
+      <c r="G384" t="str">
+        <v>'대여 약관·규정'의 반납 상태 기준(세척·건조)가 실제 데이터와 같은지 대조한다.</v>
+      </c>
+      <c r="H384" t="str">
+        <v>표시된 값이 실제와 같고, 값이 없을 때 빈칸 대신 안내가 나온다.</v>
+      </c>
+      <c r="I384" t="str">
+        <v/>
+      </c>
+      <c r="J384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B385" t="str">
+        <v/>
+      </c>
+      <c r="C385" t="str">
+        <v/>
+      </c>
+      <c r="D385" t="str">
+        <v/>
+      </c>
+      <c r="E385" t="str">
+        <v/>
+      </c>
+      <c r="F385" t="str">
+        <v>분실 처리 기준</v>
+      </c>
+      <c r="G385" t="str">
+        <v>'대여 약관·규정' 화면에서 분실 처리 기준이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H385" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I385" t="str">
+        <v/>
+      </c>
+      <c r="J385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B386" t="str">
+        <v/>
+      </c>
+      <c r="C386" t="str">
+        <v/>
+      </c>
+      <c r="D386" t="str">
+        <v/>
+      </c>
+      <c r="E386" t="str">
+        <v/>
+      </c>
+      <c r="F386" t="str">
+        <v>내 대여로 계산해보기</v>
+      </c>
+      <c r="G386" t="str">
+        <v>'대여 약관·규정' 화면에서 내 대여로 계산해보기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H386" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I386" t="str">
+        <v/>
+      </c>
+      <c r="J386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B387" t="str">
+        <v/>
+      </c>
+      <c r="C387" t="str">
+        <v/>
+      </c>
+      <c r="D387" t="str">
+        <v/>
+      </c>
+      <c r="E387" t="str">
+        <v/>
+      </c>
+      <c r="F387" t="str">
+        <v>규정 바뀐 이력</v>
+      </c>
+      <c r="G387" t="str">
+        <v>'대여 약관·규정' 화면에서 규정 바뀐 이력이 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
+      </c>
+      <c r="H387" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I387" t="str">
+        <v/>
+      </c>
+      <c r="J387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>SCN-037</v>
+      </c>
+      <c r="B388" t="str">
+        <v/>
+      </c>
+      <c r="C388" t="str">
+        <v/>
+      </c>
+      <c r="D388" t="str">
+        <v/>
+      </c>
+      <c r="E388" t="str">
+        <v/>
+      </c>
+      <c r="F388" t="str">
         <v>약관 내려받기</v>
       </c>
-      <c r="G382" t="str">
+      <c r="G388" t="str">
         <v>'대여 약관·규정' 화면에서 약관 내려받기가 설계대로 있는지 보고, 누를 수 있으면 눌러 본다.</v>
       </c>
-      <c r="H382" t="str">
-        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
-      </c>
-      <c r="I382" t="str">
-        <v/>
-      </c>
-      <c r="J382" t="str">
+      <c r="H388" t="str">
+        <v>설계한 자리에 있고, 눌렀을 때 아무 반응이 없거나 오류가 나지 않는다.</v>
+      </c>
+      <c r="I388" t="str">
+        <v/>
+      </c>
+      <c r="J388" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J382"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J388"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
@@ -1412,10 +1412,10 @@
         <v>좁은 화면(모바일)에서 가로 스크롤</v>
       </c>
       <c r="G19" t="str">
-        <v>브라우저 폭을 375px로 좁혀 화면을 훑는다.</v>
+        <v>브라우저 폭을 390px 로 좁혀 화면을 훑고, 360px 로 한 번 더 훑는다. ⚠ 세로 flex 로 바꾼 상자의 자식이 밀리는 것은 390px 에서는 안 보이고 360px 에서만 나온다.</v>
       </c>
       <c r="H19" t="str">
-        <v>가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
+        <v>두 폭 모두에서 가로 스크롤이 생기지 않고, 내용이 화면 밖으로 나가지 않는다.</v>
       </c>
       <c r="I19" t="str">
         <v/>

--- a/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
+++ b/판매용_템플릿/_판매팩/장비렌탈_디럭스/08_검수시나리오.xlsx
@@ -1572,7 +1572,7 @@
         <v>글자 대비 — 색을 고른 뒤 반드시 잰다</v>
       </c>
       <c r="G24" t="str">
-        <v>스펙팩 7-9-2 가 가리키는 대로 브라우저에서 잰다. ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
+        <v>스펙팩 7-9 의 글을 화면에 붙여 넣으면 ⑧번이 잰다(7-9-2 는 파일만 보므로 대비를 재지 않는다). ⚠ 반투명 배경(10% 배지 등)은 «쌓아서» 진짜 바탕색을 구한 뒤 재야 한다 — 알파를 빼고 재면 멀쩡한 배지가 미달로 잡힌다.</v>
       </c>
       <c r="H24" t="str">
         <v>본문 4.5 이상, 24px 이상이거나 굵은 18.66px 이상은 3.0 이상. 미달 0건.</v>
